--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$429</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$663</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E429"/>
+  <dimension ref="A1:E663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11172,8 +11172,5858 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>штоки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>замена штоков dq200</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>пыльники штоков dq200</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>штоки вилок dq200</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>длина штоков dq200</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>замена штока мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>штоки переключения передач dq200</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>dq200 замена штоков сцепления</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>какие стоят штоки сцепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>стакан штока dq200</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200 отличия с 2012 года</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="n">
+        <v>72009</v>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>робот человек</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="n">
+        <v>62881</v>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>роботы под прикрытием</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="n">
+        <v>26120</v>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="n">
+        <v>20359</v>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="n">
+        <v>17816</v>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>робот emo</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="n">
+        <v>12708</v>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>трансмиссия это</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="n">
+        <v>9444</v>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>распаковка роботов</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="n">
+        <v>9100</v>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="n">
+        <v>9020</v>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>робот гуманоид</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="n">
+        <v>8636</v>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>боевой робот номер 4</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="n">
+        <v>7999</v>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="n">
+        <v>6423</v>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>дитя робота</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="n">
+        <v>6171</v>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="n">
+        <v>4794</v>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="n">
+        <v>4353</v>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается робот от автомата</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="n">
+        <v>4114</v>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается автомат от робота</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="n">
+        <v>4114</v>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника дсг</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="n">
+        <v>3968</v>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>коробка робот что это</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="n">
+        <v>3652</v>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>замена мехатроника</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="n">
+        <v>3480</v>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="n">
+        <v>3357</v>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника купить</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="n">
+        <v>3099</v>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="n">
+        <v>3049</v>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>что такое трансмиссия</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="n">
+        <v>2930</v>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>сервопривод это</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="n">
+        <v>2891</v>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 мехатроника</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="n">
+        <v>2666</v>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>робот козел</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="n">
+        <v>2531</v>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="n">
+        <v>2428</v>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="n">
+        <v>2262</v>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>ремонт мехатроника</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="n">
+        <v>2172</v>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника дсг 7</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="n">
+        <v>2134</v>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="n">
+        <v>2037</v>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="n">
+        <v>1937</v>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>роботех</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника кем работать</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="n">
+        <v>1805</v>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>коробка передач робот что это</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="n">
+        <v>1781</v>
+      </c>
+      <c r="D483" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="n">
+        <v>1716</v>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="n">
+        <v>1632</v>
+      </c>
+      <c r="D485" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника что за профессия</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="n">
+        <v>1626</v>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E486" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>робот федор</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="n">
+        <v>1602</v>
+      </c>
+      <c r="D487" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E487" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что за профессия</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="n">
+        <v>1557</v>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="D489" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dq250</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="D491" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника ауди</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="n">
+        <v>1312</v>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается коробка автомат от робота</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="n">
+        <v>1288</v>
+      </c>
+      <c r="D493" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>вкалывают роботы а не человек</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="n">
+        <v>1251</v>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>масло мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="n">
+        <v>1247</v>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается вариатор от робота</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="n">
+        <v>1197</v>
+      </c>
+      <c r="D497" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E497" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>снятие мехатроника</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="n">
+        <v>1188</v>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E498" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>цена мехатроника</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="n">
+        <v>1177</v>
+      </c>
+      <c r="D499" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E499" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="n">
+        <v>1147</v>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник шкода</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D503" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>замена масла в мехатронике</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника фольксваген</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>ремкомплект мехатроника</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника шкода октавия</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника факультеты</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника акпп</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="n">
+        <v>924</v>
+      </c>
+      <c r="D509" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="D511" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника обучение</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="n">
+        <v>882</v>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>масло мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника направления</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="n">
+        <v>862</v>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>замена мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="n">
+        <v>818</v>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>факультет мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="D521" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>r2d2 робот</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="n">
+        <v>691</v>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>направление мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="D523" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>обучение мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="n">
+        <v>678</v>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника вузы</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии светлый</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="D527" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>профессия мехатроника и робототехника кем работать</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="n">
+        <v>548</v>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>15.03 06 мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E530" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника баллы</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="D531" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E531" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми словами</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="n">
+        <v>457</v>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>институт мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>кем работают после мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>что такое мехатроник</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника университеты</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника поступить</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника зарплата</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника учиться</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>программа мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>15.02 10 мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>специалист по мехатронике и робототехнике</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника колледжи</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника предметы</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника проходные баллы</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника отзывы</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какая специальность</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>курс мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что это</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>магистратура робототехника и мехатроника</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>политех мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника код</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника учебный план</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника в машине это</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>15.02 10 мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника мгту</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника урфу</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>кафедры мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>мэи робототехника и мехатроника</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>баумана мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какой факультет</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в машине это</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>итмо мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>москва мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>спо мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника колледж кем работать</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника работа</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника юургу</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника спб</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника профессия это</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какие предметы</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после колледжа</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника робототехника и машиностроение</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это коробка</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в коробке передач это</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после вуза</t>
+        </is>
+      </c>
+      <c r="C585" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C586" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C587" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C588" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника по отраслям что это</t>
+        </is>
+      </c>
+      <c r="C589" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что это за профессия</t>
+        </is>
+      </c>
+      <c r="C590" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что за профессия зарплата</t>
+        </is>
+      </c>
+      <c r="C592" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C593" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника в автомобиле это</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C605" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроника это</t>
+        </is>
+      </c>
+      <c r="C606" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C607" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C608" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник что это такое в автомобиле</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроник это</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника что это за специальность</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника это</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это профессия</t>
+        </is>
+      </c>
+      <c r="C615" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника что за профессия</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>техник мехатроника это</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника акпп это</t>
+        </is>
+      </c>
+      <c r="C624" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C626" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C627" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C628" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C629" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C630" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C632" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg это</t>
+        </is>
+      </c>
+      <c r="C633" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми словами в машине</t>
+        </is>
+      </c>
+      <c r="C635" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C636" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника что это</t>
+        </is>
+      </c>
+      <c r="C637" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C638" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в акпп что это</t>
+        </is>
+      </c>
+      <c r="C639" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в дсг это</t>
+        </is>
+      </c>
+      <c r="C640" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в авто это</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это простыми словами</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроник это кто и чем занимается</t>
+        </is>
+      </c>
+      <c r="C643" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D643" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>техник мехатроник это</t>
+        </is>
+      </c>
+      <c r="C644" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D644" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии город светлый</t>
+        </is>
+      </c>
+      <c r="C645" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D645" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>специалист по мехатронике и робототехнике это</t>
+        </is>
+      </c>
+      <c r="C646" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D646" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 это</t>
+        </is>
+      </c>
+      <c r="C647" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D647" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>компьютерная мехатроника это</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="D649" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>штоки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="D650" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200</t>
+        </is>
+      </c>
+      <c r="C651" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D651" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>замена штоков dq200</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>пыльники штоков dq200</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D653" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C654" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D654" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B655" s="2" t="inlineStr">
+        <is>
+          <t>штоки вилок dq200</t>
+        </is>
+      </c>
+      <c r="C655" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D655" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>длина штоков dq200</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D656" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t>замена штока мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D657" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D658" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E658" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>штоки переключения передач dq200</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D659" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>dq200 замена штоков сцепления</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D660" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B661" s="2" t="inlineStr">
+        <is>
+          <t>какие стоят штоки сцепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C661" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D661" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>стакан штока dq200</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D662" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B663" s="2" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200 отличия с 2012 года</t>
+        </is>
+      </c>
+      <c r="C663" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D663" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E429"/>
+  <autoFilter ref="A1:E663"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1533</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1769</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1533"/>
+  <dimension ref="A1:E1769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -38772,8 +38772,5908 @@
         </is>
       </c>
     </row>
+    <row r="1534">
+      <c r="A1534" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1534" s="2" t="inlineStr">
+        <is>
+          <t>кпп это</t>
+        </is>
+      </c>
+      <c r="C1534" s="2" t="n">
+        <v>34915</v>
+      </c>
+      <c r="D1534" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1534" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1535" s="2" t="inlineStr">
+        <is>
+          <t>определение скорости клубочковой фильтрации</t>
+        </is>
+      </c>
+      <c r="C1535" s="2" t="n">
+        <v>7201</v>
+      </c>
+      <c r="D1535" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1535" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1536" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается вариатор от автомата</t>
+        </is>
+      </c>
+      <c r="C1536" s="2" t="n">
+        <v>3421</v>
+      </c>
+      <c r="D1536" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1536" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1537" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается автомат от вариатора</t>
+        </is>
+      </c>
+      <c r="C1537" s="2" t="n">
+        <v>3421</v>
+      </c>
+      <c r="D1537" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1537" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1538" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации анализ крови что это</t>
+        </is>
+      </c>
+      <c r="C1538" s="2" t="n">
+        <v>2243</v>
+      </c>
+      <c r="D1538" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1538" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1539" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это</t>
+        </is>
+      </c>
+      <c r="C1539" s="2" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D1539" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1539" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1540" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается робот от автомата в машине</t>
+        </is>
+      </c>
+      <c r="C1540" s="2" t="n">
+        <v>681</v>
+      </c>
+      <c r="D1540" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1540" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1541" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C1541" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="D1541" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1541" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1542" s="2" t="inlineStr">
+        <is>
+          <t>атп шоп запчасти для акпп</t>
+        </is>
+      </c>
+      <c r="C1542" s="2" t="n">
+        <v>492</v>
+      </c>
+      <c r="D1542" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1542" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1543" s="2" t="inlineStr">
+        <is>
+          <t>коробка распаячная 80х80х40</t>
+        </is>
+      </c>
+      <c r="C1543" s="2" t="n">
+        <v>485</v>
+      </c>
+      <c r="D1543" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1543" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1544" s="2" t="inlineStr">
+        <is>
+          <t>вариатор это автомат или механика</t>
+        </is>
+      </c>
+      <c r="C1544" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="D1544" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1544" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1545" s="2" t="inlineStr">
+        <is>
+          <t>трансдеталь запчасти для акпп</t>
+        </is>
+      </c>
+      <c r="C1545" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="D1545" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1545" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1546" s="2" t="inlineStr">
+        <is>
+          <t>atpshop запчасти акпп</t>
+        </is>
+      </c>
+      <c r="C1546" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="D1546" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1546" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1547" s="2" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1547" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="D1547" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1547" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1548" s="2" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1548" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="D1548" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1548" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1549" s="2" t="inlineStr">
+        <is>
+          <t>атп шоп запчасти для акпп москва</t>
+        </is>
+      </c>
+      <c r="C1549" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1549" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1549" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1550" s="2" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1550" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1550" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1550" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1551" s="2" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1551" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1551" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1551" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1552" s="2" t="inlineStr">
+        <is>
+          <t>замена крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1552" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1552" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1552" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1553" s="2" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1553" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1553" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1553" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1554" s="2" t="inlineStr">
+        <is>
+          <t>тверь крышка мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1554" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1554" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1554" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1555" s="2" t="inlineStr">
+        <is>
+          <t>крышка сапуна мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1555" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1555" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1555" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1556" s="2" t="inlineStr">
+        <is>
+          <t>замена прокладки крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1556" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1556" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1556" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B1557" s="2" t="inlineStr">
+        <is>
+          <t>степень затяжки болтов крышки мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C1557" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1557" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1557" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1558" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника</t>
+        </is>
+      </c>
+      <c r="C1558" s="2" t="n">
+        <v>72009</v>
+      </c>
+      <c r="D1558" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1558" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1559" s="2" t="inlineStr">
+        <is>
+          <t>робот человек</t>
+        </is>
+      </c>
+      <c r="C1559" s="2" t="n">
+        <v>62881</v>
+      </c>
+      <c r="D1559" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1559" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1560" s="2" t="inlineStr">
+        <is>
+          <t>роботы под прикрытием</t>
+        </is>
+      </c>
+      <c r="C1560" s="2" t="n">
+        <v>26120</v>
+      </c>
+      <c r="D1560" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1560" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1561" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник</t>
+        </is>
+      </c>
+      <c r="C1561" s="2" t="n">
+        <v>20359</v>
+      </c>
+      <c r="D1561" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1561" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1562" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1562" s="2" t="n">
+        <v>17816</v>
+      </c>
+      <c r="D1562" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1562" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1563" s="2" t="inlineStr">
+        <is>
+          <t>робот emo</t>
+        </is>
+      </c>
+      <c r="C1563" s="2" t="n">
+        <v>12708</v>
+      </c>
+      <c r="D1563" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1563" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1564" s="2" t="inlineStr">
+        <is>
+          <t>трансмиссия это</t>
+        </is>
+      </c>
+      <c r="C1564" s="2" t="n">
+        <v>9444</v>
+      </c>
+      <c r="D1564" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1564" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1565" s="2" t="inlineStr">
+        <is>
+          <t>распаковка роботов</t>
+        </is>
+      </c>
+      <c r="C1565" s="2" t="n">
+        <v>9100</v>
+      </c>
+      <c r="D1565" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1565" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1566" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1566" s="2" t="n">
+        <v>9020</v>
+      </c>
+      <c r="D1566" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1566" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1567" s="2" t="inlineStr">
+        <is>
+          <t>робот гуманоид</t>
+        </is>
+      </c>
+      <c r="C1567" s="2" t="n">
+        <v>8636</v>
+      </c>
+      <c r="D1567" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1567" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1568" s="2" t="inlineStr">
+        <is>
+          <t>боевой робот номер 4</t>
+        </is>
+      </c>
+      <c r="C1568" s="2" t="n">
+        <v>7999</v>
+      </c>
+      <c r="D1568" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1568" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1569" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C1569" s="2" t="n">
+        <v>6423</v>
+      </c>
+      <c r="D1569" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1569" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1570" s="2" t="inlineStr">
+        <is>
+          <t>дитя робота</t>
+        </is>
+      </c>
+      <c r="C1570" s="2" t="n">
+        <v>6171</v>
+      </c>
+      <c r="D1570" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1570" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1571" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника</t>
+        </is>
+      </c>
+      <c r="C1571" s="2" t="n">
+        <v>4794</v>
+      </c>
+      <c r="D1571" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1571" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1572" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C1572" s="2" t="n">
+        <v>4353</v>
+      </c>
+      <c r="D1572" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1572" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1573" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается робот от автомата</t>
+        </is>
+      </c>
+      <c r="C1573" s="2" t="n">
+        <v>4114</v>
+      </c>
+      <c r="D1573" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1573" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1574" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается автомат от робота</t>
+        </is>
+      </c>
+      <c r="C1574" s="2" t="n">
+        <v>4114</v>
+      </c>
+      <c r="D1574" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1574" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1575" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника дсг</t>
+        </is>
+      </c>
+      <c r="C1575" s="2" t="n">
+        <v>3968</v>
+      </c>
+      <c r="D1575" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1575" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1576" s="2" t="inlineStr">
+        <is>
+          <t>коробка робот что это</t>
+        </is>
+      </c>
+      <c r="C1576" s="2" t="n">
+        <v>3652</v>
+      </c>
+      <c r="D1576" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1576" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1577" s="2" t="inlineStr">
+        <is>
+          <t>замена мехатроника</t>
+        </is>
+      </c>
+      <c r="C1577" s="2" t="n">
+        <v>3480</v>
+      </c>
+      <c r="D1577" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1577" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1578" s="2" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1578" s="2" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1578" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1578" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1579" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это</t>
+        </is>
+      </c>
+      <c r="C1579" s="2" t="n">
+        <v>3357</v>
+      </c>
+      <c r="D1579" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1579" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1580" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника купить</t>
+        </is>
+      </c>
+      <c r="C1580" s="2" t="n">
+        <v>3099</v>
+      </c>
+      <c r="D1580" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1580" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1581" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники</t>
+        </is>
+      </c>
+      <c r="C1581" s="2" t="n">
+        <v>3049</v>
+      </c>
+      <c r="D1581" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1581" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1582" s="2" t="inlineStr">
+        <is>
+          <t>что такое трансмиссия</t>
+        </is>
+      </c>
+      <c r="C1582" s="2" t="n">
+        <v>2930</v>
+      </c>
+      <c r="D1582" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1582" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1583" s="2" t="inlineStr">
+        <is>
+          <t>сервопривод это</t>
+        </is>
+      </c>
+      <c r="C1583" s="2" t="n">
+        <v>2891</v>
+      </c>
+      <c r="D1583" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1583" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1584" s="2" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 мехатроника</t>
+        </is>
+      </c>
+      <c r="C1584" s="2" t="n">
+        <v>2666</v>
+      </c>
+      <c r="D1584" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1584" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1585" s="2" t="inlineStr">
+        <is>
+          <t>робот козел</t>
+        </is>
+      </c>
+      <c r="C1585" s="2" t="n">
+        <v>2531</v>
+      </c>
+      <c r="D1585" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1585" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1586" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что</t>
+        </is>
+      </c>
+      <c r="C1586" s="2" t="n">
+        <v>2428</v>
+      </c>
+      <c r="D1586" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1586" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1587" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg</t>
+        </is>
+      </c>
+      <c r="C1587" s="2" t="n">
+        <v>2262</v>
+      </c>
+      <c r="D1587" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1587" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1588" s="2" t="inlineStr">
+        <is>
+          <t>ремонт мехатроника</t>
+        </is>
+      </c>
+      <c r="C1588" s="2" t="n">
+        <v>2172</v>
+      </c>
+      <c r="D1588" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1588" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1589" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника дсг 7</t>
+        </is>
+      </c>
+      <c r="C1589" s="2" t="n">
+        <v>2134</v>
+      </c>
+      <c r="D1589" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1589" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1590" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг</t>
+        </is>
+      </c>
+      <c r="C1590" s="2" t="n">
+        <v>2037</v>
+      </c>
+      <c r="D1590" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1590" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1591" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1591" s="2" t="n">
+        <v>1937</v>
+      </c>
+      <c r="D1591" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1591" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1592" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1592" s="2" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D1592" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1592" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1593" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1593" s="2" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D1593" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1593" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1594" s="2" t="inlineStr">
+        <is>
+          <t>роботех</t>
+        </is>
+      </c>
+      <c r="C1594" s="2" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D1594" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1594" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1595" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника кем работать</t>
+        </is>
+      </c>
+      <c r="C1595" s="2" t="n">
+        <v>1805</v>
+      </c>
+      <c r="D1595" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1595" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1596" s="2" t="inlineStr">
+        <is>
+          <t>коробка передач робот что это</t>
+        </is>
+      </c>
+      <c r="C1596" s="2" t="n">
+        <v>1781</v>
+      </c>
+      <c r="D1596" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1596" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1597" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать</t>
+        </is>
+      </c>
+      <c r="C1597" s="2" t="n">
+        <v>1716</v>
+      </c>
+      <c r="D1597" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1597" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1598" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1598" s="2" t="n">
+        <v>1632</v>
+      </c>
+      <c r="D1598" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1598" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1599" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника что за профессия</t>
+        </is>
+      </c>
+      <c r="C1599" s="2" t="n">
+        <v>1626</v>
+      </c>
+      <c r="D1599" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1599" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1600" s="2" t="inlineStr">
+        <is>
+          <t>робот федор</t>
+        </is>
+      </c>
+      <c r="C1600" s="2" t="n">
+        <v>1602</v>
+      </c>
+      <c r="D1600" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1600" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1601" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что за профессия</t>
+        </is>
+      </c>
+      <c r="C1601" s="2" t="n">
+        <v>1557</v>
+      </c>
+      <c r="D1601" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1601" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1602" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7</t>
+        </is>
+      </c>
+      <c r="C1602" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="D1602" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1602" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1603" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1603" s="2" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D1603" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1603" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1604" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dq250</t>
+        </is>
+      </c>
+      <c r="C1604" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="D1604" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1604" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1605" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника ауди</t>
+        </is>
+      </c>
+      <c r="C1605" s="2" t="n">
+        <v>1312</v>
+      </c>
+      <c r="D1605" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1605" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1606" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается коробка автомат от робота</t>
+        </is>
+      </c>
+      <c r="C1606" s="2" t="n">
+        <v>1288</v>
+      </c>
+      <c r="D1606" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1606" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1607" s="2" t="inlineStr">
+        <is>
+          <t>вкалывают роботы а не человек</t>
+        </is>
+      </c>
+      <c r="C1607" s="2" t="n">
+        <v>1251</v>
+      </c>
+      <c r="D1607" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1607" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1608" s="2" t="inlineStr">
+        <is>
+          <t>масло мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C1608" s="2" t="n">
+        <v>1247</v>
+      </c>
+      <c r="D1608" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1608" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1609" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C1609" s="2" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D1609" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1609" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1610" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается вариатор от робота</t>
+        </is>
+      </c>
+      <c r="C1610" s="2" t="n">
+        <v>1197</v>
+      </c>
+      <c r="D1610" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1610" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1611" s="2" t="inlineStr">
+        <is>
+          <t>снятие мехатроника</t>
+        </is>
+      </c>
+      <c r="C1611" s="2" t="n">
+        <v>1188</v>
+      </c>
+      <c r="D1611" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1611" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1612" s="2" t="inlineStr">
+        <is>
+          <t>цена мехатроника</t>
+        </is>
+      </c>
+      <c r="C1612" s="2" t="n">
+        <v>1177</v>
+      </c>
+      <c r="D1612" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1612" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1613" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это</t>
+        </is>
+      </c>
+      <c r="C1613" s="2" t="n">
+        <v>1147</v>
+      </c>
+      <c r="D1613" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1613" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1614" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7</t>
+        </is>
+      </c>
+      <c r="C1614" s="2" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D1614" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1614" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1615" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник шкода</t>
+        </is>
+      </c>
+      <c r="C1615" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="D1615" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1615" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1616" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1616" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1616" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1616" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1617" s="2" t="inlineStr">
+        <is>
+          <t>замена масла в мехатронике</t>
+        </is>
+      </c>
+      <c r="C1617" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D1617" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1617" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1618" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника фольксваген</t>
+        </is>
+      </c>
+      <c r="C1618" s="2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D1618" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1618" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1619" s="2" t="inlineStr">
+        <is>
+          <t>ремкомплект мехатроника</t>
+        </is>
+      </c>
+      <c r="C1619" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="D1619" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1619" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1620" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника шкода октавия</t>
+        </is>
+      </c>
+      <c r="C1620" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="D1620" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1620" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1621" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника факультеты</t>
+        </is>
+      </c>
+      <c r="C1621" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="D1621" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1621" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1622" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника акпп</t>
+        </is>
+      </c>
+      <c r="C1622" s="2" t="n">
+        <v>924</v>
+      </c>
+      <c r="D1622" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1622" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1623" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1623" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1623" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1623" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1624" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой</t>
+        </is>
+      </c>
+      <c r="C1624" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="D1624" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1624" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1625" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника обучение</t>
+        </is>
+      </c>
+      <c r="C1625" s="2" t="n">
+        <v>882</v>
+      </c>
+      <c r="D1625" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1625" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1626" s="2" t="inlineStr">
+        <is>
+          <t>масло мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C1626" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="D1626" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1626" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1627" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1627" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1627" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1627" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1628" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника направления</t>
+        </is>
+      </c>
+      <c r="C1628" s="2" t="n">
+        <v>862</v>
+      </c>
+      <c r="D1628" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1628" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1629" s="2" t="inlineStr">
+        <is>
+          <t>замена мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1629" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="D1629" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1629" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1630" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C1630" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="D1630" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1630" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1631" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии</t>
+        </is>
+      </c>
+      <c r="C1631" s="2" t="n">
+        <v>818</v>
+      </c>
+      <c r="D1631" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1631" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1632" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C1632" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="D1632" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1632" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1633" s="2" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1633" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1633" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1633" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1634" s="2" t="inlineStr">
+        <is>
+          <t>факультет мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1634" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="D1634" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1634" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1635" s="2" t="inlineStr">
+        <is>
+          <t>r2d2 робот</t>
+        </is>
+      </c>
+      <c r="C1635" s="2" t="n">
+        <v>691</v>
+      </c>
+      <c r="D1635" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1635" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1636" s="2" t="inlineStr">
+        <is>
+          <t>направление мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1636" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="D1636" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1636" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1637" s="2" t="inlineStr">
+        <is>
+          <t>обучение мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1637" s="2" t="n">
+        <v>678</v>
+      </c>
+      <c r="D1637" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1637" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1638" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника вузы</t>
+        </is>
+      </c>
+      <c r="C1638" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="D1638" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1638" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1639" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии светлый</t>
+        </is>
+      </c>
+      <c r="C1639" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="D1639" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1639" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1640" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C1640" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="D1640" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1640" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1641" s="2" t="inlineStr">
+        <is>
+          <t>профессия мехатроника и робототехника кем работать</t>
+        </is>
+      </c>
+      <c r="C1641" s="2" t="n">
+        <v>548</v>
+      </c>
+      <c r="D1641" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1641" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1642" s="2" t="inlineStr">
+        <is>
+          <t>15.03 06 мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1642" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="D1642" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1642" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1643" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми</t>
+        </is>
+      </c>
+      <c r="C1643" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="D1643" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1643" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1644" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника баллы</t>
+        </is>
+      </c>
+      <c r="C1644" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="D1644" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1644" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1645" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми словами</t>
+        </is>
+      </c>
+      <c r="C1645" s="2" t="n">
+        <v>457</v>
+      </c>
+      <c r="D1645" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1645" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1646" s="2" t="inlineStr">
+        <is>
+          <t>институт мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1646" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="D1646" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1646" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1647" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1647" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1647" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1647" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1648" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1648" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1648" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1648" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1649" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника</t>
+        </is>
+      </c>
+      <c r="C1649" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="D1649" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1649" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1650" s="2" t="inlineStr">
+        <is>
+          <t>кем работают после мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1650" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="D1650" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1650" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1651" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1651" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1651" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1651" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1652" s="2" t="inlineStr">
+        <is>
+          <t>что такое мехатроник</t>
+        </is>
+      </c>
+      <c r="C1652" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="D1652" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1652" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1653" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника университеты</t>
+        </is>
+      </c>
+      <c r="C1653" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="D1653" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1653" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1654" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника поступить</t>
+        </is>
+      </c>
+      <c r="C1654" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="D1654" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1654" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1655" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника зарплата</t>
+        </is>
+      </c>
+      <c r="C1655" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="D1655" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1655" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1656" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника учиться</t>
+        </is>
+      </c>
+      <c r="C1656" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="D1656" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1656" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1657" s="2" t="inlineStr">
+        <is>
+          <t>программа мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1657" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="D1657" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1657" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1658" s="2" t="inlineStr">
+        <is>
+          <t>15.02 10 мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1658" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="D1658" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1658" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1659" s="2" t="inlineStr">
+        <is>
+          <t>специалист по мехатронике и робототехнике</t>
+        </is>
+      </c>
+      <c r="C1659" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="D1659" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1659" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1660" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника колледжи</t>
+        </is>
+      </c>
+      <c r="C1660" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="D1660" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1660" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1661" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника предметы</t>
+        </is>
+      </c>
+      <c r="C1661" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="D1661" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1661" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1662" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника проходные баллы</t>
+        </is>
+      </c>
+      <c r="C1662" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="D1662" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1662" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1663" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника отзывы</t>
+        </is>
+      </c>
+      <c r="C1663" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="D1663" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1663" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1664" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какая специальность</t>
+        </is>
+      </c>
+      <c r="C1664" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="D1664" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1664" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1665" s="2" t="inlineStr">
+        <is>
+          <t>курс мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1665" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="D1665" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1665" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1666" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что это</t>
+        </is>
+      </c>
+      <c r="C1666" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="D1666" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1666" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1667" s="2" t="inlineStr">
+        <is>
+          <t>магистратура робототехника и мехатроника</t>
+        </is>
+      </c>
+      <c r="C1667" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="D1667" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1667" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1668" s="2" t="inlineStr">
+        <is>
+          <t>политех мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1668" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="D1668" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1668" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1669" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника код</t>
+        </is>
+      </c>
+      <c r="C1669" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="D1669" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1669" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1670" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника учебный план</t>
+        </is>
+      </c>
+      <c r="C1670" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D1670" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1670" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1671" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника в машине это</t>
+        </is>
+      </c>
+      <c r="C1671" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D1671" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1671" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1672" s="2" t="inlineStr">
+        <is>
+          <t>15.02 10 мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C1672" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="D1672" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1672" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1673" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника мгту</t>
+        </is>
+      </c>
+      <c r="C1673" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="D1673" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1673" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1674" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника урфу</t>
+        </is>
+      </c>
+      <c r="C1674" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="D1674" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1674" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1675" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1675" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1675" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1675" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1676" s="2" t="inlineStr">
+        <is>
+          <t>кафедры мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1676" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D1676" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1676" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1677" s="2" t="inlineStr">
+        <is>
+          <t>мэи робототехника и мехатроника</t>
+        </is>
+      </c>
+      <c r="C1677" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D1677" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1677" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1678" s="2" t="inlineStr">
+        <is>
+          <t>баумана мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1678" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="D1678" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1678" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1679" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1679" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1679" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1679" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1680" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какой факультет</t>
+        </is>
+      </c>
+      <c r="C1680" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="D1680" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1680" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1681" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1681" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1681" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1681" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1682" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1682" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1682" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1682" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1683" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в машине это</t>
+        </is>
+      </c>
+      <c r="C1683" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D1683" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1683" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1684" s="2" t="inlineStr">
+        <is>
+          <t>итмо мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1684" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="D1684" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1684" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1685" s="2" t="inlineStr">
+        <is>
+          <t>москва мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1685" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="D1685" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1685" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1686" s="2" t="inlineStr">
+        <is>
+          <t>спо мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1686" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D1686" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1686" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1687" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника колледж кем работать</t>
+        </is>
+      </c>
+      <c r="C1687" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D1687" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1687" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1688" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника работа</t>
+        </is>
+      </c>
+      <c r="C1688" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="D1688" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1688" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1689" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника юургу</t>
+        </is>
+      </c>
+      <c r="C1689" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="D1689" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1689" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1690" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника спб</t>
+        </is>
+      </c>
+      <c r="C1690" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="D1690" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1690" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1691" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника профессия это</t>
+        </is>
+      </c>
+      <c r="C1691" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="D1691" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1691" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1692" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какие предметы</t>
+        </is>
+      </c>
+      <c r="C1692" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1692" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1692" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1693" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после колледжа</t>
+        </is>
+      </c>
+      <c r="C1693" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="D1693" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1693" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1694" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника робототехника и машиностроение</t>
+        </is>
+      </c>
+      <c r="C1694" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="D1694" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1694" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1695" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это коробка</t>
+        </is>
+      </c>
+      <c r="C1695" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="D1695" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1695" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1696" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1696" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1696" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1696" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1697" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в коробке передач это</t>
+        </is>
+      </c>
+      <c r="C1697" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="D1697" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1697" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1698" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после вуза</t>
+        </is>
+      </c>
+      <c r="C1698" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="D1698" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1698" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1699" s="2" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1699" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1699" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1699" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1700" s="2" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1700" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1700" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1700" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1701" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1701" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1701" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1701" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1702" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника по отраслям что это</t>
+        </is>
+      </c>
+      <c r="C1702" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D1702" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1702" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1703" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что это за профессия</t>
+        </is>
+      </c>
+      <c r="C1703" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D1703" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1703" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1704" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1704" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1704" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1704" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1705" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что за профессия зарплата</t>
+        </is>
+      </c>
+      <c r="C1705" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="D1705" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1705" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1706" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1706" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1706" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1706" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1707" s="2" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1707" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1707" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1707" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1708" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1708" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1708" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1708" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1709" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1709" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1709" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1709" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1710" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1710" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1710" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1710" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1711" s="2" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1711" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1711" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1711" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1712" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1712" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1712" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1712" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1713" s="2" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1713" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1713" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1713" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1714" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1714" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1714" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1714" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1715" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника в автомобиле это</t>
+        </is>
+      </c>
+      <c r="C1715" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D1715" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1715" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1716" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1716" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1716" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1716" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1717" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1717" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1717" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1717" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1718" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1718" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1718" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1718" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1719" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроника это</t>
+        </is>
+      </c>
+      <c r="C1719" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1719" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1719" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1720" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1720" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1720" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1720" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1721" s="2" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1721" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1721" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1721" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1722" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1722" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1722" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1722" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1723" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1723" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1723" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1723" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1724" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник что это такое в автомобиле</t>
+        </is>
+      </c>
+      <c r="C1724" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1724" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1724" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1725" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроник это</t>
+        </is>
+      </c>
+      <c r="C1725" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1725" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1725" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1726" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника что это за специальность</t>
+        </is>
+      </c>
+      <c r="C1726" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="D1726" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1726" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1727" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника это</t>
+        </is>
+      </c>
+      <c r="C1727" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D1727" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1727" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1728" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это профессия</t>
+        </is>
+      </c>
+      <c r="C1728" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D1728" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1728" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1729" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1729" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1729" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1729" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1730" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1730" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1730" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1730" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1731" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника что за профессия</t>
+        </is>
+      </c>
+      <c r="C1731" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D1731" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1731" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1732" s="2" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1732" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1732" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1732" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1733" s="2" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1733" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1733" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1733" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1734" s="2" t="inlineStr">
+        <is>
+          <t>техник мехатроника это</t>
+        </is>
+      </c>
+      <c r="C1734" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D1734" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1734" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1735" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1735" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1735" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1735" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1736" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1736" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1736" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1736" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1737" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника акпп это</t>
+        </is>
+      </c>
+      <c r="C1737" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1737" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1737" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1738" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1738" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1738" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1738" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1739" s="2" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1739" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1739" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1739" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1740" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1740" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1740" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1740" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1741" s="2" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1741" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1741" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1741" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1742" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1742" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1742" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1742" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1743" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1743" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1743" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1743" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1744" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1744" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1744" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1744" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1745" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1745" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1745" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1745" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1746" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg это</t>
+        </is>
+      </c>
+      <c r="C1746" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1746" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1746" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1747" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1747" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1747" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1747" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1748" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми словами в машине</t>
+        </is>
+      </c>
+      <c r="C1748" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1748" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1748" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1749" s="2" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1749" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1749" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1749" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1750" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника что это</t>
+        </is>
+      </c>
+      <c r="C1750" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1750" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1750" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1751" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1751" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1751" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1751" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1752" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в акпп что это</t>
+        </is>
+      </c>
+      <c r="C1752" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1752" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1752" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1753" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в дсг это</t>
+        </is>
+      </c>
+      <c r="C1753" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1753" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1753" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1754" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в авто это</t>
+        </is>
+      </c>
+      <c r="C1754" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1754" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1754" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1755" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это простыми словами</t>
+        </is>
+      </c>
+      <c r="C1755" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1755" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1755" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1756" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроник это кто и чем занимается</t>
+        </is>
+      </c>
+      <c r="C1756" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1756" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1756" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1757" s="2" t="inlineStr">
+        <is>
+          <t>техник мехатроник это</t>
+        </is>
+      </c>
+      <c r="C1757" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1757" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1757" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1758" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии город светлый</t>
+        </is>
+      </c>
+      <c r="C1758" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1758" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1758" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1759" s="2" t="inlineStr">
+        <is>
+          <t>специалист по мехатронике и робототехнике это</t>
+        </is>
+      </c>
+      <c r="C1759" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1759" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1759" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1760" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 это</t>
+        </is>
+      </c>
+      <c r="C1760" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1760" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1760" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="2" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B1761" s="2" t="inlineStr">
+        <is>
+          <t>компьютерная мехатроника это</t>
+        </is>
+      </c>
+      <c r="C1761" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1761" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1761" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B1762" s="2" t="inlineStr">
+        <is>
+          <t>допустимая величина бокового сдвига редуктора на оси</t>
+        </is>
+      </c>
+      <c r="C1762" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="D1762" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1762" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B1763" s="2" t="inlineStr">
+        <is>
+          <t>пандус для инвалидов размеры требования гост уклон</t>
+        </is>
+      </c>
+      <c r="C1763" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="D1763" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1763" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B1764" s="2" t="inlineStr">
+        <is>
+          <t>болты мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1764" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1764" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1764" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B1765" s="2" t="inlineStr">
+        <is>
+          <t>затяжка болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1765" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1765" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1765" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B1766" s="2" t="inlineStr">
+        <is>
+          <t>момент затяжки болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1766" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D1766" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1766" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B1767" s="2" t="inlineStr">
+        <is>
+          <t>болты крепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1767" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1767" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1767" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B1768" s="2" t="inlineStr">
+        <is>
+          <t>степень затяжки болтов крышки мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C1768" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1768" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1768" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B1769" s="2" t="inlineStr">
+        <is>
+          <t>комплект болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1769" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1769" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1769" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1533"/>
+  <autoFilter ref="A1:E1769"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1769</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$2032</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1769"/>
+  <dimension ref="A1:E2032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -44672,8 +44672,6583 @@
         </is>
       </c>
     </row>
+    <row r="1770">
+      <c r="A1770" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B1770" s="2" t="inlineStr">
+        <is>
+          <t>допустимая величина бокового сдвига редуктора на оси</t>
+        </is>
+      </c>
+      <c r="C1770" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="D1770" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1770" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B1771" s="2" t="inlineStr">
+        <is>
+          <t>пандус для инвалидов размеры требования гост уклон</t>
+        </is>
+      </c>
+      <c r="C1771" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="D1771" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1771" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B1772" s="2" t="inlineStr">
+        <is>
+          <t>болты мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1772" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1772" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1772" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B1773" s="2" t="inlineStr">
+        <is>
+          <t>затяжка болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1773" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1773" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1773" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B1774" s="2" t="inlineStr">
+        <is>
+          <t>момент затяжки болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1774" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D1774" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1774" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B1775" s="2" t="inlineStr">
+        <is>
+          <t>болты крепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1775" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1775" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1775" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B1776" s="2" t="inlineStr">
+        <is>
+          <t>степень затяжки болтов крышки мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C1776" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1776" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1776" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="2" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B1777" s="2" t="inlineStr">
+        <is>
+          <t>комплект болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1777" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1777" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1777" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1778" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная</t>
+        </is>
+      </c>
+      <c r="C1778" s="2" t="n">
+        <v>84882</v>
+      </c>
+      <c r="D1778" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1778" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1779" s="2" t="inlineStr">
+        <is>
+          <t>дорожная плита размеры</t>
+        </is>
+      </c>
+      <c r="C1779" s="2" t="n">
+        <v>6671</v>
+      </c>
+      <c r="D1779" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1779" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1780" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная цена</t>
+        </is>
+      </c>
+      <c r="C1780" s="2" t="n">
+        <v>5622</v>
+      </c>
+      <c r="D1780" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1780" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1781" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается электрическая плита от индукционной</t>
+        </is>
+      </c>
+      <c r="C1781" s="2" t="n">
+        <v>5046</v>
+      </c>
+      <c r="D1781" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1781" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1782" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 6</t>
+        </is>
+      </c>
+      <c r="C1782" s="2" t="n">
+        <v>3687</v>
+      </c>
+      <c r="D1782" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1782" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1783" s="2" t="inlineStr">
+        <is>
+          <t>индукционная плита что это простыми словами</t>
+        </is>
+      </c>
+      <c r="C1783" s="2" t="n">
+        <v>3585</v>
+      </c>
+      <c r="D1783" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1783" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1784" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 2</t>
+        </is>
+      </c>
+      <c r="C1784" s="2" t="n">
+        <v>3418</v>
+      </c>
+      <c r="D1784" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1784" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1785" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная пдн</t>
+        </is>
+      </c>
+      <c r="C1785" s="2" t="n">
+        <v>3366</v>
+      </c>
+      <c r="D1785" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1785" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1786" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная бу купить</t>
+        </is>
+      </c>
+      <c r="C1786" s="2" t="n">
+        <v>3339</v>
+      </c>
+      <c r="D1786" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1786" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1787" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 2п</t>
+        </is>
+      </c>
+      <c r="C1787" s="2" t="n">
+        <v>2927</v>
+      </c>
+      <c r="D1787" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1787" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1788" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 30.18</t>
+        </is>
+      </c>
+      <c r="C1788" s="2" t="n">
+        <v>2756</v>
+      </c>
+      <c r="D1788" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1788" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1789" s="2" t="inlineStr">
+        <is>
+          <t>плита бетонная дорожная</t>
+        </is>
+      </c>
+      <c r="C1789" s="2" t="n">
+        <v>2613</v>
+      </c>
+      <c r="D1789" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1789" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1790" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 3000х1750</t>
+        </is>
+      </c>
+      <c r="C1790" s="2" t="n">
+        <v>2553</v>
+      </c>
+      <c r="D1790" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1790" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1791" s="2" t="inlineStr">
+        <is>
+          <t>дорожная плита 18</t>
+        </is>
+      </c>
+      <c r="C1791" s="2" t="n">
+        <v>2545</v>
+      </c>
+      <c r="D1791" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1791" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1792" s="2" t="inlineStr">
+        <is>
+          <t>дорожная плита 6х2</t>
+        </is>
+      </c>
+      <c r="C1792" s="2" t="n">
+        <v>2407</v>
+      </c>
+      <c r="D1792" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1792" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1793" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 2п 30</t>
+        </is>
+      </c>
+      <c r="C1793" s="2" t="n">
+        <v>2347</v>
+      </c>
+      <c r="D1793" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1793" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1794" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 14</t>
+        </is>
+      </c>
+      <c r="C1794" s="2" t="n">
+        <v>2198</v>
+      </c>
+      <c r="D1794" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1794" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1795" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 6000х2000х140</t>
+        </is>
+      </c>
+      <c r="C1795" s="2" t="n">
+        <v>2087</v>
+      </c>
+      <c r="D1795" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1795" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1796" s="2" t="inlineStr">
+        <is>
+          <t>дорожная плита весит</t>
+        </is>
+      </c>
+      <c r="C1796" s="2" t="n">
+        <v>2039</v>
+      </c>
+      <c r="D1796" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1796" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1797" s="2" t="inlineStr">
+        <is>
+          <t>сколько весит дорожная плита</t>
+        </is>
+      </c>
+      <c r="C1797" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D1797" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1797" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1798" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 6 2</t>
+        </is>
+      </c>
+      <c r="C1798" s="2" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D1798" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1798" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1799" s="2" t="inlineStr">
+        <is>
+          <t>дорожная плита 3х 1.75</t>
+        </is>
+      </c>
+      <c r="C1799" s="2" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D1799" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1799" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1800" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 2п 30.18</t>
+        </is>
+      </c>
+      <c r="C1800" s="2" t="n">
+        <v>1764</v>
+      </c>
+      <c r="D1800" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1800" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1801" s="2" t="inlineStr">
+        <is>
+          <t>плита железобетонная дорожная</t>
+        </is>
+      </c>
+      <c r="C1801" s="2" t="n">
+        <v>1759</v>
+      </c>
+      <c r="D1801" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1801" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1802" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная пд</t>
+        </is>
+      </c>
+      <c r="C1802" s="2" t="n">
+        <v>1685</v>
+      </c>
+      <c r="D1802" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1802" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1803" s="2" t="inlineStr">
+        <is>
+          <t>какая плита лучше индукционная или электрическая</t>
+        </is>
+      </c>
+      <c r="C1803" s="2" t="n">
+        <v>1637</v>
+      </c>
+      <c r="D1803" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1803" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1804" s="2" t="inlineStr">
+        <is>
+          <t>дорожная плита 30 18</t>
+        </is>
+      </c>
+      <c r="C1804" s="2" t="n">
+        <v>1634</v>
+      </c>
+      <c r="D1804" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1804" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1805" s="2" t="inlineStr">
+        <is>
+          <t>дорожная плита авито</t>
+        </is>
+      </c>
+      <c r="C1805" s="2" t="n">
+        <v>1547</v>
+      </c>
+      <c r="D1805" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1805" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1806" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 2п 30.18 30</t>
+        </is>
+      </c>
+      <c r="C1806" s="2" t="n">
+        <v>1522</v>
+      </c>
+      <c r="D1806" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1806" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1807" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 3х 1.5</t>
+        </is>
+      </c>
+      <c r="C1807" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="D1807" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1807" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1808" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 1п 30</t>
+        </is>
+      </c>
+      <c r="C1808" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D1808" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1808" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1809" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная 10</t>
+        </is>
+      </c>
+      <c r="C1809" s="2" t="n">
+        <v>1073</v>
+      </c>
+      <c r="D1809" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1809" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1810" s="2" t="inlineStr">
+        <is>
+          <t>пага дорожная плита</t>
+        </is>
+      </c>
+      <c r="C1810" s="2" t="n">
+        <v>1067</v>
+      </c>
+      <c r="D1810" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1810" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1811" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная пдн 14</t>
+        </is>
+      </c>
+      <c r="C1811" s="2" t="n">
+        <v>1062</v>
+      </c>
+      <c r="D1811" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1811" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1812" s="2" t="inlineStr">
+        <is>
+          <t>плита дорожная пд 6</t>
+        </is>
+      </c>
+      <c r="C1812" s="2" t="n">
+        <v>914</v>
+      </c>
+      <c r="D1812" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1812" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1813" s="2" t="inlineStr">
+        <is>
+          <t>какая плита лучше индукционная или инфракрасная</t>
+        </is>
+      </c>
+      <c r="C1813" s="2" t="n">
+        <v>671</v>
+      </c>
+      <c r="D1813" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1813" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1814" s="2" t="inlineStr">
+        <is>
+          <t>индукционная плита или электрическая разница</t>
+        </is>
+      </c>
+      <c r="C1814" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="D1814" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1814" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1815" s="2" t="inlineStr">
+        <is>
+          <t>как понять индукционная плита или нет</t>
+        </is>
+      </c>
+      <c r="C1815" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="D1815" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1815" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1816" s="2" t="inlineStr">
+        <is>
+          <t>электроплита weissgauff как включить</t>
+        </is>
+      </c>
+      <c r="C1816" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="D1816" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1816" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1817" s="2" t="inlineStr">
+        <is>
+          <t>плита dq200</t>
+        </is>
+      </c>
+      <c r="C1817" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="D1817" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1817" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1818" s="2" t="inlineStr">
+        <is>
+          <t>плита стеклокерамика и индукционная чем отличаются</t>
+        </is>
+      </c>
+      <c r="C1818" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="D1818" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1818" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1819" s="2" t="inlineStr">
+        <is>
+          <t>плита мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1819" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="D1819" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1819" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1820" s="2" t="inlineStr">
+        <is>
+          <t>индукционная плита что это простыми словами фото</t>
+        </is>
+      </c>
+      <c r="C1820" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1820" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1820" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1821" s="2" t="inlineStr">
+        <is>
+          <t>усиленная плита dq200</t>
+        </is>
+      </c>
+      <c r="C1821" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1821" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1821" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1822" s="2" t="inlineStr">
+        <is>
+          <t>плита мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1822" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1822" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1822" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1823" s="2" t="inlineStr">
+        <is>
+          <t>усиленная плита мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1823" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1823" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1823" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1824" s="2" t="inlineStr">
+        <is>
+          <t>момент затяжки плиты dq200</t>
+        </is>
+      </c>
+      <c r="C1824" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1824" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1824" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1825" s="2" t="inlineStr">
+        <is>
+          <t>индукционная плита это простыми словами что значит</t>
+        </is>
+      </c>
+      <c r="C1825" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1825" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1825" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1826" s="2" t="inlineStr">
+        <is>
+          <t>dq200 замена плиты</t>
+        </is>
+      </c>
+      <c r="C1826" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1826" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1826" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1827" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 плита</t>
+        </is>
+      </c>
+      <c r="C1827" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1827" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1827" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1828" s="2" t="inlineStr">
+        <is>
+          <t>усиленная плита мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1828" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1828" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1828" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1829" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника</t>
+        </is>
+      </c>
+      <c r="C1829" s="2" t="n">
+        <v>72009</v>
+      </c>
+      <c r="D1829" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1829" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1830" s="2" t="inlineStr">
+        <is>
+          <t>робот человек</t>
+        </is>
+      </c>
+      <c r="C1830" s="2" t="n">
+        <v>62881</v>
+      </c>
+      <c r="D1830" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1830" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1831" s="2" t="inlineStr">
+        <is>
+          <t>роботы под прикрытием</t>
+        </is>
+      </c>
+      <c r="C1831" s="2" t="n">
+        <v>26120</v>
+      </c>
+      <c r="D1831" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1831" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1832" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник</t>
+        </is>
+      </c>
+      <c r="C1832" s="2" t="n">
+        <v>20359</v>
+      </c>
+      <c r="D1832" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1832" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1833" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1833" s="2" t="n">
+        <v>17816</v>
+      </c>
+      <c r="D1833" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1833" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1834" s="2" t="inlineStr">
+        <is>
+          <t>робот emo</t>
+        </is>
+      </c>
+      <c r="C1834" s="2" t="n">
+        <v>12708</v>
+      </c>
+      <c r="D1834" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1834" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1835" s="2" t="inlineStr">
+        <is>
+          <t>трансмиссия это</t>
+        </is>
+      </c>
+      <c r="C1835" s="2" t="n">
+        <v>9444</v>
+      </c>
+      <c r="D1835" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1835" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1836" s="2" t="inlineStr">
+        <is>
+          <t>распаковка роботов</t>
+        </is>
+      </c>
+      <c r="C1836" s="2" t="n">
+        <v>9100</v>
+      </c>
+      <c r="D1836" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1836" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1837" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1837" s="2" t="n">
+        <v>9020</v>
+      </c>
+      <c r="D1837" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1837" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1838" s="2" t="inlineStr">
+        <is>
+          <t>робот гуманоид</t>
+        </is>
+      </c>
+      <c r="C1838" s="2" t="n">
+        <v>8636</v>
+      </c>
+      <c r="D1838" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1838" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1839" s="2" t="inlineStr">
+        <is>
+          <t>боевой робот номер 4</t>
+        </is>
+      </c>
+      <c r="C1839" s="2" t="n">
+        <v>7999</v>
+      </c>
+      <c r="D1839" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1839" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1840" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C1840" s="2" t="n">
+        <v>6423</v>
+      </c>
+      <c r="D1840" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1840" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1841" s="2" t="inlineStr">
+        <is>
+          <t>дитя робота</t>
+        </is>
+      </c>
+      <c r="C1841" s="2" t="n">
+        <v>6171</v>
+      </c>
+      <c r="D1841" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1841" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1842" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника</t>
+        </is>
+      </c>
+      <c r="C1842" s="2" t="n">
+        <v>4794</v>
+      </c>
+      <c r="D1842" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1842" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1843" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C1843" s="2" t="n">
+        <v>4353</v>
+      </c>
+      <c r="D1843" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1843" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1844" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается робот от автомата</t>
+        </is>
+      </c>
+      <c r="C1844" s="2" t="n">
+        <v>4114</v>
+      </c>
+      <c r="D1844" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1844" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1845" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается автомат от робота</t>
+        </is>
+      </c>
+      <c r="C1845" s="2" t="n">
+        <v>4114</v>
+      </c>
+      <c r="D1845" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1845" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1846" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника дсг</t>
+        </is>
+      </c>
+      <c r="C1846" s="2" t="n">
+        <v>3968</v>
+      </c>
+      <c r="D1846" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1846" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1847" s="2" t="inlineStr">
+        <is>
+          <t>коробка робот что это</t>
+        </is>
+      </c>
+      <c r="C1847" s="2" t="n">
+        <v>3652</v>
+      </c>
+      <c r="D1847" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1847" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1848" s="2" t="inlineStr">
+        <is>
+          <t>замена мехатроника</t>
+        </is>
+      </c>
+      <c r="C1848" s="2" t="n">
+        <v>3480</v>
+      </c>
+      <c r="D1848" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1848" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1849" s="2" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1849" s="2" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1849" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1849" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1850" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это</t>
+        </is>
+      </c>
+      <c r="C1850" s="2" t="n">
+        <v>3357</v>
+      </c>
+      <c r="D1850" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1850" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1851" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника купить</t>
+        </is>
+      </c>
+      <c r="C1851" s="2" t="n">
+        <v>3099</v>
+      </c>
+      <c r="D1851" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1851" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1852" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники</t>
+        </is>
+      </c>
+      <c r="C1852" s="2" t="n">
+        <v>3049</v>
+      </c>
+      <c r="D1852" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1852" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1853" s="2" t="inlineStr">
+        <is>
+          <t>что такое трансмиссия</t>
+        </is>
+      </c>
+      <c r="C1853" s="2" t="n">
+        <v>2930</v>
+      </c>
+      <c r="D1853" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1853" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1854" s="2" t="inlineStr">
+        <is>
+          <t>сервопривод это</t>
+        </is>
+      </c>
+      <c r="C1854" s="2" t="n">
+        <v>2891</v>
+      </c>
+      <c r="D1854" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1854" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1855" s="2" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 мехатроника</t>
+        </is>
+      </c>
+      <c r="C1855" s="2" t="n">
+        <v>2666</v>
+      </c>
+      <c r="D1855" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1855" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1856" s="2" t="inlineStr">
+        <is>
+          <t>робот козел</t>
+        </is>
+      </c>
+      <c r="C1856" s="2" t="n">
+        <v>2531</v>
+      </c>
+      <c r="D1856" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1856" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1857" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что</t>
+        </is>
+      </c>
+      <c r="C1857" s="2" t="n">
+        <v>2428</v>
+      </c>
+      <c r="D1857" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1857" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1858" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg</t>
+        </is>
+      </c>
+      <c r="C1858" s="2" t="n">
+        <v>2262</v>
+      </c>
+      <c r="D1858" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1858" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1859" s="2" t="inlineStr">
+        <is>
+          <t>ремонт мехатроника</t>
+        </is>
+      </c>
+      <c r="C1859" s="2" t="n">
+        <v>2172</v>
+      </c>
+      <c r="D1859" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1859" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1860" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника дсг 7</t>
+        </is>
+      </c>
+      <c r="C1860" s="2" t="n">
+        <v>2134</v>
+      </c>
+      <c r="D1860" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1860" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1861" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг</t>
+        </is>
+      </c>
+      <c r="C1861" s="2" t="n">
+        <v>2037</v>
+      </c>
+      <c r="D1861" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1861" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1862" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1862" s="2" t="n">
+        <v>1937</v>
+      </c>
+      <c r="D1862" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1862" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1863" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1863" s="2" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D1863" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1863" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1864" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1864" s="2" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D1864" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1864" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1865" s="2" t="inlineStr">
+        <is>
+          <t>роботех</t>
+        </is>
+      </c>
+      <c r="C1865" s="2" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D1865" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1865" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1866" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника кем работать</t>
+        </is>
+      </c>
+      <c r="C1866" s="2" t="n">
+        <v>1805</v>
+      </c>
+      <c r="D1866" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1866" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1867" s="2" t="inlineStr">
+        <is>
+          <t>коробка передач робот что это</t>
+        </is>
+      </c>
+      <c r="C1867" s="2" t="n">
+        <v>1781</v>
+      </c>
+      <c r="D1867" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1867" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1868" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать</t>
+        </is>
+      </c>
+      <c r="C1868" s="2" t="n">
+        <v>1716</v>
+      </c>
+      <c r="D1868" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1868" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1869" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1869" s="2" t="n">
+        <v>1632</v>
+      </c>
+      <c r="D1869" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1869" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1870" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника что за профессия</t>
+        </is>
+      </c>
+      <c r="C1870" s="2" t="n">
+        <v>1626</v>
+      </c>
+      <c r="D1870" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1870" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1871" s="2" t="inlineStr">
+        <is>
+          <t>робот федор</t>
+        </is>
+      </c>
+      <c r="C1871" s="2" t="n">
+        <v>1602</v>
+      </c>
+      <c r="D1871" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1871" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1872" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что за профессия</t>
+        </is>
+      </c>
+      <c r="C1872" s="2" t="n">
+        <v>1557</v>
+      </c>
+      <c r="D1872" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1872" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1873" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7</t>
+        </is>
+      </c>
+      <c r="C1873" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="D1873" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1873" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1874" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1874" s="2" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D1874" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1874" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1875" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dq250</t>
+        </is>
+      </c>
+      <c r="C1875" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="D1875" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1875" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1876" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника ауди</t>
+        </is>
+      </c>
+      <c r="C1876" s="2" t="n">
+        <v>1312</v>
+      </c>
+      <c r="D1876" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1876" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1877" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается коробка автомат от робота</t>
+        </is>
+      </c>
+      <c r="C1877" s="2" t="n">
+        <v>1288</v>
+      </c>
+      <c r="D1877" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1877" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1878" s="2" t="inlineStr">
+        <is>
+          <t>вкалывают роботы а не человек</t>
+        </is>
+      </c>
+      <c r="C1878" s="2" t="n">
+        <v>1251</v>
+      </c>
+      <c r="D1878" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1878" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1879" s="2" t="inlineStr">
+        <is>
+          <t>масло мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C1879" s="2" t="n">
+        <v>1247</v>
+      </c>
+      <c r="D1879" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1879" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1880" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C1880" s="2" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D1880" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1880" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1881" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается вариатор от робота</t>
+        </is>
+      </c>
+      <c r="C1881" s="2" t="n">
+        <v>1197</v>
+      </c>
+      <c r="D1881" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1881" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1882" s="2" t="inlineStr">
+        <is>
+          <t>снятие мехатроника</t>
+        </is>
+      </c>
+      <c r="C1882" s="2" t="n">
+        <v>1188</v>
+      </c>
+      <c r="D1882" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1882" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1883" s="2" t="inlineStr">
+        <is>
+          <t>цена мехатроника</t>
+        </is>
+      </c>
+      <c r="C1883" s="2" t="n">
+        <v>1177</v>
+      </c>
+      <c r="D1883" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1883" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1884" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это</t>
+        </is>
+      </c>
+      <c r="C1884" s="2" t="n">
+        <v>1147</v>
+      </c>
+      <c r="D1884" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1884" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1885" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7</t>
+        </is>
+      </c>
+      <c r="C1885" s="2" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D1885" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1885" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1886" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник шкода</t>
+        </is>
+      </c>
+      <c r="C1886" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="D1886" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1886" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1887" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1887" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1887" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1887" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1888" s="2" t="inlineStr">
+        <is>
+          <t>замена масла в мехатронике</t>
+        </is>
+      </c>
+      <c r="C1888" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D1888" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1888" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1889" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника фольксваген</t>
+        </is>
+      </c>
+      <c r="C1889" s="2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D1889" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1889" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1890" s="2" t="inlineStr">
+        <is>
+          <t>ремкомплект мехатроника</t>
+        </is>
+      </c>
+      <c r="C1890" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="D1890" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1890" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1891" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника шкода октавия</t>
+        </is>
+      </c>
+      <c r="C1891" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="D1891" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1891" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1892" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника факультеты</t>
+        </is>
+      </c>
+      <c r="C1892" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="D1892" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1892" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1893" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника акпп</t>
+        </is>
+      </c>
+      <c r="C1893" s="2" t="n">
+        <v>924</v>
+      </c>
+      <c r="D1893" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1893" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1894" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1894" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1894" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1894" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1895" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой</t>
+        </is>
+      </c>
+      <c r="C1895" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="D1895" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1895" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1896" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника обучение</t>
+        </is>
+      </c>
+      <c r="C1896" s="2" t="n">
+        <v>882</v>
+      </c>
+      <c r="D1896" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1896" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1897" s="2" t="inlineStr">
+        <is>
+          <t>масло мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C1897" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="D1897" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1897" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1898" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1898" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1898" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1898" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1899" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника направления</t>
+        </is>
+      </c>
+      <c r="C1899" s="2" t="n">
+        <v>862</v>
+      </c>
+      <c r="D1899" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1899" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1900" s="2" t="inlineStr">
+        <is>
+          <t>замена мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1900" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="D1900" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1900" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1901" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C1901" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="D1901" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1901" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1902" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии</t>
+        </is>
+      </c>
+      <c r="C1902" s="2" t="n">
+        <v>818</v>
+      </c>
+      <c r="D1902" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1902" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1903" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C1903" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="D1903" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1903" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1904" s="2" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1904" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1904" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1904" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1905" s="2" t="inlineStr">
+        <is>
+          <t>факультет мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1905" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="D1905" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1905" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1906" s="2" t="inlineStr">
+        <is>
+          <t>r2d2 робот</t>
+        </is>
+      </c>
+      <c r="C1906" s="2" t="n">
+        <v>691</v>
+      </c>
+      <c r="D1906" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1906" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1907" s="2" t="inlineStr">
+        <is>
+          <t>направление мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1907" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="D1907" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1907" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1908" s="2" t="inlineStr">
+        <is>
+          <t>обучение мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1908" s="2" t="n">
+        <v>678</v>
+      </c>
+      <c r="D1908" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1908" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1909" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника вузы</t>
+        </is>
+      </c>
+      <c r="C1909" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="D1909" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1909" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1910" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии светлый</t>
+        </is>
+      </c>
+      <c r="C1910" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="D1910" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1910" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1911" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C1911" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="D1911" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1911" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1912" s="2" t="inlineStr">
+        <is>
+          <t>профессия мехатроника и робототехника кем работать</t>
+        </is>
+      </c>
+      <c r="C1912" s="2" t="n">
+        <v>548</v>
+      </c>
+      <c r="D1912" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1912" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1913" s="2" t="inlineStr">
+        <is>
+          <t>15.03 06 мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1913" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="D1913" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1913" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1914" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми</t>
+        </is>
+      </c>
+      <c r="C1914" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="D1914" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1914" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1915" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника баллы</t>
+        </is>
+      </c>
+      <c r="C1915" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="D1915" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1915" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1916" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми словами</t>
+        </is>
+      </c>
+      <c r="C1916" s="2" t="n">
+        <v>457</v>
+      </c>
+      <c r="D1916" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1916" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1917" s="2" t="inlineStr">
+        <is>
+          <t>институт мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1917" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="D1917" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1917" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1918" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1918" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1918" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1918" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1919" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1919" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1919" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1919" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1920" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника</t>
+        </is>
+      </c>
+      <c r="C1920" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="D1920" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1920" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1921" s="2" t="inlineStr">
+        <is>
+          <t>кем работают после мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1921" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="D1921" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1921" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1922" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1922" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1922" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1922" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1923" s="2" t="inlineStr">
+        <is>
+          <t>что такое мехатроник</t>
+        </is>
+      </c>
+      <c r="C1923" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="D1923" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1923" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1924" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника университеты</t>
+        </is>
+      </c>
+      <c r="C1924" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="D1924" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1924" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1925" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника поступить</t>
+        </is>
+      </c>
+      <c r="C1925" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="D1925" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1925" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1926" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника зарплата</t>
+        </is>
+      </c>
+      <c r="C1926" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="D1926" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1926" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1927" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника учиться</t>
+        </is>
+      </c>
+      <c r="C1927" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="D1927" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1927" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1928" s="2" t="inlineStr">
+        <is>
+          <t>программа мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1928" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="D1928" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1928" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1929" s="2" t="inlineStr">
+        <is>
+          <t>15.02 10 мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1929" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="D1929" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1929" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1930" s="2" t="inlineStr">
+        <is>
+          <t>специалист по мехатронике и робототехнике</t>
+        </is>
+      </c>
+      <c r="C1930" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="D1930" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1930" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1931" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника колледжи</t>
+        </is>
+      </c>
+      <c r="C1931" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="D1931" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1931" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1932" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника предметы</t>
+        </is>
+      </c>
+      <c r="C1932" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="D1932" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1932" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1933" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника проходные баллы</t>
+        </is>
+      </c>
+      <c r="C1933" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="D1933" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1933" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1934" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника отзывы</t>
+        </is>
+      </c>
+      <c r="C1934" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="D1934" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1934" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1935" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какая специальность</t>
+        </is>
+      </c>
+      <c r="C1935" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="D1935" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1935" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1936" s="2" t="inlineStr">
+        <is>
+          <t>курс мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1936" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="D1936" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1936" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1937" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что это</t>
+        </is>
+      </c>
+      <c r="C1937" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="D1937" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1937" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1938" s="2" t="inlineStr">
+        <is>
+          <t>магистратура робототехника и мехатроника</t>
+        </is>
+      </c>
+      <c r="C1938" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="D1938" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1938" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1939" s="2" t="inlineStr">
+        <is>
+          <t>политех мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1939" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="D1939" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1939" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1940" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника код</t>
+        </is>
+      </c>
+      <c r="C1940" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="D1940" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1940" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1941" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника учебный план</t>
+        </is>
+      </c>
+      <c r="C1941" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D1941" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1941" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1942" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника в машине это</t>
+        </is>
+      </c>
+      <c r="C1942" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D1942" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1942" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1943" s="2" t="inlineStr">
+        <is>
+          <t>15.02 10 мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C1943" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="D1943" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1943" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1944" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника мгту</t>
+        </is>
+      </c>
+      <c r="C1944" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="D1944" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1944" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1945" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника урфу</t>
+        </is>
+      </c>
+      <c r="C1945" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="D1945" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1945" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1946" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1946" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1946" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1946" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1947" s="2" t="inlineStr">
+        <is>
+          <t>кафедры мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C1947" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D1947" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1947" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1948" s="2" t="inlineStr">
+        <is>
+          <t>мэи робототехника и мехатроника</t>
+        </is>
+      </c>
+      <c r="C1948" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D1948" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1948" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1949" s="2" t="inlineStr">
+        <is>
+          <t>баумана мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1949" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="D1949" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1949" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1950" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1950" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1950" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1950" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1951" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какой факультет</t>
+        </is>
+      </c>
+      <c r="C1951" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="D1951" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1951" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1952" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1952" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1952" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1952" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1953" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1953" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1953" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1953" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1954" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в машине это</t>
+        </is>
+      </c>
+      <c r="C1954" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D1954" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1954" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1955" s="2" t="inlineStr">
+        <is>
+          <t>итмо мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1955" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="D1955" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1955" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1956" s="2" t="inlineStr">
+        <is>
+          <t>москва мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1956" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="D1956" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1956" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1957" s="2" t="inlineStr">
+        <is>
+          <t>спо мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C1957" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D1957" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1957" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1958" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника колледж кем работать</t>
+        </is>
+      </c>
+      <c r="C1958" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D1958" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1958" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1959" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника работа</t>
+        </is>
+      </c>
+      <c r="C1959" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="D1959" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1959" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1960" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника юургу</t>
+        </is>
+      </c>
+      <c r="C1960" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="D1960" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1960" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1961" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника спб</t>
+        </is>
+      </c>
+      <c r="C1961" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="D1961" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1961" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1962" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника профессия это</t>
+        </is>
+      </c>
+      <c r="C1962" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="D1962" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1962" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1963" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какие предметы</t>
+        </is>
+      </c>
+      <c r="C1963" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="D1963" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1963" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1964" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после колледжа</t>
+        </is>
+      </c>
+      <c r="C1964" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="D1964" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1964" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1965" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника робототехника и машиностроение</t>
+        </is>
+      </c>
+      <c r="C1965" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="D1965" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1965" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1966" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это коробка</t>
+        </is>
+      </c>
+      <c r="C1966" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="D1966" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1966" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1967" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1967" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1967" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1967" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1968" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в коробке передач это</t>
+        </is>
+      </c>
+      <c r="C1968" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="D1968" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1968" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1969" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после вуза</t>
+        </is>
+      </c>
+      <c r="C1969" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="D1969" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1969" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1970" s="2" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1970" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1970" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1970" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1971" s="2" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1971" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1971" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1971" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1972" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1972" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1972" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1972" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1973" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника по отраслям что это</t>
+        </is>
+      </c>
+      <c r="C1973" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D1973" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1973" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1974" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что это за профессия</t>
+        </is>
+      </c>
+      <c r="C1974" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D1974" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1974" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1975" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1975" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1975" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1975" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1976" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что за профессия зарплата</t>
+        </is>
+      </c>
+      <c r="C1976" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="D1976" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1976" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1977" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1977" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1977" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1977" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1978" s="2" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1978" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1978" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1978" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1979" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1979" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1979" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1979" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1980" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1980" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1980" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1980" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1981" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1981" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1981" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1981" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1982" s="2" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1982" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1982" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1982" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1983" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1983" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1983" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1983" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1984" s="2" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1984" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1984" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1984" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1985" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1985" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1985" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1985" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1986" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника в автомобиле это</t>
+        </is>
+      </c>
+      <c r="C1986" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D1986" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1986" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1987" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1987" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1987" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1987" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1988" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1988" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1988" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1988" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1989" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1989" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1989" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1989" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1990" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроника это</t>
+        </is>
+      </c>
+      <c r="C1990" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1990" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1990" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1991" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1991" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1991" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1991" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1992" s="2" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1992" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1992" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1992" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1993" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1993" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1993" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1993" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1994" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1994" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1994" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1994" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1995" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник что это такое в автомобиле</t>
+        </is>
+      </c>
+      <c r="C1995" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1995" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1995" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1996" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроник это</t>
+        </is>
+      </c>
+      <c r="C1996" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1996" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1996" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1997" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника что это за специальность</t>
+        </is>
+      </c>
+      <c r="C1997" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="D1997" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1997" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1998" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника это</t>
+        </is>
+      </c>
+      <c r="C1998" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D1998" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1998" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B1999" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это профессия</t>
+        </is>
+      </c>
+      <c r="C1999" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D1999" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1999" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2000" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C2000" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D2000" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2000" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2001" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C2001" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D2001" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2001" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2002" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника что за профессия</t>
+        </is>
+      </c>
+      <c r="C2002" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D2002" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2002" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2003" s="2" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C2003" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D2003" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2003" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2004" s="2" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2004" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D2004" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2004" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2005" s="2" t="inlineStr">
+        <is>
+          <t>техник мехатроника это</t>
+        </is>
+      </c>
+      <c r="C2005" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D2005" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2005" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2006" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C2006" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2006" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2006" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2007" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C2007" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2007" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2007" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2008" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника акпп это</t>
+        </is>
+      </c>
+      <c r="C2008" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2008" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2008" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2009" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C2009" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2009" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2009" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2010" s="2" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2010" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2010" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2010" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2011" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C2011" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2011" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2011" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2012" s="2" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2012" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2012" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2012" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2013" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C2013" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2013" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2013" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2014" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C2014" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2014" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2014" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2015" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C2015" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2015" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2015" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2016" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C2016" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2016" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2016" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2017" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg это</t>
+        </is>
+      </c>
+      <c r="C2017" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D2017" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2017" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2018" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C2018" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2018" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2018" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2019" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми словами в машине</t>
+        </is>
+      </c>
+      <c r="C2019" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2019" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2019" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2020" s="2" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2020" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2020" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2020" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2021" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника что это</t>
+        </is>
+      </c>
+      <c r="C2021" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2021" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2021" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2022" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2022" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2022" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2022" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2023" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в акпп что это</t>
+        </is>
+      </c>
+      <c r="C2023" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2023" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2023" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2024" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в дсг это</t>
+        </is>
+      </c>
+      <c r="C2024" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2024" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2024" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2025" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в авто это</t>
+        </is>
+      </c>
+      <c r="C2025" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2025" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2025" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2026" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это простыми словами</t>
+        </is>
+      </c>
+      <c r="C2026" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2026" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2026" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2027" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроник это кто и чем занимается</t>
+        </is>
+      </c>
+      <c r="C2027" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2027" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2027" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2028" s="2" t="inlineStr">
+        <is>
+          <t>техник мехатроник это</t>
+        </is>
+      </c>
+      <c r="C2028" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2028" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2028" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2029" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии город светлый</t>
+        </is>
+      </c>
+      <c r="C2029" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2029" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2029" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2030" s="2" t="inlineStr">
+        <is>
+          <t>специалист по мехатронике и робототехнике это</t>
+        </is>
+      </c>
+      <c r="C2030" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2030" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2030" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2031" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 это</t>
+        </is>
+      </c>
+      <c r="C2031" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2031" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2031" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B2032" s="2" t="inlineStr">
+        <is>
+          <t>компьютерная мехатроника это</t>
+        </is>
+      </c>
+      <c r="C2032" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2032" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2032" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1769"/>
+  <autoFilter ref="A1:E2032"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$3079</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$3350</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3079"/>
+  <dimension ref="A1:E3350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -77422,8 +77422,6783 @@
         </is>
       </c>
     </row>
+    <row r="3080">
+      <c r="A3080" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3080" s="2" t="inlineStr">
+        <is>
+          <t>коробка отбора мощности</t>
+        </is>
+      </c>
+      <c r="C3080" s="2" t="n">
+        <v>18114</v>
+      </c>
+      <c r="D3080" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3080" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3081">
+      <c r="A3081" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3081" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации это</t>
+        </is>
+      </c>
+      <c r="C3081" s="2" t="n">
+        <v>11528</v>
+      </c>
+      <c r="D3081" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3081" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3082">
+      <c r="A3082" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3082" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации что это</t>
+        </is>
+      </c>
+      <c r="C3082" s="2" t="n">
+        <v>10676</v>
+      </c>
+      <c r="D3082" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3082" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3083">
+      <c r="A3083" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3083" s="2" t="inlineStr">
+        <is>
+          <t>что такое скорость клубочковой фильтрации</t>
+        </is>
+      </c>
+      <c r="C3083" s="2" t="n">
+        <v>3999</v>
+      </c>
+      <c r="D3083" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3083" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3084">
+      <c r="A3084" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3084" s="2" t="inlineStr">
+        <is>
+          <t>фильтр грубой очистки 1 2</t>
+        </is>
+      </c>
+      <c r="C3084" s="2" t="n">
+        <v>2957</v>
+      </c>
+      <c r="D3084" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3084" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3085">
+      <c r="A3085" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3085" s="2" t="inlineStr">
+        <is>
+          <t>определение скорости клубочковой фильтрации что это</t>
+        </is>
+      </c>
+      <c r="C3085" s="2" t="n">
+        <v>2828</v>
+      </c>
+      <c r="D3085" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3085" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3086">
+      <c r="A3086" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3086" s="2" t="inlineStr">
+        <is>
+          <t>определение скорости клубочковой фильтрации скф что это</t>
+        </is>
+      </c>
+      <c r="C3086" s="2" t="n">
+        <v>2344</v>
+      </c>
+      <c r="D3086" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3086" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3087">
+      <c r="A3087" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3087" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации анализ крови что это</t>
+        </is>
+      </c>
+      <c r="C3087" s="2" t="n">
+        <v>2243</v>
+      </c>
+      <c r="D3087" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3087" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3088" s="2" t="inlineStr">
+        <is>
+          <t>трансмиссионное масло api gl 4</t>
+        </is>
+      </c>
+      <c r="C3088" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D3088" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3088" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3089" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации у женщин что это</t>
+        </is>
+      </c>
+      <c r="C3089" s="2" t="n">
+        <v>1714</v>
+      </c>
+      <c r="D3089" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3089" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3090" s="2" t="inlineStr">
+        <is>
+          <t>скф скорость клубочковой фильтрации что это такое</t>
+        </is>
+      </c>
+      <c r="C3090" s="2" t="n">
+        <v>1505</v>
+      </c>
+      <c r="D3090" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3090" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3091" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается сетевой фильтр от удлинителя</t>
+        </is>
+      </c>
+      <c r="C3091" s="2" t="n">
+        <v>1129</v>
+      </c>
+      <c r="D3091" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3091" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3092" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации понижена</t>
+        </is>
+      </c>
+      <c r="C3092" s="2" t="n">
+        <v>1094</v>
+      </c>
+      <c r="D3092" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3092" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3093" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации что это значит</t>
+        </is>
+      </c>
+      <c r="C3093" s="2" t="n">
+        <v>922</v>
+      </c>
+      <c r="D3093" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3093" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3094" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации незначительно снижена</t>
+        </is>
+      </c>
+      <c r="C3094" s="2" t="n">
+        <v>548</v>
+      </c>
+      <c r="D3094" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3094" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3095" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации что это за анализ</t>
+        </is>
+      </c>
+      <c r="C3095" s="2" t="n">
+        <v>493</v>
+      </c>
+      <c r="D3095" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3095" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3096" s="2" t="inlineStr">
+        <is>
+          <t>универсальный калькулятор скорости клубочковой фильтрации</t>
+        </is>
+      </c>
+      <c r="C3096" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="D3096" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3096" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3097" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации у мужчин что это</t>
+        </is>
+      </c>
+      <c r="C3097" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="D3097" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3097" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3098" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации что это норма</t>
+        </is>
+      </c>
+      <c r="C3098" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="D3098" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3098" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3099" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации снижена что это</t>
+        </is>
+      </c>
+      <c r="C3099" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="D3099" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3099" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3100" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации понижена у женщин причины</t>
+        </is>
+      </c>
+      <c r="C3100" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="D3100" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3101" s="2" t="inlineStr">
+        <is>
+          <t>коробка беглова для новорожденных 2026 состав</t>
+        </is>
+      </c>
+      <c r="C3101" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="D3101" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3102" s="2" t="inlineStr">
+        <is>
+          <t>повышенная скорость клубочковой фильтрации что это</t>
+        </is>
+      </c>
+      <c r="C3102" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="D3102" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3103" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации повышена что это</t>
+        </is>
+      </c>
+      <c r="C3103" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="D3103" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3104" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации снижена что это значит</t>
+        </is>
+      </c>
+      <c r="C3104" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="D3104" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3105" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации незначительно снижена что это</t>
+        </is>
+      </c>
+      <c r="C3105" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="D3105" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3106" s="2" t="inlineStr">
+        <is>
+          <t>комплект прокладок гидроблока кпп zf 4wg 210</t>
+        </is>
+      </c>
+      <c r="C3106" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="D3106" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3107" s="2" t="inlineStr">
+        <is>
+          <t>высокая скорость клубочковой фильтрации что это</t>
+        </is>
+      </c>
+      <c r="C3107" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3107" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3108" s="2" t="inlineStr">
+        <is>
+          <t>замена масла кпп веста нг</t>
+        </is>
+      </c>
+      <c r="C3108" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3108" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3109" s="2" t="inlineStr">
+        <is>
+          <t>валы и шестерни кпп ямз 238вм</t>
+        </is>
+      </c>
+      <c r="C3109" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3109" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3110" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации повышена что это значит</t>
+        </is>
+      </c>
+      <c r="C3110" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="D3110" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3111" s="2" t="inlineStr">
+        <is>
+          <t>низкая скорость клубочковой фильтрации что это</t>
+        </is>
+      </c>
+      <c r="C3111" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3111" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3112" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации понижена это</t>
+        </is>
+      </c>
+      <c r="C3112" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="D3112" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3113" s="2" t="inlineStr">
+        <is>
+          <t>кровь на скорость клубочковой фильтрации что это</t>
+        </is>
+      </c>
+      <c r="C3113" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D3113" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3114" s="2" t="inlineStr">
+        <is>
+          <t>замена вала кпп на 175 моторе</t>
+        </is>
+      </c>
+      <c r="C3114" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3114" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3115" s="2" t="inlineStr">
+        <is>
+          <t>пониженная скорость клубочковой фильтрации что это</t>
+        </is>
+      </c>
+      <c r="C3115" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3115" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3116">
+      <c r="A3116" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3116" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации что это понижена</t>
+        </is>
+      </c>
+      <c r="C3116" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3116" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3117">
+      <c r="A3117" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3117" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации выше нормы что это</t>
+        </is>
+      </c>
+      <c r="C3117" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3117" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3118">
+      <c r="A3118" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3118" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации по креатинину что это</t>
+        </is>
+      </c>
+      <c r="C3118" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3118" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3119">
+      <c r="A3119" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3119" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации умеренно снижена что это</t>
+        </is>
+      </c>
+      <c r="C3119" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3119" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3119" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3120">
+      <c r="A3120" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3120" s="2" t="inlineStr">
+        <is>
+          <t>низкая скорость клубочковой фильтрации что это значит</t>
+        </is>
+      </c>
+      <c r="C3120" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3120" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3121">
+      <c r="A3121" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3121" s="2" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C3121" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D3121" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3121" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3122">
+      <c r="A3122" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3122" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации понижена что это значит</t>
+        </is>
+      </c>
+      <c r="C3122" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3122" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3123">
+      <c r="A3123" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3123" s="2" t="inlineStr">
+        <is>
+          <t>расчет скорости клубочковой фильтрации что это</t>
+        </is>
+      </c>
+      <c r="C3123" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3123" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3124">
+      <c r="A3124" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3124" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации калькулятор что это</t>
+        </is>
+      </c>
+      <c r="C3124" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3124" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3125">
+      <c r="A3125" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3125" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации 59 что это значит</t>
+        </is>
+      </c>
+      <c r="C3125" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3125" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3126">
+      <c r="A3126" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3126" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации это какой анализ</t>
+        </is>
+      </c>
+      <c r="C3126" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3126" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3127" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации 44 что это значит</t>
+        </is>
+      </c>
+      <c r="C3127" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3127" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3128">
+      <c r="A3128" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3128" s="2" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра шкода кодиак коробка dq500</t>
+        </is>
+      </c>
+      <c r="C3128" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3128" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3129" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации 46 что это</t>
+        </is>
+      </c>
+      <c r="C3129" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3129" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3130" s="2" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации 102 что это</t>
+        </is>
+      </c>
+      <c r="C3130" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3130" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" s="2" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B3131" s="2" t="inlineStr">
+        <is>
+          <t>коробка беглова для новорожденных 2026 состав стоимость</t>
+        </is>
+      </c>
+      <c r="C3131" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3131" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3132" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника</t>
+        </is>
+      </c>
+      <c r="C3132" s="2" t="n">
+        <v>72009</v>
+      </c>
+      <c r="D3132" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3133" s="2" t="inlineStr">
+        <is>
+          <t>робот человек</t>
+        </is>
+      </c>
+      <c r="C3133" s="2" t="n">
+        <v>62881</v>
+      </c>
+      <c r="D3133" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3134">
+      <c r="A3134" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3134" s="2" t="inlineStr">
+        <is>
+          <t>роботы под прикрытием</t>
+        </is>
+      </c>
+      <c r="C3134" s="2" t="n">
+        <v>26120</v>
+      </c>
+      <c r="D3134" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3135">
+      <c r="A3135" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3135" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник</t>
+        </is>
+      </c>
+      <c r="C3135" s="2" t="n">
+        <v>20359</v>
+      </c>
+      <c r="D3135" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3136">
+      <c r="A3136" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3136" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3136" s="2" t="n">
+        <v>17816</v>
+      </c>
+      <c r="D3136" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3137">
+      <c r="A3137" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3137" s="2" t="inlineStr">
+        <is>
+          <t>робот emo</t>
+        </is>
+      </c>
+      <c r="C3137" s="2" t="n">
+        <v>12708</v>
+      </c>
+      <c r="D3137" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3138">
+      <c r="A3138" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3138" s="2" t="inlineStr">
+        <is>
+          <t>трансмиссия это</t>
+        </is>
+      </c>
+      <c r="C3138" s="2" t="n">
+        <v>9444</v>
+      </c>
+      <c r="D3138" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3139">
+      <c r="A3139" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3139" s="2" t="inlineStr">
+        <is>
+          <t>распаковка роботов</t>
+        </is>
+      </c>
+      <c r="C3139" s="2" t="n">
+        <v>9100</v>
+      </c>
+      <c r="D3139" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3140">
+      <c r="A3140" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3140" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C3140" s="2" t="n">
+        <v>9020</v>
+      </c>
+      <c r="D3140" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3141">
+      <c r="A3141" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3141" s="2" t="inlineStr">
+        <is>
+          <t>робот гуманоид</t>
+        </is>
+      </c>
+      <c r="C3141" s="2" t="n">
+        <v>8636</v>
+      </c>
+      <c r="D3141" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3142">
+      <c r="A3142" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3142" s="2" t="inlineStr">
+        <is>
+          <t>боевой робот номер 4</t>
+        </is>
+      </c>
+      <c r="C3142" s="2" t="n">
+        <v>7999</v>
+      </c>
+      <c r="D3142" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3143">
+      <c r="A3143" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3143" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C3143" s="2" t="n">
+        <v>6423</v>
+      </c>
+      <c r="D3143" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3144">
+      <c r="A3144" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3144" s="2" t="inlineStr">
+        <is>
+          <t>дитя робота</t>
+        </is>
+      </c>
+      <c r="C3144" s="2" t="n">
+        <v>6171</v>
+      </c>
+      <c r="D3144" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3145">
+      <c r="A3145" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3145" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника</t>
+        </is>
+      </c>
+      <c r="C3145" s="2" t="n">
+        <v>4794</v>
+      </c>
+      <c r="D3145" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3146">
+      <c r="A3146" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3146" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C3146" s="2" t="n">
+        <v>4353</v>
+      </c>
+      <c r="D3146" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3147">
+      <c r="A3147" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3147" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается робот от автомата</t>
+        </is>
+      </c>
+      <c r="C3147" s="2" t="n">
+        <v>4114</v>
+      </c>
+      <c r="D3147" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3148">
+      <c r="A3148" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3148" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается автомат от робота</t>
+        </is>
+      </c>
+      <c r="C3148" s="2" t="n">
+        <v>4114</v>
+      </c>
+      <c r="D3148" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3149">
+      <c r="A3149" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3149" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника дсг</t>
+        </is>
+      </c>
+      <c r="C3149" s="2" t="n">
+        <v>3968</v>
+      </c>
+      <c r="D3149" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3150">
+      <c r="A3150" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3150" s="2" t="inlineStr">
+        <is>
+          <t>коробка робот что это</t>
+        </is>
+      </c>
+      <c r="C3150" s="2" t="n">
+        <v>3652</v>
+      </c>
+      <c r="D3150" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3151">
+      <c r="A3151" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3151" s="2" t="inlineStr">
+        <is>
+          <t>замена мехатроника</t>
+        </is>
+      </c>
+      <c r="C3151" s="2" t="n">
+        <v>3480</v>
+      </c>
+      <c r="D3151" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3152">
+      <c r="A3152" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3152" s="2" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C3152" s="2" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D3152" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3153">
+      <c r="A3153" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3153" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это</t>
+        </is>
+      </c>
+      <c r="C3153" s="2" t="n">
+        <v>3357</v>
+      </c>
+      <c r="D3153" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3154">
+      <c r="A3154" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3154" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника купить</t>
+        </is>
+      </c>
+      <c r="C3154" s="2" t="n">
+        <v>3099</v>
+      </c>
+      <c r="D3154" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3155">
+      <c r="A3155" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3155" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники</t>
+        </is>
+      </c>
+      <c r="C3155" s="2" t="n">
+        <v>3049</v>
+      </c>
+      <c r="D3155" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3155" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3156">
+      <c r="A3156" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3156" s="2" t="inlineStr">
+        <is>
+          <t>что такое трансмиссия</t>
+        </is>
+      </c>
+      <c r="C3156" s="2" t="n">
+        <v>2930</v>
+      </c>
+      <c r="D3156" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3156" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3157">
+      <c r="A3157" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3157" s="2" t="inlineStr">
+        <is>
+          <t>сервопривод это</t>
+        </is>
+      </c>
+      <c r="C3157" s="2" t="n">
+        <v>2891</v>
+      </c>
+      <c r="D3157" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3158">
+      <c r="A3158" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3158" s="2" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 мехатроника</t>
+        </is>
+      </c>
+      <c r="C3158" s="2" t="n">
+        <v>2666</v>
+      </c>
+      <c r="D3158" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3159">
+      <c r="A3159" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3159" s="2" t="inlineStr">
+        <is>
+          <t>робот козел</t>
+        </is>
+      </c>
+      <c r="C3159" s="2" t="n">
+        <v>2531</v>
+      </c>
+      <c r="D3159" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3159" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3160">
+      <c r="A3160" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3160" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что</t>
+        </is>
+      </c>
+      <c r="C3160" s="2" t="n">
+        <v>2428</v>
+      </c>
+      <c r="D3160" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3160" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3161">
+      <c r="A3161" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3161" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg</t>
+        </is>
+      </c>
+      <c r="C3161" s="2" t="n">
+        <v>2262</v>
+      </c>
+      <c r="D3161" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3161" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3162">
+      <c r="A3162" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3162" s="2" t="inlineStr">
+        <is>
+          <t>ремонт мехатроника</t>
+        </is>
+      </c>
+      <c r="C3162" s="2" t="n">
+        <v>2172</v>
+      </c>
+      <c r="D3162" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3163">
+      <c r="A3163" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3163" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника дсг 7</t>
+        </is>
+      </c>
+      <c r="C3163" s="2" t="n">
+        <v>2134</v>
+      </c>
+      <c r="D3163" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3163" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3164">
+      <c r="A3164" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3164" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг</t>
+        </is>
+      </c>
+      <c r="C3164" s="2" t="n">
+        <v>2037</v>
+      </c>
+      <c r="D3164" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3164" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3165">
+      <c r="A3165" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3165" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C3165" s="2" t="n">
+        <v>1937</v>
+      </c>
+      <c r="D3165" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3165" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3166">
+      <c r="A3166" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3166" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C3166" s="2" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D3166" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3166" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3167">
+      <c r="A3167" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3167" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3167" s="2" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D3167" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3167" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3168">
+      <c r="A3168" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3168" s="2" t="inlineStr">
+        <is>
+          <t>роботех</t>
+        </is>
+      </c>
+      <c r="C3168" s="2" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D3168" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3169">
+      <c r="A3169" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3169" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника кем работать</t>
+        </is>
+      </c>
+      <c r="C3169" s="2" t="n">
+        <v>1805</v>
+      </c>
+      <c r="D3169" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3169" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3170">
+      <c r="A3170" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3170" s="2" t="inlineStr">
+        <is>
+          <t>коробка передач робот что это</t>
+        </is>
+      </c>
+      <c r="C3170" s="2" t="n">
+        <v>1781</v>
+      </c>
+      <c r="D3170" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3170" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3171">
+      <c r="A3171" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3171" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать</t>
+        </is>
+      </c>
+      <c r="C3171" s="2" t="n">
+        <v>1716</v>
+      </c>
+      <c r="D3171" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3171" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3172">
+      <c r="A3172" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3172" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3172" s="2" t="n">
+        <v>1632</v>
+      </c>
+      <c r="D3172" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3172" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3173">
+      <c r="A3173" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3173" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника что за профессия</t>
+        </is>
+      </c>
+      <c r="C3173" s="2" t="n">
+        <v>1626</v>
+      </c>
+      <c r="D3173" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3173" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3174">
+      <c r="A3174" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3174" s="2" t="inlineStr">
+        <is>
+          <t>робот федор</t>
+        </is>
+      </c>
+      <c r="C3174" s="2" t="n">
+        <v>1602</v>
+      </c>
+      <c r="D3174" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3174" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3175">
+      <c r="A3175" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3175" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что за профессия</t>
+        </is>
+      </c>
+      <c r="C3175" s="2" t="n">
+        <v>1557</v>
+      </c>
+      <c r="D3175" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3175" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3176">
+      <c r="A3176" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3176" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7</t>
+        </is>
+      </c>
+      <c r="C3176" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="D3176" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3176" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3177">
+      <c r="A3177" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3177" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C3177" s="2" t="n">
+        <v>1380</v>
+      </c>
+      <c r="D3177" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3177" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3178">
+      <c r="A3178" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3178" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника dq250</t>
+        </is>
+      </c>
+      <c r="C3178" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="D3178" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3178" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3179">
+      <c r="A3179" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3179" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника ауди</t>
+        </is>
+      </c>
+      <c r="C3179" s="2" t="n">
+        <v>1312</v>
+      </c>
+      <c r="D3179" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3179" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3180">
+      <c r="A3180" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3180" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается коробка автомат от робота</t>
+        </is>
+      </c>
+      <c r="C3180" s="2" t="n">
+        <v>1288</v>
+      </c>
+      <c r="D3180" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3180" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3181">
+      <c r="A3181" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3181" s="2" t="inlineStr">
+        <is>
+          <t>вкалывают роботы а не человек</t>
+        </is>
+      </c>
+      <c r="C3181" s="2" t="n">
+        <v>1251</v>
+      </c>
+      <c r="D3181" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3181" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3182">
+      <c r="A3182" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3182" s="2" t="inlineStr">
+        <is>
+          <t>масло мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C3182" s="2" t="n">
+        <v>1247</v>
+      </c>
+      <c r="D3182" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3182" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3183">
+      <c r="A3183" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3183" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dsg</t>
+        </is>
+      </c>
+      <c r="C3183" s="2" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D3183" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3183" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3184">
+      <c r="A3184" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3184" s="2" t="inlineStr">
+        <is>
+          <t>чем отличается вариатор от робота</t>
+        </is>
+      </c>
+      <c r="C3184" s="2" t="n">
+        <v>1197</v>
+      </c>
+      <c r="D3184" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3184" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3185">
+      <c r="A3185" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3185" s="2" t="inlineStr">
+        <is>
+          <t>снятие мехатроника</t>
+        </is>
+      </c>
+      <c r="C3185" s="2" t="n">
+        <v>1188</v>
+      </c>
+      <c r="D3185" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3185" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3186">
+      <c r="A3186" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3186" s="2" t="inlineStr">
+        <is>
+          <t>цена мехатроника</t>
+        </is>
+      </c>
+      <c r="C3186" s="2" t="n">
+        <v>1177</v>
+      </c>
+      <c r="D3186" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3186" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3187">
+      <c r="A3187" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3187" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это</t>
+        </is>
+      </c>
+      <c r="C3187" s="2" t="n">
+        <v>1147</v>
+      </c>
+      <c r="D3187" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3187" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3188">
+      <c r="A3188" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3188" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7</t>
+        </is>
+      </c>
+      <c r="C3188" s="2" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D3188" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3189">
+      <c r="A3189" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3189" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник шкода</t>
+        </is>
+      </c>
+      <c r="C3189" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="D3189" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3189" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3190">
+      <c r="A3190" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3190" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C3190" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D3190" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3191">
+      <c r="A3191" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3191" s="2" t="inlineStr">
+        <is>
+          <t>замена масла в мехатронике</t>
+        </is>
+      </c>
+      <c r="C3191" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D3191" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3191" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3192">
+      <c r="A3192" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3192" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника фольксваген</t>
+        </is>
+      </c>
+      <c r="C3192" s="2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D3192" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3192" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3193" s="2" t="inlineStr">
+        <is>
+          <t>ремкомплект мехатроника</t>
+        </is>
+      </c>
+      <c r="C3193" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="D3193" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3193" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3194">
+      <c r="A3194" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3194" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника шкода октавия</t>
+        </is>
+      </c>
+      <c r="C3194" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="D3194" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3195">
+      <c r="A3195" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3195" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника факультеты</t>
+        </is>
+      </c>
+      <c r="C3195" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="D3195" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3196">
+      <c r="A3196" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3196" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника акпп</t>
+        </is>
+      </c>
+      <c r="C3196" s="2" t="n">
+        <v>924</v>
+      </c>
+      <c r="D3196" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3197">
+      <c r="A3197" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3197" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C3197" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="D3197" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3197" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3198">
+      <c r="A3198" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3198" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой</t>
+        </is>
+      </c>
+      <c r="C3198" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="D3198" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3198" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3199">
+      <c r="A3199" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3199" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника обучение</t>
+        </is>
+      </c>
+      <c r="C3199" s="2" t="n">
+        <v>882</v>
+      </c>
+      <c r="D3199" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3199" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3200">
+      <c r="A3200" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3200" s="2" t="inlineStr">
+        <is>
+          <t>масло мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C3200" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="D3200" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3200" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3201">
+      <c r="A3201" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3201" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C3201" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="D3201" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3201" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3202">
+      <c r="A3202" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3202" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника направления</t>
+        </is>
+      </c>
+      <c r="C3202" s="2" t="n">
+        <v>862</v>
+      </c>
+      <c r="D3202" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3202" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3203">
+      <c r="A3203" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3203" s="2" t="inlineStr">
+        <is>
+          <t>замена мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C3203" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="D3203" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3203" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3204">
+      <c r="A3204" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3204" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроника dsg 7</t>
+        </is>
+      </c>
+      <c r="C3204" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="D3204" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3204" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3205">
+      <c r="A3205" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3205" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии</t>
+        </is>
+      </c>
+      <c r="C3205" s="2" t="n">
+        <v>818</v>
+      </c>
+      <c r="D3205" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3205" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3206">
+      <c r="A3206" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3206" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C3206" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="D3206" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3206" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3207">
+      <c r="A3207" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3207" s="2" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C3207" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="D3207" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3207" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3208">
+      <c r="A3208" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3208" s="2" t="inlineStr">
+        <is>
+          <t>факультет мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C3208" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="D3208" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3208" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3209">
+      <c r="A3209" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3209" s="2" t="inlineStr">
+        <is>
+          <t>r2d2 робот</t>
+        </is>
+      </c>
+      <c r="C3209" s="2" t="n">
+        <v>691</v>
+      </c>
+      <c r="D3209" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3209" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3210">
+      <c r="A3210" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3210" s="2" t="inlineStr">
+        <is>
+          <t>направление мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3210" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="D3210" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3210" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3211">
+      <c r="A3211" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3211" s="2" t="inlineStr">
+        <is>
+          <t>обучение мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3211" s="2" t="n">
+        <v>678</v>
+      </c>
+      <c r="D3211" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3211" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3212">
+      <c r="A3212" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3212" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника вузы</t>
+        </is>
+      </c>
+      <c r="C3212" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="D3212" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3212" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3213">
+      <c r="A3213" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3213" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии светлый</t>
+        </is>
+      </c>
+      <c r="C3213" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="D3213" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3213" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3214">
+      <c r="A3214" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3214" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C3214" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="D3214" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3214" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3215">
+      <c r="A3215" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3215" s="2" t="inlineStr">
+        <is>
+          <t>профессия мехатроника и робототехника кем работать</t>
+        </is>
+      </c>
+      <c r="C3215" s="2" t="n">
+        <v>548</v>
+      </c>
+      <c r="D3215" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3215" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3216">
+      <c r="A3216" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3216" s="2" t="inlineStr">
+        <is>
+          <t>15.03 06 мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3216" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="D3216" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3216" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3217">
+      <c r="A3217" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3217" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми</t>
+        </is>
+      </c>
+      <c r="C3217" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="D3217" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3217" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3218">
+      <c r="A3218" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3218" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника баллы</t>
+        </is>
+      </c>
+      <c r="C3218" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="D3218" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3218" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3219">
+      <c r="A3219" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3219" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми словами</t>
+        </is>
+      </c>
+      <c r="C3219" s="2" t="n">
+        <v>457</v>
+      </c>
+      <c r="D3219" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3219" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3220">
+      <c r="A3220" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3220" s="2" t="inlineStr">
+        <is>
+          <t>институт мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C3220" s="2" t="n">
+        <v>452</v>
+      </c>
+      <c r="D3220" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3220" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3221">
+      <c r="A3221" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3221" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C3221" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D3221" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3221" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3222">
+      <c r="A3222" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3222" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C3222" s="2" t="n">
+        <v>447</v>
+      </c>
+      <c r="D3222" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3222" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3223">
+      <c r="A3223" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3223" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника</t>
+        </is>
+      </c>
+      <c r="C3223" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="D3223" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3223" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3224">
+      <c r="A3224" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3224" s="2" t="inlineStr">
+        <is>
+          <t>кем работают после мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C3224" s="2" t="n">
+        <v>435</v>
+      </c>
+      <c r="D3224" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3224" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3225">
+      <c r="A3225" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3225" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C3225" s="2" t="n">
+        <v>428</v>
+      </c>
+      <c r="D3225" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3225" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3226">
+      <c r="A3226" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3226" s="2" t="inlineStr">
+        <is>
+          <t>что такое мехатроник</t>
+        </is>
+      </c>
+      <c r="C3226" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="D3226" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3226" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3227">
+      <c r="A3227" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3227" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника университеты</t>
+        </is>
+      </c>
+      <c r="C3227" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="D3227" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3227" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3228">
+      <c r="A3228" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3228" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника поступить</t>
+        </is>
+      </c>
+      <c r="C3228" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="D3228" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3228" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3229">
+      <c r="A3229" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3229" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника зарплата</t>
+        </is>
+      </c>
+      <c r="C3229" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="D3229" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3229" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3230">
+      <c r="A3230" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3230" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника учиться</t>
+        </is>
+      </c>
+      <c r="C3230" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="D3230" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3230" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3231">
+      <c r="A3231" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3231" s="2" t="inlineStr">
+        <is>
+          <t>программа мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3231" s="2" t="n">
+        <v>345</v>
+      </c>
+      <c r="D3231" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3231" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3232">
+      <c r="A3232" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3232" s="2" t="inlineStr">
+        <is>
+          <t>15.02 10 мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3232" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="D3232" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3232" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3233">
+      <c r="A3233" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3233" s="2" t="inlineStr">
+        <is>
+          <t>специалист по мехатронике и робототехнике</t>
+        </is>
+      </c>
+      <c r="C3233" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="D3233" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3233" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3234">
+      <c r="A3234" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3234" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника колледжи</t>
+        </is>
+      </c>
+      <c r="C3234" s="2" t="n">
+        <v>332</v>
+      </c>
+      <c r="D3234" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3234" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3235">
+      <c r="A3235" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3235" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника предметы</t>
+        </is>
+      </c>
+      <c r="C3235" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="D3235" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3235" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3236">
+      <c r="A3236" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3236" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника проходные баллы</t>
+        </is>
+      </c>
+      <c r="C3236" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="D3236" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3236" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3237">
+      <c r="A3237" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3237" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника отзывы</t>
+        </is>
+      </c>
+      <c r="C3237" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="D3237" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3237" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3238">
+      <c r="A3238" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3238" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какая специальность</t>
+        </is>
+      </c>
+      <c r="C3238" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="D3238" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3238" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3239">
+      <c r="A3239" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3239" s="2" t="inlineStr">
+        <is>
+          <t>курс мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C3239" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="D3239" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3239" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3240">
+      <c r="A3240" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3240" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что это</t>
+        </is>
+      </c>
+      <c r="C3240" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="D3240" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3240" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3241">
+      <c r="A3241" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3241" s="2" t="inlineStr">
+        <is>
+          <t>магистратура робототехника и мехатроника</t>
+        </is>
+      </c>
+      <c r="C3241" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="D3241" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3241" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3242">
+      <c r="A3242" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3242" s="2" t="inlineStr">
+        <is>
+          <t>политех мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3242" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="D3242" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3242" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3243">
+      <c r="A3243" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3243" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника код</t>
+        </is>
+      </c>
+      <c r="C3243" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="D3243" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3243" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3244">
+      <c r="A3244" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3244" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника учебный план</t>
+        </is>
+      </c>
+      <c r="C3244" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D3244" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3244" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3245">
+      <c r="A3245" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3245" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника в машине это</t>
+        </is>
+      </c>
+      <c r="C3245" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="D3245" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3245" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3246">
+      <c r="A3246" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3246" s="2" t="inlineStr">
+        <is>
+          <t>15.02 10 мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C3246" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="D3246" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3246" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3247">
+      <c r="A3247" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3247" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника мгту</t>
+        </is>
+      </c>
+      <c r="C3247" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="D3247" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3247" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3248">
+      <c r="A3248" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3248" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника урфу</t>
+        </is>
+      </c>
+      <c r="C3248" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="D3248" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3248" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3249">
+      <c r="A3249" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3249" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C3249" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="D3249" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3249" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3250">
+      <c r="A3250" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3250" s="2" t="inlineStr">
+        <is>
+          <t>кафедры мехатроники и робототехники</t>
+        </is>
+      </c>
+      <c r="C3250" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D3250" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3250" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3251">
+      <c r="A3251" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3251" s="2" t="inlineStr">
+        <is>
+          <t>мэи робототехника и мехатроника</t>
+        </is>
+      </c>
+      <c r="C3251" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="D3251" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3251" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3252">
+      <c r="A3252" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3252" s="2" t="inlineStr">
+        <is>
+          <t>баумана мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3252" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="D3252" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3252" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3253">
+      <c r="A3253" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3253" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C3253" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="D3253" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3253" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3254">
+      <c r="A3254" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3254" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какой факультет</t>
+        </is>
+      </c>
+      <c r="C3254" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="D3254" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3254" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3255">
+      <c r="A3255" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3255" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C3255" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="D3255" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3255" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3256">
+      <c r="A3256" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3256" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C3256" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="D3256" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3256" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3257">
+      <c r="A3257" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3257" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в машине это</t>
+        </is>
+      </c>
+      <c r="C3257" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3257" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3257" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3258">
+      <c r="A3258" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3258" s="2" t="inlineStr">
+        <is>
+          <t>итмо мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3258" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="D3258" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3258" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3259">
+      <c r="A3259" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3259" s="2" t="inlineStr">
+        <is>
+          <t>москва мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3259" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="D3259" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3259" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3260">
+      <c r="A3260" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3260" s="2" t="inlineStr">
+        <is>
+          <t>спо мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3260" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D3260" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3260" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3261">
+      <c r="A3261" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3261" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника колледж кем работать</t>
+        </is>
+      </c>
+      <c r="C3261" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D3261" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3261" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3262">
+      <c r="A3262" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3262" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника работа</t>
+        </is>
+      </c>
+      <c r="C3262" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="D3262" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3262" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3263">
+      <c r="A3263" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3263" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника юургу</t>
+        </is>
+      </c>
+      <c r="C3263" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="D3263" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3263" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3264">
+      <c r="A3264" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3264" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника спб</t>
+        </is>
+      </c>
+      <c r="C3264" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="D3264" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3264" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3265">
+      <c r="A3265" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3265" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника профессия это</t>
+        </is>
+      </c>
+      <c r="C3265" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="D3265" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3265" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3266">
+      <c r="A3266" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3266" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника какие предметы</t>
+        </is>
+      </c>
+      <c r="C3266" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="D3266" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3266" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3267">
+      <c r="A3267" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3267" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после колледжа</t>
+        </is>
+      </c>
+      <c r="C3267" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="D3267" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3267" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3268">
+      <c r="A3268" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3268" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника робототехника и машиностроение</t>
+        </is>
+      </c>
+      <c r="C3268" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="D3268" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3268" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3269">
+      <c r="A3269" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3269" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это коробка</t>
+        </is>
+      </c>
+      <c r="C3269" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="D3269" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3269" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3270">
+      <c r="A3270" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3270" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C3270" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="D3270" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3270" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3271">
+      <c r="A3271" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3271" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в коробке передач это</t>
+        </is>
+      </c>
+      <c r="C3271" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="D3271" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3271" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3272">
+      <c r="A3272" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3272" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после вуза</t>
+        </is>
+      </c>
+      <c r="C3272" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="D3272" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3272" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3273">
+      <c r="A3273" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3273" s="2" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C3273" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="D3273" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3273" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3274">
+      <c r="A3274" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3274" s="2" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C3274" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="D3274" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3274" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3275">
+      <c r="A3275" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3275" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C3275" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="D3275" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3275" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3276">
+      <c r="A3276" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3276" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника по отраслям что это</t>
+        </is>
+      </c>
+      <c r="C3276" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="D3276" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3276" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3277">
+      <c r="A3277" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3277" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что это за профессия</t>
+        </is>
+      </c>
+      <c r="C3277" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3277" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3277" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3278">
+      <c r="A3278" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3278" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C3278" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D3278" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3278" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3279">
+      <c r="A3279" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3279" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что за профессия зарплата</t>
+        </is>
+      </c>
+      <c r="C3279" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3279" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3279" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3280">
+      <c r="A3280" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3280" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C3280" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3280" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3280" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3281">
+      <c r="A3281" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3281" s="2" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C3281" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3281" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3281" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3282">
+      <c r="A3282" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3282" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C3282" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="D3282" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3282" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3283">
+      <c r="A3283" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3283" s="2" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C3283" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3283" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3283" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3284">
+      <c r="A3284" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3284" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C3284" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3284" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3284" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3285">
+      <c r="A3285" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3285" s="2" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C3285" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D3285" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3285" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3286">
+      <c r="A3286" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3286" s="2" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C3286" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="D3286" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3286" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3287">
+      <c r="A3287" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3287" s="2" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C3287" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3287" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3287" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3288">
+      <c r="A3288" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3288" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C3288" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="D3288" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3288" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3289">
+      <c r="A3289" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3289" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника в автомобиле это</t>
+        </is>
+      </c>
+      <c r="C3289" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D3289" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3289" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3290">
+      <c r="A3290" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3290" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C3290" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3290" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3290" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3291">
+      <c r="A3291" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3291" s="2" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C3291" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3291" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3291" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3292">
+      <c r="A3292" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3292" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C3292" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3292" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3292" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3293">
+      <c r="A3293" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3293" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроника это</t>
+        </is>
+      </c>
+      <c r="C3293" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3293" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3293" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3294">
+      <c r="A3294" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3294" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C3294" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D3294" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3294" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3295">
+      <c r="A3295" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3295" s="2" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C3295" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="D3295" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3295" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3296">
+      <c r="A3296" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3296" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C3296" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3296" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3296" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3297">
+      <c r="A3297" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3297" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C3297" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3297" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3297" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3298">
+      <c r="A3298" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3298" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник что это такое в автомобиле</t>
+        </is>
+      </c>
+      <c r="C3298" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3298" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3298" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3299">
+      <c r="A3299" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3299" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроник это</t>
+        </is>
+      </c>
+      <c r="C3299" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3299" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3299" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3300">
+      <c r="A3300" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3300" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника что это за специальность</t>
+        </is>
+      </c>
+      <c r="C3300" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3300" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3300" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3301">
+      <c r="A3301" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3301" s="2" t="inlineStr">
+        <is>
+          <t>специальность мехатроника и робототехника это</t>
+        </is>
+      </c>
+      <c r="C3301" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3301" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3301" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3302">
+      <c r="A3302" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3302" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это профессия</t>
+        </is>
+      </c>
+      <c r="C3302" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D3302" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3302" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3303">
+      <c r="A3303" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3303" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C3303" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D3303" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3303" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3304">
+      <c r="A3304" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3304" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C3304" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D3304" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3304" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3305">
+      <c r="A3305" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3305" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника что за профессия</t>
+        </is>
+      </c>
+      <c r="C3305" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3305" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3305" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3306">
+      <c r="A3306" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3306" s="2" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C3306" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D3306" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3306" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3307">
+      <c r="A3307" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3307" s="2" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C3307" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3307" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3307" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3308">
+      <c r="A3308" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3308" s="2" t="inlineStr">
+        <is>
+          <t>техник мехатроника это</t>
+        </is>
+      </c>
+      <c r="C3308" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D3308" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3308" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3309">
+      <c r="A3309" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3309" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C3309" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3309" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3309" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3310">
+      <c r="A3310" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3310" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C3310" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3310" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3310" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3311">
+      <c r="A3311" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3311" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника акпп это</t>
+        </is>
+      </c>
+      <c r="C3311" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3311" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3311" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3312">
+      <c r="A3312" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3312" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C3312" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3312" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3312" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3313">
+      <c r="A3313" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3313" s="2" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C3313" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3313" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3313" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3314">
+      <c r="A3314" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3314" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C3314" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3314" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3314" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3315">
+      <c r="A3315" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3315" s="2" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C3315" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3315" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3315" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3316">
+      <c r="A3316" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3316" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C3316" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3316" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3316" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3317">
+      <c r="A3317" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3317" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C3317" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3317" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3317" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3318">
+      <c r="A3318" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3318" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C3318" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3318" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3318" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3319">
+      <c r="A3319" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3319" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C3319" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3319" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3319" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3320">
+      <c r="A3320" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3320" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dsg это</t>
+        </is>
+      </c>
+      <c r="C3320" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3320" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3320" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3321">
+      <c r="A3321" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3321" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C3321" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3321" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3321" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3322">
+      <c r="A3322" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3322" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника это простыми словами в машине</t>
+        </is>
+      </c>
+      <c r="C3322" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3322" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3322" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3323">
+      <c r="A3323" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3323" s="2" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C3323" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3323" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3323" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3324">
+      <c r="A3324" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3324" s="2" t="inlineStr">
+        <is>
+          <t>мехатроника и мобильная робототехника что это</t>
+        </is>
+      </c>
+      <c r="C3324" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D3324" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3324" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3325">
+      <c r="A3325" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3325" s="2" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C3325" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3325" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3325" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3326">
+      <c r="A3326" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3326" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в акпп что это</t>
+        </is>
+      </c>
+      <c r="C3326" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3326" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3326" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3327">
+      <c r="A3327" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3327" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в дсг это</t>
+        </is>
+      </c>
+      <c r="C3327" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3327" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3327" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3328">
+      <c r="A3328" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3328" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник в авто это</t>
+        </is>
+      </c>
+      <c r="C3328" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3328" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3328" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3329">
+      <c r="A3329" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3329" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник это простыми словами</t>
+        </is>
+      </c>
+      <c r="C3329" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3329" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3329" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3330">
+      <c r="A3330" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3330" s="2" t="inlineStr">
+        <is>
+          <t>инженер мехатроник это кто и чем занимается</t>
+        </is>
+      </c>
+      <c r="C3330" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3330" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3330" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3331">
+      <c r="A3331" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3331" s="2" t="inlineStr">
+        <is>
+          <t>техник мехатроник это</t>
+        </is>
+      </c>
+      <c r="C3331" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3331" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3331" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3332">
+      <c r="A3332" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3332" s="2" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии город светлый</t>
+        </is>
+      </c>
+      <c r="C3332" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3332" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3332" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3333">
+      <c r="A3333" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3333" s="2" t="inlineStr">
+        <is>
+          <t>специалист по мехатронике и робототехнике это</t>
+        </is>
+      </c>
+      <c r="C3333" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3333" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3333" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3334">
+      <c r="A3334" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3334" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 это</t>
+        </is>
+      </c>
+      <c r="C3334" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3334" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3334" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3335">
+      <c r="A3335" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B3335" s="2" t="inlineStr">
+        <is>
+          <t>компьютерная мехатроника это</t>
+        </is>
+      </c>
+      <c r="C3335" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3335" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3335" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3336">
+      <c r="A3336" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3336" s="2" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
+      <c r="C3336" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="D3336" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3336" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3337">
+      <c r="A3337" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3337" s="2" t="inlineStr">
+        <is>
+          <t>штоки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C3337" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="D3337" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3337" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3338">
+      <c r="A3338" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3338" s="2" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200</t>
+        </is>
+      </c>
+      <c r="C3338" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D3338" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3338" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3339">
+      <c r="A3339" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3339" s="2" t="inlineStr">
+        <is>
+          <t>замена штоков dq200</t>
+        </is>
+      </c>
+      <c r="C3339" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D3339" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3339" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3340">
+      <c r="A3340" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3340" s="2" t="inlineStr">
+        <is>
+          <t>пыльники штоков dq200</t>
+        </is>
+      </c>
+      <c r="C3340" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D3340" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3340" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3341">
+      <c r="A3341" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3341" s="2" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C3341" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D3341" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3341" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3342">
+      <c r="A3342" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3342" s="2" t="inlineStr">
+        <is>
+          <t>штоки вилок dq200</t>
+        </is>
+      </c>
+      <c r="C3342" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3342" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3342" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3343">
+      <c r="A3343" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3343" s="2" t="inlineStr">
+        <is>
+          <t>длина штоков dq200</t>
+        </is>
+      </c>
+      <c r="C3343" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3343" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3343" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3344">
+      <c r="A3344" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3344" s="2" t="inlineStr">
+        <is>
+          <t>замена штока мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C3344" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3344" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3344" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3345">
+      <c r="A3345" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3345" s="2" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C3345" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3345" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3345" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3346">
+      <c r="A3346" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3346" s="2" t="inlineStr">
+        <is>
+          <t>штоки переключения передач dq200</t>
+        </is>
+      </c>
+      <c r="C3346" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3346" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3346" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3347">
+      <c r="A3347" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3347" s="2" t="inlineStr">
+        <is>
+          <t>dq200 замена штоков сцепления</t>
+        </is>
+      </c>
+      <c r="C3347" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3347" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3347" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3348">
+      <c r="A3348" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3348" s="2" t="inlineStr">
+        <is>
+          <t>какие стоят штоки сцепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C3348" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3348" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3348" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3349">
+      <c r="A3349" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3349" s="2" t="inlineStr">
+        <is>
+          <t>стакан штока dq200</t>
+        </is>
+      </c>
+      <c r="C3349" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3349" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3349" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3350">
+      <c r="A3350" s="2" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B3350" s="2" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200 отличия с 2012 года</t>
+        </is>
+      </c>
+      <c r="C3350" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3350" s="2" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3350" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E3079"/>
+  <autoFilter ref="A1:E3350"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="17860" windowHeight="10480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Семантика" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Семантика" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$65</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -191,6 +191,10 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -646,12 +650,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1064,13 +1069,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,8 +1106,1608 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>70225</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>16891</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроника</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>4602</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника это</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3165</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2428</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1552</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника что за профессия</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1391</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>818</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>колледж мехатроники и пищевой индустрии светлый</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>584</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>15.03 06 мехатроника и робототехника</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>462</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>15.02 10 мехатроника и робототехника по отраслям</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после колледжа</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника и робототехника кем работать после вуза</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="17860" windowHeight="10480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Семантика" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Семантика" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$54</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -191,6 +191,10 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -646,12 +650,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1064,13 +1069,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1100,8 +1106,1333 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>70225</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроника</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4602</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>мехатроника это</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3165</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$90</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2431,8 +2431,908 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации что</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>13353</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации это</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>10829</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации что это</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>анизотропная фильтрация</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>4620</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>что такое скорость клубочковой фильтрации</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>3708</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>система фильтрации воды для дома</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>2251</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>скорость клубочковой фильтрации понижена</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dq500</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>675</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>корпус фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>масляный фильтр dq500</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>замена фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>фильтр акпп dq500</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>алюминиевый корпус фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>фильтр дсг dq500</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dsg 7 dq500</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>корпус фильтра dsg dq500</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dq500 tiguan</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>фильтр в коробку dq500</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dq500 артикул</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>фильтр для dsg dq500</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>фильтр кпп dq500</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>корпус фильтра коробки dq500</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>фильтр дсг 7 dq500</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>какой фильтр для dq500</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>dq500 крышка фильтра алюминиевая</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dsg dq500 подделка и оригинал</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра шкода кодиак коробка dq500</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>алюминиевый стакан фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>фильтр масляный кпп дсг dq500</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>алюминиевый корпус фильтра dq500 каталожный номер</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>зеленое кольцо для корпуса фильтра дсг dq500</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>крышка фильтра акпп для dq500 вместо dq250</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>dq500 маленькое резиновое колечко в фильтре</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>фильтр дсг 7 dq500 сколько штук</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>замена внутреннего фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E54"/>
+  <autoFilter ref="A1:E90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$112</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3331,8 +3331,558 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>прокладка сливной пробки</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>15735</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>крышка с гидрозатвором</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>3234</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>пневмозаглушка</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>2829</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>антизаглушка</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>1899</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>крышки полинка</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>1654</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>как закрыть банку с закручивающейся крышкой</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>крышка с гидрозатвором на банку</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>прокладка клапанной крышки 4216</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>557</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>как открыть закатанную крышку банки</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>481</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>крышка ступицы бпв</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>389</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>пробковая прокладка клапанной крышки</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>388</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>крышка ступицы bpw</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>387</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>банка с крышкой на защелке</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>366</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>винтовые крышки для банок как закрыть правильно</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>как открыть банку с закатанной крышкой</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>как разобрать крышку термоса с кнопкой</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>как открыть крышку унитаза с кнопкой вверху</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>заглушка dq200</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>заглушка кпп dq200</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>заглушка первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>задняя крышка заглушка корпуса механической части dq200</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>замена заглушки первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E90"/>
+  <autoFilter ref="A1:E112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$117</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3881,8 +3881,133 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>0BH325159</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>0bh325159</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>0BH325159</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>0bh325159 vag</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>0BH325159</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>0bh325159 алюминиевый</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>0BH325159</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>0bh325159 vag корпус</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>0BH325159</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>0bh325159 vag корпус фильтра</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E112"/>
+  <autoFilter ref="A1:E117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$197</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4006,8 +4006,2008 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>штоки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков dq200</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>пыльники штоков dq200</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>штоки вилок dq200</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>длина штоков dq200</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>замена штока мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>штоки переключения передач dq200</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>dq200 замена штоков сцепления</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>какие стоят штоки сцепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>стакан штока dq200</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200 отличия с 2012 года</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>штоки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков dq200</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>пыльники штоков dq200</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>штоки вилок dq200</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>длина штоков dq200</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>замена штока мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>штоки переключения передач dq200</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>dq200 замена штоков сцепления</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>какие стоят штоки сцепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>стакан штока dq200</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200 отличия с 2012 года</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E117"/>
+  <autoFilter ref="A1:E197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$300</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E300"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6006,8 +6006,2583 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>валы и шестерни кпп ямз 238вм</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра шкода кодиак коробка dq500</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7  0am325025 гидравлическая часть</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E197"/>
+  <autoFilter ref="A1:E300"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$402</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E300"/>
+  <dimension ref="A1:E402"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8581,8 +8581,2558 @@
         </is>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E308" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E309" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E311" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E312" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E318" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E323" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C324" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E324" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C326" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C328" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E328" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C330" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E330" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E331" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C338" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E339" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C340" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E345" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C348" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E349" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 0am325025 с электронной платой</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C350" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E350" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>электронная плата dq200</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E351" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>dsg7 dq200 электронная плата купить</t>
+        </is>
+      </c>
+      <c r="C352" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E352" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C353" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D353" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E353" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C354" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D354" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E354" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E355" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C356" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E356" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E357" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C358" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E358" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C359" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E359" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C360" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D360" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E360" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C361" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D361" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E361" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C362" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D362" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C363" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D363" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E363" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C364" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D364" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C366" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E366" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C367" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E367" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C368" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D368" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E368" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C369" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D369" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E369" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C370" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D370" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E370" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C371" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E371" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C372" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E372" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C373" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D373" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E373" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C374" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D374" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E374" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C375" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D375" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E375" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C376" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D376" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E376" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C377" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D377" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E377" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C378" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D378" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E378" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C379" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D379" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E379" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C380" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E380" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C381" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D381" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E381" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C382" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D382" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E382" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C383" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D383" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E383" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C384" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D384" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E384" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C385" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E385" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C386" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C387" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D387" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E387" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C388" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E388" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C389" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E389" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C390" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D390" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E390" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C391" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C392" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D392" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E392" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C393" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D393" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E393" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C394" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D394" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E394" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C395" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D395" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E395" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C396" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D396" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E396" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C397" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D397" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E397" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C398" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D398" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E398" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C399" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C400" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D400" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E400" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C401" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D401" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C402" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D402" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E300"/>
+  <autoFilter ref="A1:E402"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$427</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E402"/>
+  <dimension ref="A1:E427"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11131,8 +11131,633 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C403" s="3" t="n">
+        <v>568</v>
+      </c>
+      <c r="D403" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="D404" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E404" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C405" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="D405" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E405" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C406" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D406" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E406" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D407" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E407" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>замена крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D408" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E408" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C409" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D409" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E409" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>тверь крышка мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C410" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D410" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E410" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="inlineStr">
+        <is>
+          <t>крышка сапуна мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C411" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D411" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E411" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>замена прокладки крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C412" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D412" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E412" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="inlineStr">
+        <is>
+          <t>степень затяжки болтов крышки мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C413" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D413" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E413" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>допустимая величина бокового сдвига редуктора на оси</t>
+        </is>
+      </c>
+      <c r="C414" s="3" t="n">
+        <v>562</v>
+      </c>
+      <c r="D414" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E414" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B415" s="3" t="inlineStr">
+        <is>
+          <t>болты мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C415" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D415" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E415" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>затяжка болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C416" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D416" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E416" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B417" s="3" t="inlineStr">
+        <is>
+          <t>момент затяжки болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C417" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D417" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E417" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t>болты крепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C418" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D418" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E418" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B419" s="3" t="inlineStr">
+        <is>
+          <t>степень затяжки болтов крышки мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C419" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D419" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E419" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>комплект болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C420" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D420" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E420" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B421" s="3" t="inlineStr">
+        <is>
+          <t>допустимая величина бокового сдвига редуктора на оси</t>
+        </is>
+      </c>
+      <c r="C421" s="3" t="n">
+        <v>562</v>
+      </c>
+      <c r="D421" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E421" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>болты мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D422" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E422" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B423" s="3" t="inlineStr">
+        <is>
+          <t>затяжка болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C423" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D423" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E423" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>момент затяжки болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C424" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D424" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E424" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B425" s="3" t="inlineStr">
+        <is>
+          <t>болты крепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C425" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D425" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E425" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>степень затяжки болтов крышки мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C426" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D426" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E426" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="3" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+      <c r="B427" s="3" t="inlineStr">
+        <is>
+          <t>комплект болтов мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C427" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D427" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E427" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E402"/>
+  <autoFilter ref="A1:E427"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$427</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$536</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E427"/>
+  <dimension ref="A1:E536"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11756,8 +11756,2733 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>плита dq200</t>
+        </is>
+      </c>
+      <c r="C428" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E428" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B429" s="3" t="inlineStr">
+        <is>
+          <t>плита мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C429" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="D429" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E429" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B430" s="3" t="inlineStr">
+        <is>
+          <t>усиленная плита dq200</t>
+        </is>
+      </c>
+      <c r="C430" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D430" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E430" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B431" s="3" t="inlineStr">
+        <is>
+          <t>плита мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C431" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D431" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E431" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>усиленная плита мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D432" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E432" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B433" s="3" t="inlineStr">
+        <is>
+          <t>момент затяжки плиты dq200</t>
+        </is>
+      </c>
+      <c r="C433" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D433" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E433" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>dq200 замена плиты</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D434" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E434" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 плита</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D435" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E435" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>усиленная плита мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D436" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E436" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B437" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C437" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D437" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E437" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C438" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D438" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E438" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B439" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C439" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D439" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E439" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B440" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C440" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D440" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E440" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B441" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C441" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D441" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E441" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B442" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C442" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D442" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E442" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B443" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C443" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D443" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E443" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C444" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D444" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E444" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B445" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C445" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D445" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E445" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C446" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D446" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E446" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B447" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C447" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D447" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E447" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C448" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D448" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E448" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B449" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C449" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D449" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E449" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C450" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D450" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E450" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B451" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C451" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D451" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E451" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C452" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D452" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E452" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B453" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C453" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D453" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E453" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C454" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D454" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E454" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B455" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C455" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D455" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E455" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C456" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D456" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E456" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B457" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C457" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D457" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E457" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C458" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D458" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E458" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B459" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C459" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D459" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E459" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C460" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D460" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E460" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B461" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C461" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D461" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E461" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C462" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D462" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E462" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B463" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C463" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D463" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E463" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C464" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D464" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E464" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B465" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C465" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D465" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E465" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B466" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C466" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D466" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E466" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B467" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C467" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D467" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E467" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C468" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D468" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E468" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B469" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C469" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D469" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E469" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C470" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D470" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E470" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C471" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D471" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E471" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B472" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C472" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D472" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E472" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B473" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C473" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D473" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E473" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C474" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D474" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E474" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B475" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C475" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D475" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E475" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C476" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D476" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E476" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B477" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C477" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D477" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E477" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C478" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D478" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E478" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B479" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C479" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D479" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E479" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D480" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E480" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B481" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C481" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D481" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E481" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D482" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E482" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C483" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D483" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E483" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D484" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E484" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B485" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C485" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D485" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E485" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C486" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D486" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E486" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B487" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C487" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D487" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E487" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C488" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D488" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E488" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B489" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C489" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D489" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E489" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C490" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D490" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E490" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B491" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C491" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D491" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E491" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D492" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E492" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C493" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D493" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E493" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D494" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E494" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C495" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D495" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E495" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D496" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E496" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B497" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C497" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D497" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E497" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D498" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E498" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B499" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C499" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D499" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E499" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C500" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D500" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E500" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B501" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C501" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D501" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E501" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C502" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D502" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E502" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B503" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C503" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D503" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E503" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C504" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D504" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E504" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B505" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C505" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D505" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E505" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C506" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D506" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E506" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B507" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C507" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D507" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E507" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C508" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D508" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E508" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B509" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C509" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D509" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E509" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C510" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D510" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E510" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B511" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C511" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D511" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E511" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C512" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D512" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E512" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B513" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C513" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D513" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E513" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C514" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D514" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E514" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C515" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D515" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E515" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B516" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C516" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D516" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E516" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B517" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C517" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D517" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E517" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C518" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D518" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E518" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B519" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C519" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D519" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E519" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C520" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D520" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E520" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B521" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C521" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D521" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E521" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C522" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D522" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E522" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B523" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C523" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D523" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E523" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C524" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D524" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E524" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B525" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C525" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D525" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E525" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B526" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C526" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D526" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E526" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B527" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C527" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D527" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E527" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B528" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C528" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D528" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E528" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B529" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C529" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D529" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E529" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B530" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C530" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D530" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E530" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B531" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C531" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D531" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E531" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B532" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C532" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D532" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E532" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B533" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C533" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D533" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E533" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B534" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C534" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D534" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E534" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B535" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C535" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D535" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E535" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B536" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C536" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D536" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E536" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E427"/>
+  <autoFilter ref="A1:E536"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$536</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$665</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E536"/>
+  <dimension ref="A1:E665"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14481,8 +14481,3233 @@
         </is>
       </c>
     </row>
+    <row r="537">
+      <c r="A537" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B537" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C537" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D537" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E537" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B538" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C538" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D538" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E538" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B539" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C539" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D539" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E539" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B540" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C540" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D540" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E540" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B541" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C541" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D541" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E541" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B542" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C542" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D542" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E542" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B543" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C543" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D543" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E543" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B544" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C544" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D544" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E544" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B545" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C545" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D545" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E545" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B546" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C546" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D546" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E546" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B547" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C547" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D547" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E547" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B548" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C548" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D548" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E548" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B549" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C549" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D549" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E549" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B550" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C550" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D550" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E550" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B551" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C551" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D551" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E551" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B552" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C552" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D552" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E552" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B553" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C553" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D553" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E553" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B554" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C554" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D554" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E554" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B555" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C555" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D555" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E555" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B556" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C556" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D556" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E556" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B557" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C557" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D557" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E557" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B558" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C558" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D558" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E558" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B559" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C559" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D559" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E559" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B560" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C560" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D560" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E560" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B561" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C561" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D561" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E561" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B562" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C562" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D562" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E562" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B563" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C563" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D563" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E563" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B564" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C564" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D564" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E564" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B565" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C565" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D565" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E565" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B566" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C566" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D566" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E566" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B567" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C567" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D567" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E567" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B568" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C568" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D568" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E568" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B569" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C569" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D569" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E569" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B570" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C570" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D570" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E570" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B571" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C571" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D571" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E571" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B572" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C572" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D572" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E572" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B573" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C573" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D573" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E573" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B574" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C574" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D574" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E574" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B575" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C575" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D575" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E575" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B576" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C576" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D576" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E576" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B577" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C577" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D577" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E577" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B578" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C578" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D578" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E578" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B579" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C579" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D579" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E579" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B580" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C580" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D580" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E580" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B581" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C581" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D581" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E581" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B582" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C582" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D582" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E582" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B583" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C583" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D583" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E583" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B584" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C584" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D584" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E584" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B585" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C585" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D585" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E585" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B586" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C586" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D586" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E586" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B587" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dq500</t>
+        </is>
+      </c>
+      <c r="C587" s="3" t="n">
+        <v>675</v>
+      </c>
+      <c r="D587" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E587" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B588" s="3" t="inlineStr">
+        <is>
+          <t>корпус фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C588" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="D588" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E588" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B589" s="3" t="inlineStr">
+        <is>
+          <t>масляный фильтр dq500</t>
+        </is>
+      </c>
+      <c r="C589" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="D589" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E589" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B590" s="3" t="inlineStr">
+        <is>
+          <t>замена фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C590" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D590" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E590" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B591" s="3" t="inlineStr">
+        <is>
+          <t>фильтр акпп dq500</t>
+        </is>
+      </c>
+      <c r="C591" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D591" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E591" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B592" s="3" t="inlineStr">
+        <is>
+          <t>алюминиевый корпус фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C592" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D592" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E592" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B593" s="3" t="inlineStr">
+        <is>
+          <t>фильтр дсг dq500</t>
+        </is>
+      </c>
+      <c r="C593" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D593" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E593" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B594" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dsg 7 dq500</t>
+        </is>
+      </c>
+      <c r="C594" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D594" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E594" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B595" s="3" t="inlineStr">
+        <is>
+          <t>корпус фильтра dsg dq500</t>
+        </is>
+      </c>
+      <c r="C595" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D595" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E595" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B596" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C596" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D596" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E596" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B597" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dq500 tiguan</t>
+        </is>
+      </c>
+      <c r="C597" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D597" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E597" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B598" s="3" t="inlineStr">
+        <is>
+          <t>фильтр в коробку dq500</t>
+        </is>
+      </c>
+      <c r="C598" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D598" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E598" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B599" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dq500 артикул</t>
+        </is>
+      </c>
+      <c r="C599" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D599" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E599" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B600" s="3" t="inlineStr">
+        <is>
+          <t>фильтр для dsg dq500</t>
+        </is>
+      </c>
+      <c r="C600" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D600" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E600" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B601" s="3" t="inlineStr">
+        <is>
+          <t>фильтр кпп dq500</t>
+        </is>
+      </c>
+      <c r="C601" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D601" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E601" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B602" s="3" t="inlineStr">
+        <is>
+          <t>корпус фильтра коробки dq500</t>
+        </is>
+      </c>
+      <c r="C602" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D602" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E602" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B603" s="3" t="inlineStr">
+        <is>
+          <t>фильтр дсг 7 dq500</t>
+        </is>
+      </c>
+      <c r="C603" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D603" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E603" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B604" s="3" t="inlineStr">
+        <is>
+          <t>какой фильтр для dq500</t>
+        </is>
+      </c>
+      <c r="C604" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D604" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E604" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B605" s="3" t="inlineStr">
+        <is>
+          <t>dq500 крышка фильтра алюминиевая</t>
+        </is>
+      </c>
+      <c r="C605" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D605" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E605" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B606" s="3" t="inlineStr">
+        <is>
+          <t>фильтр dsg dq500 подделка и оригинал</t>
+        </is>
+      </c>
+      <c r="C606" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D606" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E606" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B607" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра шкода кодиак коробка dq500</t>
+        </is>
+      </c>
+      <c r="C607" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D607" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E607" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B608" s="3" t="inlineStr">
+        <is>
+          <t>алюминиевый стакан фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C608" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D608" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E608" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B609" s="3" t="inlineStr">
+        <is>
+          <t>фильтр масляный кпп дсг dq500</t>
+        </is>
+      </c>
+      <c r="C609" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D609" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E609" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B610" s="3" t="inlineStr">
+        <is>
+          <t>алюминиевый корпус фильтра dq500 каталожный номер</t>
+        </is>
+      </c>
+      <c r="C610" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D610" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E610" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B611" s="3" t="inlineStr">
+        <is>
+          <t>зеленое кольцо для корпуса фильтра дсг dq500</t>
+        </is>
+      </c>
+      <c r="C611" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D611" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E611" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B612" s="3" t="inlineStr">
+        <is>
+          <t>крышка фильтра акпп для dq500 вместо dq250</t>
+        </is>
+      </c>
+      <c r="C612" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D612" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E612" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B613" s="3" t="inlineStr">
+        <is>
+          <t>dq500 маленькое резиновое колечко в фильтре</t>
+        </is>
+      </c>
+      <c r="C613" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D613" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E613" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B614" s="3" t="inlineStr">
+        <is>
+          <t>фильтр дсг 7 dq500 сколько штук</t>
+        </is>
+      </c>
+      <c r="C614" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D614" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E614" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="3" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+      <c r="B615" s="3" t="inlineStr">
+        <is>
+          <t>замена внутреннего фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C615" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D615" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E615" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B616" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C616" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D616" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E616" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B617" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C617" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D617" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E617" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B618" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C618" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D618" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E618" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B619" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C619" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D619" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E619" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B620" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C620" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D620" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E620" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B621" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C621" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D621" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E621" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B622" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C622" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D622" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E622" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B623" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C623" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D623" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E623" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B624" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C624" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D624" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E624" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B625" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C625" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D625" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E625" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B626" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C626" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D626" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E626" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B627" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C627" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D627" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E627" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B628" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C628" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D628" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E628" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B629" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C629" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D629" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E629" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B630" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C630" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D630" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E630" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B631" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C631" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D631" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E631" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B632" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C632" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D632" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E632" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B633" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C633" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D633" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E633" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B634" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C634" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D634" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E634" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B635" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C635" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D635" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E635" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B636" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C636" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D636" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E636" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B637" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C637" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D637" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E637" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B638" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C638" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D638" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E638" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B639" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C639" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D639" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E639" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B640" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C640" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D640" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E640" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B641" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C641" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D641" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E641" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B642" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C642" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D642" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E642" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B643" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C643" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D643" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E643" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B644" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C644" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D644" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E644" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B645" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C645" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D645" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E645" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B646" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C646" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D646" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E646" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B647" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C647" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D647" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E647" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B648" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C648" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D648" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E648" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B649" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C649" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D649" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E649" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B650" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C650" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D650" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E650" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B651" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C651" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D651" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E651" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B652" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C652" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D652" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E652" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B653" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C653" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D653" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E653" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B654" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C654" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D654" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E654" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B655" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C655" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D655" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E655" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B656" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C656" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D656" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E656" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B657" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C657" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D657" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E657" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B658" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C658" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D658" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E658" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B659" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C659" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D659" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E659" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B660" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C660" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D660" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E660" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B661" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C661" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D661" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E661" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B662" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C662" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D662" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E662" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B663" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C663" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D663" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E663" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B664" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C664" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D664" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E664" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW ремкомплект dq200</t>
+        </is>
+      </c>
+      <c r="B665" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C665" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D665" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E665" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E536"/>
+  <autoFilter ref="A1:E665"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$665</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$672</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E665"/>
+  <dimension ref="A1:E672"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17706,8 +17706,183 @@
         </is>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG6 DQ250 02E305045</t>
+        </is>
+      </c>
+      <c r="B666" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq250</t>
+        </is>
+      </c>
+      <c r="C666" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D666" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E666" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG6 DQ250 02E305045</t>
+        </is>
+      </c>
+      <c r="B667" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq250 алюминиевый</t>
+        </is>
+      </c>
+      <c r="C667" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D667" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E667" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра 02E305045 DSG6 DQ250+фильтр 02e305051C</t>
+        </is>
+      </c>
+      <c r="B668" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq250</t>
+        </is>
+      </c>
+      <c r="C668" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D668" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E668" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра 02E305045 DSG6 DQ250+фильтр 02e305051C</t>
+        </is>
+      </c>
+      <c r="B669" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq250 алюминиевый</t>
+        </is>
+      </c>
+      <c r="C669" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D669" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E669" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B670" s="3" t="inlineStr">
+        <is>
+          <t>валы и шестерни кпп ямз 238вм</t>
+        </is>
+      </c>
+      <c r="C670" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D670" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E670" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B671" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq500</t>
+        </is>
+      </c>
+      <c r="C671" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D671" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E671" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+      <c r="B672" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра шкода кодиак коробка dq500</t>
+        </is>
+      </c>
+      <c r="C672" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D672" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E672" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E665"/>
+  <autoFilter ref="A1:E672"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$672</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$752</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E672"/>
+  <dimension ref="A1:E752"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17881,8 +17881,2008 @@
         </is>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B673" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C673" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D673" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E673" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B674" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C674" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D674" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E674" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B675" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C675" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D675" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E675" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B676" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C676" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D676" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E676" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B677" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C677" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D677" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E677" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B678" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C678" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D678" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E678" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B679" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C679" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D679" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E679" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B680" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C680" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D680" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E680" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B681" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C681" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D681" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E681" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B682" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C682" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D682" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E682" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B683" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C683" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D683" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E683" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B684" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C684" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D684" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E684" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B685" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C685" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D685" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E685" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B686" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C686" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D686" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E686" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B687" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C687" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D687" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E687" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B688" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C688" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D688" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E688" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B689" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C689" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D689" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E689" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B690" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C690" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D690" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E690" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B691" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C691" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D691" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E691" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B692" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C692" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D692" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E692" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B693" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C693" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D693" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E693" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B694" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C694" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D694" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E694" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B695" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C695" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D695" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E695" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B696" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C696" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D696" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E696" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B697" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C697" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D697" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E697" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B698" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C698" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D698" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E698" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B699" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C699" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D699" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E699" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B700" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C700" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D700" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E700" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B701" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C701" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D701" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E701" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B702" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C702" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D702" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E702" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B703" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C703" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D703" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E703" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B704" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C704" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D704" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E704" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B705" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C705" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D705" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E705" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B706" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C706" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D706" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E706" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B707" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C707" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D707" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E707" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B708" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C708" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D708" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E708" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B709" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C709" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D709" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E709" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B710" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C710" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D710" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E710" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B711" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C711" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D711" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E711" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B712" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C712" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D712" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E712" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B713" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C713" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D713" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E713" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B714" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C714" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D714" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E714" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B715" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C715" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D715" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E715" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B716" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C716" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D716" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E716" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B717" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C717" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D717" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E717" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B718" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C718" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D718" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E718" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B719" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C719" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D719" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E719" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B720" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C720" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D720" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E720" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B721" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C721" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D721" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E721" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="3" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением ремкомплект dq200 прокладки dq200</t>
+        </is>
+      </c>
+      <c r="B722" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C722" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D722" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E722" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B723" s="3" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
+      <c r="C723" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="D723" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E723" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B724" s="3" t="inlineStr">
+        <is>
+          <t>штоки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C724" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="D724" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E724" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B725" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200</t>
+        </is>
+      </c>
+      <c r="C725" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D725" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E725" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B726" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков dq200</t>
+        </is>
+      </c>
+      <c r="C726" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D726" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E726" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B727" s="3" t="inlineStr">
+        <is>
+          <t>пыльники штоков dq200</t>
+        </is>
+      </c>
+      <c r="C727" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D727" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E727" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B728" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C728" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D728" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E728" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B729" s="3" t="inlineStr">
+        <is>
+          <t>штоки вилок dq200</t>
+        </is>
+      </c>
+      <c r="C729" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D729" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E729" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B730" s="3" t="inlineStr">
+        <is>
+          <t>длина штоков dq200</t>
+        </is>
+      </c>
+      <c r="C730" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D730" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E730" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B731" s="3" t="inlineStr">
+        <is>
+          <t>замена штока мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C731" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D731" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E731" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B732" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C732" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D732" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E732" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B733" s="3" t="inlineStr">
+        <is>
+          <t>штоки переключения передач dq200</t>
+        </is>
+      </c>
+      <c r="C733" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D733" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E733" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B734" s="3" t="inlineStr">
+        <is>
+          <t>dq200 замена штоков сцепления</t>
+        </is>
+      </c>
+      <c r="C734" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D734" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E734" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B735" s="3" t="inlineStr">
+        <is>
+          <t>какие стоят штоки сцепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C735" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D735" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E735" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B736" s="3" t="inlineStr">
+        <is>
+          <t>стакан штока dq200</t>
+        </is>
+      </c>
+      <c r="C736" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D736" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E736" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="3" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B737" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200 отличия с 2012 года</t>
+        </is>
+      </c>
+      <c r="C737" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D737" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E737" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B738" s="3" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
+      <c r="C738" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="D738" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E738" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B739" s="3" t="inlineStr">
+        <is>
+          <t>штоки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C739" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="D739" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E739" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B740" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200</t>
+        </is>
+      </c>
+      <c r="C740" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D740" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E740" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B741" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков dq200</t>
+        </is>
+      </c>
+      <c r="C741" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D741" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E741" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B742" s="3" t="inlineStr">
+        <is>
+          <t>пыльники штоков dq200</t>
+        </is>
+      </c>
+      <c r="C742" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D742" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E742" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B743" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C743" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D743" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E743" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B744" s="3" t="inlineStr">
+        <is>
+          <t>штоки вилок dq200</t>
+        </is>
+      </c>
+      <c r="C744" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D744" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E744" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B745" s="3" t="inlineStr">
+        <is>
+          <t>длина штоков dq200</t>
+        </is>
+      </c>
+      <c r="C745" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D745" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E745" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B746" s="3" t="inlineStr">
+        <is>
+          <t>замена штока мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C746" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D746" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E746" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B747" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C747" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D747" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E747" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B748" s="3" t="inlineStr">
+        <is>
+          <t>штоки переключения передач dq200</t>
+        </is>
+      </c>
+      <c r="C748" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D748" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E748" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B749" s="3" t="inlineStr">
+        <is>
+          <t>dq200 замена штоков сцепления</t>
+        </is>
+      </c>
+      <c r="C749" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D749" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E749" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B750" s="3" t="inlineStr">
+        <is>
+          <t>какие стоят штоки сцепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C750" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D750" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E750" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B751" s="3" t="inlineStr">
+        <is>
+          <t>стакан штока dq200</t>
+        </is>
+      </c>
+      <c r="C751" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D751" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E751" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="3" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B752" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200 отличия с 2012 года</t>
+        </is>
+      </c>
+      <c r="C752" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D752" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E752" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E672"/>
+  <autoFilter ref="A1:E752"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$752</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$902</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E752"/>
+  <dimension ref="A1:E902"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19881,8 +19881,3758 @@
         </is>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B753" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C753" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D753" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E753" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B754" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C754" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D754" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E754" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B755" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C755" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D755" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E755" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B756" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C756" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D756" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E756" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B757" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C757" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D757" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E757" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B758" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C758" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D758" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E758" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B759" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C759" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D759" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E759" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B760" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C760" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D760" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E760" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B761" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C761" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D761" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E761" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B762" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C762" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D762" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E762" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B763" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C763" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D763" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E763" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B764" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C764" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D764" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E764" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B765" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C765" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D765" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E765" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B766" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C766" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D766" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E766" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B767" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C767" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D767" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E767" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B768" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C768" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D768" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E768" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B769" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C769" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D769" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E769" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B770" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C770" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D770" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E770" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B771" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C771" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D771" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E771" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B772" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C772" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D772" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E772" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B773" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C773" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D773" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E773" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B774" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C774" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D774" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E774" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B775" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C775" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D775" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E775" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B776" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C776" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D776" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E776" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B777" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C777" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D777" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E777" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B778" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C778" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D778" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E778" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B779" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C779" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D779" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E779" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B780" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C780" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D780" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E780" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B781" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C781" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D781" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E781" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B782" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C782" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D782" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E782" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B783" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C783" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D783" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E783" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B784" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C784" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D784" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E784" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B785" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C785" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D785" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E785" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B786" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C786" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D786" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E786" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B787" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C787" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D787" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E787" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B788" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C788" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D788" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E788" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B789" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C789" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D789" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E789" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B790" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C790" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D790" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E790" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B791" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C791" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D791" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E791" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B792" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C792" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D792" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E792" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B793" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C793" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D793" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E793" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B794" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C794" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D794" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E794" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B795" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C795" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D795" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E795" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B796" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C796" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D796" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E796" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B797" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C797" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D797" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E797" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B798" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C798" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D798" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E798" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B799" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C799" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D799" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E799" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B800" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C800" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D800" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E800" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B801" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C801" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D801" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E801" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="3" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B802" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C802" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D802" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E802" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B803" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C803" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D803" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E803" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B804" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C804" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D804" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E804" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B805" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C805" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D805" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E805" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B806" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C806" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D806" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E806" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B807" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C807" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D807" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E807" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B808" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C808" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D808" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E808" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B809" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C809" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D809" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E809" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B810" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C810" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D810" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E810" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B811" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C811" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D811" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E811" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C812" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D812" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E812" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B813" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C813" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D813" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E813" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B814" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C814" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D814" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E814" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B815" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C815" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D815" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E815" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B816" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C816" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D816" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E816" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B817" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C817" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D817" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E817" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B818" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C818" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D818" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E818" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B819" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C819" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D819" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E819" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B820" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C820" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D820" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E820" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B821" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C821" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D821" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E821" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B822" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C822" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D822" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E822" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B823" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C823" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D823" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E823" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B824" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C824" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D824" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E824" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B825" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C825" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D825" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E825" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B826" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C826" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D826" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E826" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B827" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C827" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D827" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E827" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B828" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C828" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D828" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E828" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B829" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C829" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D829" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E829" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B830" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C830" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D830" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E830" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B831" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C831" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D831" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E831" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B832" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C832" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D832" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E832" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B833" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C833" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D833" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E833" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C834" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D834" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E834" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B835" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C835" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D835" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E835" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B836" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C836" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D836" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E836" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B837" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C837" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D837" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E837" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B838" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C838" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D838" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E838" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B839" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C839" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D839" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E839" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B840" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C840" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D840" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E840" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B841" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C841" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D841" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E841" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B842" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C842" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D842" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E842" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B843" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C843" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D843" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E843" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B844" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C844" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D844" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E844" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B845" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C845" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D845" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E845" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B846" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C846" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D846" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E846" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B847" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C847" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D847" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E847" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B848" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C848" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D848" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E848" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B849" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C849" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D849" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E849" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C850" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D850" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E850" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B851" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C851" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D851" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E851" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="B852" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C852" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D852" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E852" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B853" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C853" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D853" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E853" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B854" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C854" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D854" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E854" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B855" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C855" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D855" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E855" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B856" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C856" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D856" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E856" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B857" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C857" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D857" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E857" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B858" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C858" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D858" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E858" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B859" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C859" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D859" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E859" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B860" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C860" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D860" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E860" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B861" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C861" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D861" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E861" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B862" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C862" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D862" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E862" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B863" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C863" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D863" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E863" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B864" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C864" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D864" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E864" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B865" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C865" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D865" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E865" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B866" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C866" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D866" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E866" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B867" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C867" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D867" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E867" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B868" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C868" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D868" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E868" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B869" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C869" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D869" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E869" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C870" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D870" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E870" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B871" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C871" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D871" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E871" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C872" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D872" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E872" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B873" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C873" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D873" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E873" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B874" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C874" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D874" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E874" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B875" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C875" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D875" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E875" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B876" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C876" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D876" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E876" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B877" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C877" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D877" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E877" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B878" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C878" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D878" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E878" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B879" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C879" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D879" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E879" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B880" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C880" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D880" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E880" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B881" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C881" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D881" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E881" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C882" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D882" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E882" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B883" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C883" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D883" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E883" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B884" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C884" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D884" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E884" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B885" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C885" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D885" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E885" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B886" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C886" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D886" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E886" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B887" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C887" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D887" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E887" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B888" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C888" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D888" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E888" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B889" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C889" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D889" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E889" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B890" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C890" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D890" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E890" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B891" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C891" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D891" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E891" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B892" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C892" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D892" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E892" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B893" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C893" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D893" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E893" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B894" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C894" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D894" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E894" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B895" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C895" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D895" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E895" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B896" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C896" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D896" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E896" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B897" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C897" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D897" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E897" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B898" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C898" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D898" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E898" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B899" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C899" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D899" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E899" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B900" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C900" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D900" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E900" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B901" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C901" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D901" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E901" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="3" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B902" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C902" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D902" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E902" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E752"/>
+  <autoFilter ref="A1:E902"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$902</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$936</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E902"/>
+  <dimension ref="A1:E936"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -23631,8 +23631,858 @@
         </is>
       </c>
     </row>
+    <row r="903">
+      <c r="A903" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.6 л</t>
+        </is>
+      </c>
+      <c r="B903" s="3" t="inlineStr">
+        <is>
+          <t>jf015e гидроблок</t>
+        </is>
+      </c>
+      <c r="C903" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="D903" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E903" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.6 л</t>
+        </is>
+      </c>
+      <c r="B904" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок вариатора jf015e</t>
+        </is>
+      </c>
+      <c r="C904" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D904" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E904" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.6 л</t>
+        </is>
+      </c>
+      <c r="B905" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок jf015e купить</t>
+        </is>
+      </c>
+      <c r="C905" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D905" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E905" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.6 л</t>
+        </is>
+      </c>
+      <c r="B906" s="3" t="inlineStr">
+        <is>
+          <t>схема гидроблока jf015e</t>
+        </is>
+      </c>
+      <c r="C906" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D906" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E906" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.6 л</t>
+        </is>
+      </c>
+      <c r="B907" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок вариатора ниссан jf015e</t>
+        </is>
+      </c>
+      <c r="C907" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D907" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E907" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.6 л</t>
+        </is>
+      </c>
+      <c r="B908" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок jf015e на 4 соленоидов</t>
+        </is>
+      </c>
+      <c r="C908" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D908" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E908" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.6 л</t>
+        </is>
+      </c>
+      <c r="B909" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок jf015e на 5 соленоидов</t>
+        </is>
+      </c>
+      <c r="C909" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D909" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E909" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.6 л</t>
+        </is>
+      </c>
+      <c r="B910" s="3" t="inlineStr">
+        <is>
+          <t>модификации гидроблоков jf015e</t>
+        </is>
+      </c>
+      <c r="C910" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D910" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E910" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.8 л</t>
+        </is>
+      </c>
+      <c r="B911" s="3" t="inlineStr">
+        <is>
+          <t>jf015e гидроблок</t>
+        </is>
+      </c>
+      <c r="C911" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="D911" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E911" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.8 л</t>
+        </is>
+      </c>
+      <c r="B912" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок вариатора jf015e</t>
+        </is>
+      </c>
+      <c r="C912" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D912" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E912" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.8 л</t>
+        </is>
+      </c>
+      <c r="B913" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок jf015e купить</t>
+        </is>
+      </c>
+      <c r="C913" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D913" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E913" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.8 л</t>
+        </is>
+      </c>
+      <c r="B914" s="3" t="inlineStr">
+        <is>
+          <t>схема гидроблока jf015e</t>
+        </is>
+      </c>
+      <c r="C914" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D914" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E914" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.8 л</t>
+        </is>
+      </c>
+      <c r="B915" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок вариатора ниссан jf015e</t>
+        </is>
+      </c>
+      <c r="C915" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D915" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E915" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.8 л</t>
+        </is>
+      </c>
+      <c r="B916" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок jf015e на 4 соленоидов</t>
+        </is>
+      </c>
+      <c r="C916" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D916" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E916" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.8 л</t>
+        </is>
+      </c>
+      <c r="B917" s="3" t="inlineStr">
+        <is>
+          <t>гидроблок jf015e на 5 соленоидов</t>
+        </is>
+      </c>
+      <c r="C917" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D917" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E917" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="3" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.8 л</t>
+        </is>
+      </c>
+      <c r="B918" s="3" t="inlineStr">
+        <is>
+          <t>модификации гидроблоков jf015e</t>
+        </is>
+      </c>
+      <c r="C918" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D918" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E918" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B919" s="3" t="inlineStr">
+        <is>
+          <t>сапун редуктора</t>
+        </is>
+      </c>
+      <c r="C919" s="3" t="n">
+        <v>6071</v>
+      </c>
+      <c r="D919" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E919" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B920" s="3" t="inlineStr">
+        <is>
+          <t>втулка скольжения с фланцем</t>
+        </is>
+      </c>
+      <c r="C920" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="D920" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E920" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B921" s="3" t="inlineStr">
+        <is>
+          <t>сальник dq200</t>
+        </is>
+      </c>
+      <c r="C921" s="3" t="n">
+        <v>347</v>
+      </c>
+      <c r="D921" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E921" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B922" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника dq200</t>
+        </is>
+      </c>
+      <c r="C922" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D922" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E922" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B923" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников dq200</t>
+        </is>
+      </c>
+      <c r="C923" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D923" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E923" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B924" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C924" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D924" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E924" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B925" s="3" t="inlineStr">
+        <is>
+          <t>сальник привода dq200</t>
+        </is>
+      </c>
+      <c r="C925" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D925" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E925" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B926" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C926" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D926" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E926" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B927" s="3" t="inlineStr">
+        <is>
+          <t>сальники dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C927" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D927" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E927" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B928" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C928" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D928" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E928" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B929" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C929" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D929" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E929" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B930" s="3" t="inlineStr">
+        <is>
+          <t>сальник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C930" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D930" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E930" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B931" s="3" t="inlineStr">
+        <is>
+          <t>замена правого сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C931" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D931" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E931" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B932" s="3" t="inlineStr">
+        <is>
+          <t>съемник сальника dq200</t>
+        </is>
+      </c>
+      <c r="C932" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D932" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E932" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B933" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C933" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D933" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E933" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B934" s="3" t="inlineStr">
+        <is>
+          <t>сальник кпп первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C934" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D934" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E934" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B935" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала внутренний и наружный dq200</t>
+        </is>
+      </c>
+      <c r="C935" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D935" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E935" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+      <c r="B936" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C936" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D936" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E936" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E902"/>
+  <autoFilter ref="A1:E936"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$936</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1015</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E936"/>
+  <dimension ref="A1:E1015"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -24481,8 +24481,1983 @@
         </is>
       </c>
     </row>
+    <row r="937">
+      <c r="A937" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B937" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C937" s="3" t="n">
+        <v>568</v>
+      </c>
+      <c r="D937" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E937" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B938" s="3" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C938" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="D938" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E938" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B939" s="3" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C939" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="D939" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E939" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B940" s="3" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C940" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D940" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E940" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B941" s="3" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C941" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D941" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E941" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B942" s="3" t="inlineStr">
+        <is>
+          <t>замена крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C942" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D942" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E942" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B943" s="3" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C943" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D943" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E943" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B944" s="3" t="inlineStr">
+        <is>
+          <t>тверь крышка мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C944" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D944" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E944" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B945" s="3" t="inlineStr">
+        <is>
+          <t>крышка сапуна мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C945" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D945" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E945" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B946" s="3" t="inlineStr">
+        <is>
+          <t>замена прокладки крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C946" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D946" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E946" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+      <c r="B947" s="3" t="inlineStr">
+        <is>
+          <t>степень затяжки болтов крышки мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C947" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D947" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E947" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B948" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C948" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D948" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E948" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B949" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C949" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D949" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E949" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B950" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C950" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D950" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E950" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B951" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C951" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D951" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E951" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B952" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C952" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D952" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E952" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B953" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C953" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D953" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E953" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B954" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C954" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D954" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E954" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B955" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C955" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D955" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E955" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B956" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C956" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D956" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E956" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B957" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C957" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D957" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E957" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B958" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C958" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D958" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E958" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B959" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C959" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D959" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E959" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B960" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C960" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D960" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E960" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B961" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C961" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D961" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E961" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B962" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C962" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D962" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E962" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B963" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C963" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D963" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E963" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B964" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C964" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D964" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E964" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B965" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C965" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D965" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E965" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B966" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C966" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D966" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E966" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B967" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C967" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D967" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E967" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B968" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C968" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D968" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E968" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B969" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C969" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D969" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E969" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B970" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C970" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D970" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E970" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B971" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C971" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D971" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E971" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B972" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C972" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D972" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E972" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B973" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C973" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D973" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E973" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B974" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C974" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D974" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E974" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B975" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C975" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D975" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E975" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B976" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C976" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D976" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E976" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B977" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C977" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D977" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E977" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B978" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C978" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D978" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E978" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B979" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C979" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D979" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E979" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B980" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C980" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D980" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E980" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B981" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C981" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D981" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E981" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B982" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C982" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D982" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E982" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B983" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C983" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D983" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E983" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B984" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C984" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D984" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E984" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B985" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C985" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D985" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E985" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B986" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C986" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D986" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E986" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B987" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C987" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D987" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E987" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B988" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C988" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D988" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E988" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B989" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C989" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D989" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E989" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B990" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C990" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D990" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E990" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B991" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C991" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D991" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E991" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B992" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C992" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D992" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E992" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B993" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C993" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D993" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E993" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B994" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C994" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D994" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E994" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B995" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C995" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D995" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E995" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B996" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C996" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D996" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E996" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B997" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C997" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D997" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E997" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B998" s="3" t="inlineStr">
+        <is>
+          <t>сапун редуктора</t>
+        </is>
+      </c>
+      <c r="C998" s="3" t="n">
+        <v>6071</v>
+      </c>
+      <c r="D998" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E998" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B999" s="3" t="inlineStr">
+        <is>
+          <t>втулка скольжения с фланцем</t>
+        </is>
+      </c>
+      <c r="C999" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="D999" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E999" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1000" s="3" t="inlineStr">
+        <is>
+          <t>сальник dq200</t>
+        </is>
+      </c>
+      <c r="C1000" s="3" t="n">
+        <v>347</v>
+      </c>
+      <c r="D1000" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1000" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1001" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника dq200</t>
+        </is>
+      </c>
+      <c r="C1001" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1001" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1001" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1002" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников dq200</t>
+        </is>
+      </c>
+      <c r="C1002" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1002" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1002" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1003" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1003" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1003" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1003" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1004" s="3" t="inlineStr">
+        <is>
+          <t>сальник привода dq200</t>
+        </is>
+      </c>
+      <c r="C1004" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D1004" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1004" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1005" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C1005" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1005" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1005" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1006" s="3" t="inlineStr">
+        <is>
+          <t>сальники dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1006" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1006" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1006" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1007" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1007" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1007" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1007" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1008" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1008" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1008" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1008" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1009" s="3" t="inlineStr">
+        <is>
+          <t>сальник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1009" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1009" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1009" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1010" s="3" t="inlineStr">
+        <is>
+          <t>замена правого сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C1010" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1010" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1010" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1011" s="3" t="inlineStr">
+        <is>
+          <t>съемник сальника dq200</t>
+        </is>
+      </c>
+      <c r="C1011" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1011" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1011" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1012" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1012" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1012" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1012" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1013" s="3" t="inlineStr">
+        <is>
+          <t>сальник кпп первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1013" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1013" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1013" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1014" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала внутренний и наружный dq200</t>
+        </is>
+      </c>
+      <c r="C1014" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1014" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1014" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+      <c r="B1015" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1015" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1015" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1015" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E936"/>
+  <autoFilter ref="A1:E1015"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1015</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1105</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1015"/>
+  <dimension ref="A1:E1105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -26456,8 +26456,2258 @@
         </is>
       </c>
     </row>
+    <row r="1016">
+      <c r="A1016" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1016" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200</t>
+        </is>
+      </c>
+      <c r="C1016" s="3" t="n">
+        <v>613</v>
+      </c>
+      <c r="D1016" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1016" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1017" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 гидроаккумулятор</t>
+        </is>
+      </c>
+      <c r="C1017" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D1017" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1017" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1018" s="3" t="inlineStr">
+        <is>
+          <t>давление в гидроаккумуляторе dq200</t>
+        </is>
+      </c>
+      <c r="C1018" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1018" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1018" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1019" s="3" t="inlineStr">
+        <is>
+          <t>замена гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1019" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1019" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1019" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1020" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1020" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D1020" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1020" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1021" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1021" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D1021" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1021" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1022" s="3" t="inlineStr">
+        <is>
+          <t>как проверить гидроаккумулятор dq200</t>
+        </is>
+      </c>
+      <c r="C1022" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1022" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1022" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1023" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1023" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D1023" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1023" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1024" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор faw на dq200</t>
+        </is>
+      </c>
+      <c r="C1024" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1024" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1024" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1025" s="3" t="inlineStr">
+        <is>
+          <t>как снять гидроаккумулятор dq200</t>
+        </is>
+      </c>
+      <c r="C1025" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1025" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1025" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1026" s="3" t="inlineStr">
+        <is>
+          <t>взрыв гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1026" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1026" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1026" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1027" s="3" t="inlineStr">
+        <is>
+          <t>снятие гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1027" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1027" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1027" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1028" s="3" t="inlineStr">
+        <is>
+          <t>момент затяжки гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1028" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1028" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1028" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1029" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 давление в гидроаккумуляторе быстро падает</t>
+        </is>
+      </c>
+      <c r="C1029" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1029" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1029" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1030" s="3" t="inlineStr">
+        <is>
+          <t>размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200</t>
+        </is>
+      </c>
+      <c r="C1030" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1030" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1030" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1031" s="3" t="inlineStr">
+        <is>
+          <t>как стравить давление в гидроаккумуляторе dq200</t>
+        </is>
+      </c>
+      <c r="C1031" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1031" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1031" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1032" s="3" t="inlineStr">
+        <is>
+          <t>проверка гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1032" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1032" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1032" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1033" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор на dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1033" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1033" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1033" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1034" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200 ремонтный московское ш 13</t>
+        </is>
+      </c>
+      <c r="C1034" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1034" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1034" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1035" s="3" t="inlineStr">
+        <is>
+          <t>оригинальный гидроаккумулятор на dq200 кто производит faw</t>
+        </is>
+      </c>
+      <c r="C1035" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1035" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1035" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1036" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор на dq200 fte automotive</t>
+        </is>
+      </c>
+      <c r="C1036" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1036" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1036" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="3" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1037" s="3" t="inlineStr">
+        <is>
+          <t>как сбросить давление с гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1037" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1037" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1037" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1038" s="3" t="inlineStr">
+        <is>
+          <t>сапун редуктора</t>
+        </is>
+      </c>
+      <c r="C1038" s="3" t="n">
+        <v>6071</v>
+      </c>
+      <c r="D1038" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1038" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1039" s="3" t="inlineStr">
+        <is>
+          <t>втулка скольжения с фланцем</t>
+        </is>
+      </c>
+      <c r="C1039" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="D1039" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1039" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1040" s="3" t="inlineStr">
+        <is>
+          <t>сальник dq200</t>
+        </is>
+      </c>
+      <c r="C1040" s="3" t="n">
+        <v>347</v>
+      </c>
+      <c r="D1040" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1040" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1041" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника dq200</t>
+        </is>
+      </c>
+      <c r="C1041" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1041" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1041" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1042" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников dq200</t>
+        </is>
+      </c>
+      <c r="C1042" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1042" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1042" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1043" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1043" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1043" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1043" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1044" s="3" t="inlineStr">
+        <is>
+          <t>сальник привода dq200</t>
+        </is>
+      </c>
+      <c r="C1044" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D1044" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1044" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1045" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C1045" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1045" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1045" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1046" s="3" t="inlineStr">
+        <is>
+          <t>сальники dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1046" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1046" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1046" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1047" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1047" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1047" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1047" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1048" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1048" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1048" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1048" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1049" s="3" t="inlineStr">
+        <is>
+          <t>сальник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1049" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1049" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1049" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1050" s="3" t="inlineStr">
+        <is>
+          <t>замена правого сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C1050" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1050" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1050" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1051" s="3" t="inlineStr">
+        <is>
+          <t>съемник сальника dq200</t>
+        </is>
+      </c>
+      <c r="C1051" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1051" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1051" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1052" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1052" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1052" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1052" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1053" s="3" t="inlineStr">
+        <is>
+          <t>сальник кпп первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1053" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1053" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1053" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1054" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала внутренний и наружный dq200</t>
+        </is>
+      </c>
+      <c r="C1054" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1054" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1054" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+      <c r="B1055" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1055" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1055" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1055" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1056" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1056" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1056" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1056" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1057" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1057" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1057" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1057" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1058" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1058" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1058" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1058" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1059" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1059" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1059" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1059" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1060" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1060" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1060" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1060" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1061" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1061" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1061" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1061" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1062" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1062" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1062" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1062" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1063" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1063" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1063" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1063" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1064" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1064" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1064" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1064" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1065" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1065" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1065" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1065" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1066" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1066" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1066" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1066" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1067" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1067" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1067" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1067" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1068" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1068" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1068" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1068" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1069" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1069" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1069" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1069" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1070" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1070" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1070" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1070" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1071" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1071" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1071" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1071" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1072" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1072" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1072" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1072" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1073" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1073" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1073" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1073" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1074" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1074" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1074" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1074" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1075" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1075" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1075" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1075" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1076" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1076" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1076" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1076" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1077" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1077" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1077" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1077" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1078" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1078" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1078" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1078" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1079" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1079" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1079" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1079" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1080" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1080" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1080" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1080" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1081" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1081" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1081" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1081" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1082" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1082" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1082" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1082" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1083" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1083" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1083" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1083" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1084" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1084" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1084" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1084" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1085" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1085" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1085" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1085" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1086" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1086" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1086" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1086" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1087" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1087" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1087" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1087" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1088" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1088" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1088" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1088" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1089" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1089" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1089" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1089" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1090" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1090" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1090" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1090" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1091" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1091" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1091" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1091" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1092" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1092" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1092" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1092" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1093" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1093" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1093" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1093" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1094" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1094" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1094" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1094" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1095" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1095" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1095" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1095" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1096" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1096" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1096" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1096" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1097" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1097" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1097" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1097" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1098" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1098" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1098" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1098" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1099" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1099" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1099" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1099" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1100" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1100" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1100" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1100" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1101" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1101" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1101" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1101" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1102" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1102" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1102" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1102" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1103" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1103" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1103" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1103" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1104" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1104" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1104" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1104" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="3" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1105" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1105" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1105" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1105" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1015"/>
+  <autoFilter ref="A1:E1105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1207</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1105"/>
+  <dimension ref="A1:E1207"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28706,8 +28706,2558 @@
         </is>
       </c>
     </row>
+    <row r="1106">
+      <c r="A1106" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DQ250 02E</t>
+        </is>
+      </c>
+      <c r="B1106" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq250</t>
+        </is>
+      </c>
+      <c r="C1106" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1106" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1106" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="3" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DQ250 02E</t>
+        </is>
+      </c>
+      <c r="B1107" s="3" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq250 алюминиевый</t>
+        </is>
+      </c>
+      <c r="C1107" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1107" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1107" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1108" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1108" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1108" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1108" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1109" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1109" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1109" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1109" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1110" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1110" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1110" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1110" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1111" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1111" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1111" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1111" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1112" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1112" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1112" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1112" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1113" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1113" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1113" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1113" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1114" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1114" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1114" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1114" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1115" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1115" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1115" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1115" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1116" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1116" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1116" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1116" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1117" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1117" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1117" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1117" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1118" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1118" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1118" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1118" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1119" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1119" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1119" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1119" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1120" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1120" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1120" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1120" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1121" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1121" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1121" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1121" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1122" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1122" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1122" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1122" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1123" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1123" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1123" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1123" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1124" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1124" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1124" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1124" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1125" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1125" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1125" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1125" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1126" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1126" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1126" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1126" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1127" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1127" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1127" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1127" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1128" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1128" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1128" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1128" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1129" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1129" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1129" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1129" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1130" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1130" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1130" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1130" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1131" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1131" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1131" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1131" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1132" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1132" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1132" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1132" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1133" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1133" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1133" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1133" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1134" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1134" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1134" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1134" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1135" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1135" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1135" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1135" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1136" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1136" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1136" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1136" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1137" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1137" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1137" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1137" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1138" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1138" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1138" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1138" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1139" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1139" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1139" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1139" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1140" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1140" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1140" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1140" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1141" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1141" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1141" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1141" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1142" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1142" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1142" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1142" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1143" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1143" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1143" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1143" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1144" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1144" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1144" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1144" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1145" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1145" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1145" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1145" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1146" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1146" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1146" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1146" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1147" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1147" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1147" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1147" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1148" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1148" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1148" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1148" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1149" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1149" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1149" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1149" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1150" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1150" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1150" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1150" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1151" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1151" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1151" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1151" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1152" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1152" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1152" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1152" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1153" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1153" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1153" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1153" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1154" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1154" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1154" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1154" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1155" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1155" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1155" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1155" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1156" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1156" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1156" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1156" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1157" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1157" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1157" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1157" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1158" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1158" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1158" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1158" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1159" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1159" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1159" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1159" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1160" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1160" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1160" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1160" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1161" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1161" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1161" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1161" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1162" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1162" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1162" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1162" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1163" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1163" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1163" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1163" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1164" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1164" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1164" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1164" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1165" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1165" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1165" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1165" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1166" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1166" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1166" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1166" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1167" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1167" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1167" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1167" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1168" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1168" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1168" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1168" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1169" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1169" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1169" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1169" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1170" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1170" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1170" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1170" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1171" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1171" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1171" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1171" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1172" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1172" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1172" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1172" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1173" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1173" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1173" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1173" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1174" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1174" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1174" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1174" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1175" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1175" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1175" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1175" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1176" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1176" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1176" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1176" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1177" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1177" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1177" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1177" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1178" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1178" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1178" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1178" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1179" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1179" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1179" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1179" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1180" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1180" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1180" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1180" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1181" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1181" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1181" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1181" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1182" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1182" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1182" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1182" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1183" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1183" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1183" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1183" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1184" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1184" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1184" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1184" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1185" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1185" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1185" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1185" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1186" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1186" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1186" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1186" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1187" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1187" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1187" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1187" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1188" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1188" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1188" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1188" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1189" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1189" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1189" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1189" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1190" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1190" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1190" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1190" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1191" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1191" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1191" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1191" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1192" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1192" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1192" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1192" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1193" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1193" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1193" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1193" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1194" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1194" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1194" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1194" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1195" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1195" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1195" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1195" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1196" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1196" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1196" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1196" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1197" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1197" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1197" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1197" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1198" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1198" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1198" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1198" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1199" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1199" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1199" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1199" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1200" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1200" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1200" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1200" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1201" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1201" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1201" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1201" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1202" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1202" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1202" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1202" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1203" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1203" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1203" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1203" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1204" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1204" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1204" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1204" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1205" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1205" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1205" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1205" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1206" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1206" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1206" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1206" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1207" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1207" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1207" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1207" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1105"/>
+  <autoFilter ref="A1:E1207"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1290</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1207"/>
+  <dimension ref="A1:E1290"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -31256,8 +31256,2083 @@
         </is>
       </c>
     </row>
+    <row r="1208">
+      <c r="A1208" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1208" s="3" t="inlineStr">
+        <is>
+          <t>сапун редуктора</t>
+        </is>
+      </c>
+      <c r="C1208" s="3" t="n">
+        <v>6071</v>
+      </c>
+      <c r="D1208" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1208" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1209" s="3" t="inlineStr">
+        <is>
+          <t>втулка скольжения с фланцем</t>
+        </is>
+      </c>
+      <c r="C1209" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="D1209" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1209" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1210" s="3" t="inlineStr">
+        <is>
+          <t>сальник dq200</t>
+        </is>
+      </c>
+      <c r="C1210" s="3" t="n">
+        <v>347</v>
+      </c>
+      <c r="D1210" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1210" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1211" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника dq200</t>
+        </is>
+      </c>
+      <c r="C1211" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1211" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1211" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1212" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников dq200</t>
+        </is>
+      </c>
+      <c r="C1212" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1212" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1212" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1213" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1213" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1213" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1213" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1214" s="3" t="inlineStr">
+        <is>
+          <t>сальник привода dq200</t>
+        </is>
+      </c>
+      <c r="C1214" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D1214" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1214" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1215" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C1215" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1215" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1215" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1216" s="3" t="inlineStr">
+        <is>
+          <t>сальники dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1216" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1216" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1216" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1217" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1217" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1217" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1217" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1218" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1218" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1218" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1218" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1219" s="3" t="inlineStr">
+        <is>
+          <t>сальник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1219" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1219" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1219" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1220" s="3" t="inlineStr">
+        <is>
+          <t>замена правого сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C1220" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1220" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1220" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1221" s="3" t="inlineStr">
+        <is>
+          <t>съемник сальника dq200</t>
+        </is>
+      </c>
+      <c r="C1221" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1221" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1221" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1222" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1222" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1222" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1222" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1223" s="3" t="inlineStr">
+        <is>
+          <t>сальник кпп первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1223" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1223" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1223" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1224" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала внутренний и наружный dq200</t>
+        </is>
+      </c>
+      <c r="C1224" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1224" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1224" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+      <c r="B1225" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1225" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1225" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1225" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1226" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1226" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1226" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1226" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1227" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1227" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1228" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1228" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1228" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1229" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1229" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1229" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1230" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1230" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1230" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1230" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1231" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1231" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1231" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1231" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1232" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1232" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1232" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1232" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1233" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1233" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1233" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1233" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1234" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1234" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1234" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1234" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1235" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1235" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1235" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1235" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1236" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1236" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1236" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1236" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1237" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1237" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1237" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1237" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1238" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1238" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1238" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1238" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1239" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1239" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1239" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1239" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1240" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1240" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1240" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1240" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1241" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1241" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1241" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1241" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1242" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1242" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1242" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1242" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1243" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1243" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1243" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1243" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1244" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1244" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1244" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1244" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1245" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1245" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1245" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1245" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1246" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1246" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1246" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1246" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1247" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1247" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1247" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1247" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1248" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1248" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1248" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1248" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1249" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1249" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1249" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1249" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1250" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1250" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1250" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1250" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1251" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1251" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1251" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1251" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1252" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1252" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1252" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1252" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1253" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1253" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1253" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1253" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1254" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1254" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1254" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1254" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1255" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1255" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1255" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1255" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1256" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1256" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1256" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1256" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1257" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1257" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1257" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1257" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1258" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1258" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1258" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1258" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1259" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1259" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1259" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1259" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1260" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1260" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1260" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1260" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1261" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1261" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1261" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1261" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1262" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1262" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1262" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1262" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1263" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1263" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1263" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1263" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1264" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1264" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1264" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1264" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1265" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1265" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1265" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1265" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1266" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1266" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1266" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1266" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1267" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1267" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1267" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1267" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1268" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1268" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1268" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1268" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1269" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1269" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1269" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1269" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1270" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1270" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1270" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1270" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1271" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1271" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1271" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1271" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1272" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1272" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1272" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1272" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1273" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1273" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1273" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1273" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1274" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1274" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1274" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1274" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1275" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1275" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1275" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1275" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1276" s="3" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
+      <c r="C1276" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="D1276" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1276" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1277" s="3" t="inlineStr">
+        <is>
+          <t>штоки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1277" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="D1277" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1277" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1278" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200</t>
+        </is>
+      </c>
+      <c r="C1278" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D1278" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1278" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1279" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков dq200</t>
+        </is>
+      </c>
+      <c r="C1279" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1279" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1279" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1280" s="3" t="inlineStr">
+        <is>
+          <t>пыльники штоков dq200</t>
+        </is>
+      </c>
+      <c r="C1280" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D1280" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1280" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1281" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1281" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1281" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1281" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1282" s="3" t="inlineStr">
+        <is>
+          <t>штоки вилок dq200</t>
+        </is>
+      </c>
+      <c r="C1282" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1282" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1282" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1283" s="3" t="inlineStr">
+        <is>
+          <t>длина штоков dq200</t>
+        </is>
+      </c>
+      <c r="C1283" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1283" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1283" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1284" s="3" t="inlineStr">
+        <is>
+          <t>замена штока мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C1284" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1284" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1284" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1285" s="3" t="inlineStr">
+        <is>
+          <t>замена штоков мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1285" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1285" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1285" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1286" s="3" t="inlineStr">
+        <is>
+          <t>штоки переключения передач dq200</t>
+        </is>
+      </c>
+      <c r="C1286" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1286" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1286" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1287" s="3" t="inlineStr">
+        <is>
+          <t>dq200 замена штоков сцепления</t>
+        </is>
+      </c>
+      <c r="C1287" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1287" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1287" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1288" s="3" t="inlineStr">
+        <is>
+          <t>какие стоят штоки сцепления мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1288" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1288" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1288" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1289" s="3" t="inlineStr">
+        <is>
+          <t>стакан штока dq200</t>
+        </is>
+      </c>
+      <c r="C1289" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1289" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1289" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="3" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1290" s="3" t="inlineStr">
+        <is>
+          <t>штоки сцепления dq200 отличия с 2012 года</t>
+        </is>
+      </c>
+      <c r="C1290" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1290" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1290" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1207"/>
+  <autoFilter ref="A1:E1290"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1370</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1290"/>
+  <dimension ref="A1:E1370"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33331,8 +33331,2008 @@
         </is>
       </c>
     </row>
+    <row r="1291">
+      <c r="A1291" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1291" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1291" s="3" t="n">
+        <v>1289</v>
+      </c>
+      <c r="D1291" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1291" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1292" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C1292" s="3" t="n">
+        <v>590</v>
+      </c>
+      <c r="D1292" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1292" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1293" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1293" s="3" t="n">
+        <v>560</v>
+      </c>
+      <c r="D1293" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1293" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1294" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg dq250</t>
+        </is>
+      </c>
+      <c r="C1294" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D1294" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1294" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1295" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq250 купить</t>
+        </is>
+      </c>
+      <c r="C1295" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="D1295" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1295" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1296" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 6 dq250</t>
+        </is>
+      </c>
+      <c r="C1296" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D1296" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1296" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1297" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq250 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1297" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D1297" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1297" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1298" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 6 dq250 купить</t>
+        </is>
+      </c>
+      <c r="C1298" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D1298" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1298" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1299" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C1299" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1299" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1299" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1300" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C1300" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1300" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1300" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1301" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq250 цена</t>
+        </is>
+      </c>
+      <c r="C1301" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1301" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1301" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1302" s="3" t="inlineStr">
+        <is>
+          <t>плата в мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C1302" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1302" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1302" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1303" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 6 dq250</t>
+        </is>
+      </c>
+      <c r="C1303" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1303" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1303" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1304" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq250 мехатроник артикул</t>
+        </is>
+      </c>
+      <c r="C1304" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1304" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1304" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1305" s="3" t="inlineStr">
+        <is>
+          <t>соленоид n215 на мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C1305" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1305" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1305" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1306" s="3" t="inlineStr">
+        <is>
+          <t>dq250 мехатроник для дизеля</t>
+        </is>
+      </c>
+      <c r="C1306" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1306" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1306" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1307" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq250 шкода октавия а7</t>
+        </is>
+      </c>
+      <c r="C1307" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1307" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1307" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="3" t="inlineStr">
+        <is>
+          <t>Мехатроник dq250 dsg6 с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="B1308" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник шкода карок dq250</t>
+        </is>
+      </c>
+      <c r="C1308" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1308" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1308" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1309" s="3" t="inlineStr">
+        <is>
+          <t>соленоидный клапан это</t>
+        </is>
+      </c>
+      <c r="C1309" s="3" t="n">
+        <v>515</v>
+      </c>
+      <c r="D1309" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1309" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1310" s="3" t="inlineStr">
+        <is>
+          <t>соленоиды 6t40</t>
+        </is>
+      </c>
+      <c r="C1310" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="D1310" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1310" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1311" s="3" t="inlineStr">
+        <is>
+          <t>соленоиды в акпп 6t40</t>
+        </is>
+      </c>
+      <c r="C1311" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="D1311" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1311" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1312" s="3" t="inlineStr">
+        <is>
+          <t>комплект соленоидов 6t40</t>
+        </is>
+      </c>
+      <c r="C1312" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D1312" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1312" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1313" s="3" t="inlineStr">
+        <is>
+          <t>соленоиды 6t40 артикул</t>
+        </is>
+      </c>
+      <c r="C1313" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1313" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1313" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1314" s="3" t="inlineStr">
+        <is>
+          <t>замена соленоидов 6t40</t>
+        </is>
+      </c>
+      <c r="C1314" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D1314" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1314" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1315" s="3" t="inlineStr">
+        <is>
+          <t>соленоиды в акпп 6t40 ген 3 артикул</t>
+        </is>
+      </c>
+      <c r="C1315" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1315" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1315" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1316" s="3" t="inlineStr">
+        <is>
+          <t>блок соленоидов 6t40</t>
+        </is>
+      </c>
+      <c r="C1316" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1316" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1316" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1317" s="3" t="inlineStr">
+        <is>
+          <t>купить соленоид 6t40</t>
+        </is>
+      </c>
+      <c r="C1317" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1317" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1317" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1318" s="3" t="inlineStr">
+        <is>
+          <t>замена соленоида в акпп 6t40</t>
+        </is>
+      </c>
+      <c r="C1318" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1318" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1318" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1319" s="3" t="inlineStr">
+        <is>
+          <t>соленоиды 6t40 первой генерации</t>
+        </is>
+      </c>
+      <c r="C1319" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1319" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1319" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="3" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45 6t50</t>
+        </is>
+      </c>
+      <c r="B1320" s="3" t="inlineStr">
+        <is>
+          <t>артикул соленоидов опель астра j 2012 6t40</t>
+        </is>
+      </c>
+      <c r="C1320" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1320" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1320" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1321" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1321" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1321" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1321" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1322" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1322" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1322" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1322" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1323" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1323" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1323" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1323" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1324" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1324" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1324" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1324" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1325" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1325" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1325" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1325" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1326" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1326" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1326" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1326" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1327" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1327" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1327" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1327" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1328" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1328" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1328" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1328" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1329" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1329" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1329" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1329" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1330" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1330" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1330" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1330" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1331" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1331" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1331" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1331" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1332" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1332" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1332" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1332" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1333" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1333" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1333" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1333" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1334" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1334" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1334" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1334" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1335" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1335" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1335" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1335" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1336" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1336" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1336" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1336" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1337" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1337" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1337" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1337" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1338" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1338" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1338" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1338" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1339" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1339" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1339" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1339" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1340" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1340" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1340" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1340" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1341" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1341" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1341" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1341" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1342" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1342" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1342" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1342" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1343" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1343" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1343" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1343" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1344" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1344" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1344" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1344" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1345" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1345" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1345" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1345" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1346" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1346" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1346" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1346" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1347" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1347" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1347" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1347" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1348" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1348" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1348" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1348" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1349" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1349" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1349" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1349" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1350" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1350" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1350" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1350" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1351" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1351" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1351" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1351" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1352" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1352" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1352" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1352" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1353" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1353" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1353" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1353" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1354" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1354" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1354" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1354" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1355" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1355" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1355" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1355" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1356" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1356" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1356" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1356" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1357" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1357" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1357" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1357" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1358" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1358" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1358" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1358" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1359" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1359" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1359" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1359" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1360" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1360" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1360" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1360" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1361" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1361" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1361" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1361" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1362" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1362" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1362" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1362" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1363" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1363" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1363" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1363" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1364" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1364" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1364" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1364" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1365" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1365" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1365" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1365" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1366" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1366" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1366" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1366" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1367" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1367" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1367" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1367" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1368" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1368" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1368" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1368" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1369" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1369" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1369" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1369" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="3" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+      <c r="B1370" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1370" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1370" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1370" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1290"/>
+  <autoFilter ref="A1:E1370"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1370</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1453</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1370"/>
+  <dimension ref="A1:E1453"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -35331,8 +35331,2083 @@
         </is>
       </c>
     </row>
+    <row r="1371">
+      <c r="A1371" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1371" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200</t>
+        </is>
+      </c>
+      <c r="C1371" s="3" t="n">
+        <v>613</v>
+      </c>
+      <c r="D1371" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1371" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1372" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 гидроаккумулятор</t>
+        </is>
+      </c>
+      <c r="C1372" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D1372" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1372" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1373" s="3" t="inlineStr">
+        <is>
+          <t>давление в гидроаккумуляторе dq200</t>
+        </is>
+      </c>
+      <c r="C1373" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1373" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1373" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1374" s="3" t="inlineStr">
+        <is>
+          <t>замена гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1374" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D1374" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1374" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1375" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1375" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D1375" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1375" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1376" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1376" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D1376" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1376" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1377" s="3" t="inlineStr">
+        <is>
+          <t>как проверить гидроаккумулятор dq200</t>
+        </is>
+      </c>
+      <c r="C1377" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1377" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1377" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1378" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1378" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D1378" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1378" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1379" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор faw на dq200</t>
+        </is>
+      </c>
+      <c r="C1379" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1379" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1379" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1380" s="3" t="inlineStr">
+        <is>
+          <t>как снять гидроаккумулятор dq200</t>
+        </is>
+      </c>
+      <c r="C1380" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1380" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1380" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1381" s="3" t="inlineStr">
+        <is>
+          <t>взрыв гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1381" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1381" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1381" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1382" s="3" t="inlineStr">
+        <is>
+          <t>снятие гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1382" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1382" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1382" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1383" s="3" t="inlineStr">
+        <is>
+          <t>момент затяжки гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1383" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1383" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1383" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1384" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 давление в гидроаккумуляторе быстро падает</t>
+        </is>
+      </c>
+      <c r="C1384" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1384" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1384" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1385" s="3" t="inlineStr">
+        <is>
+          <t>размер уплотнительного кольца ремонтного гидроаккумулятора dsg dq200</t>
+        </is>
+      </c>
+      <c r="C1385" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1385" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1385" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1386" s="3" t="inlineStr">
+        <is>
+          <t>как стравить давление в гидроаккумуляторе dq200</t>
+        </is>
+      </c>
+      <c r="C1386" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1386" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1386" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1387" s="3" t="inlineStr">
+        <is>
+          <t>проверка гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1387" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1387" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1387" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1388" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор на dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1388" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1388" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1388" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1389" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200 ремонтный московское ш 13</t>
+        </is>
+      </c>
+      <c r="C1389" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1389" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1389" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1390" s="3" t="inlineStr">
+        <is>
+          <t>оригинальный гидроаккумулятор на dq200 кто производит faw</t>
+        </is>
+      </c>
+      <c r="C1390" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1390" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1390" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1391" s="3" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор на dq200 fte automotive</t>
+        </is>
+      </c>
+      <c r="C1391" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1391" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1391" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="3" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1392" s="3" t="inlineStr">
+        <is>
+          <t>как сбросить давление с гидроаккумулятора dq200</t>
+        </is>
+      </c>
+      <c r="C1392" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1392" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1392" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1393" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
+      <c r="C1393" s="3" t="n">
+        <v>568</v>
+      </c>
+      <c r="D1393" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1393" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1394" s="3" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1394" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="D1394" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1394" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1395" s="3" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1395" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="D1395" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1395" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1396" s="3" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1396" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1396" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1396" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1397" s="3" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1397" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1397" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1397" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1398" s="3" t="inlineStr">
+        <is>
+          <t>замена крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1398" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1398" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1398" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1399" s="3" t="inlineStr">
+        <is>
+          <t>прокладка крышки мехатроника dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1399" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D1399" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1399" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1400" s="3" t="inlineStr">
+        <is>
+          <t>тверь крышка мехатроника dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1400" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1400" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1400" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1401" s="3" t="inlineStr">
+        <is>
+          <t>крышка сапуна мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1401" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1401" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1401" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1402" s="3" t="inlineStr">
+        <is>
+          <t>замена прокладки крышки мехатроника dq200</t>
+        </is>
+      </c>
+      <c r="C1402" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1402" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1402" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="3" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1403" s="3" t="inlineStr">
+        <is>
+          <t>степень затяжки болтов крышки мехатроника dsg dq200</t>
+        </is>
+      </c>
+      <c r="C1403" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1403" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1403" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1404" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1404" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1404" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1404" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1405" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1405" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1405" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1405" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1406" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1406" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1406" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1406" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1407" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1407" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1407" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1407" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1408" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1408" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1408" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1408" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1409" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1409" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1409" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1409" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1410" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1410" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1410" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1410" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1411" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1411" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1411" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1411" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1412" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1412" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1412" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1412" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1413" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1413" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1413" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1413" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1414" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1414" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1414" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1414" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1415" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1415" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1415" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1415" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1416" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1416" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1416" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1416" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1417" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1417" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1417" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1417" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1418" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1418" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1418" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1418" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1419" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1419" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1419" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1419" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1420" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1420" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1420" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1420" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1421" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1421" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1421" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1421" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1422" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1422" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1422" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1422" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1423" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1423" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1423" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1423" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1424" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1424" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1424" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1424" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1425" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1425" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1425" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1425" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1426" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1426" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1426" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1426" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1427" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1427" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1427" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1427" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1428" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1428" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1428" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1428" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1429" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1429" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1429" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1429" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1430" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1430" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1430" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1430" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1431" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1431" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1431" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1431" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1432" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1432" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1432" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1432" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1433" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1433" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1433" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1433" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1434" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1434" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1434" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1434" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1435" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1435" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1435" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1435" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1436" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1436" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1436" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1436" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1437" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1437" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1437" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1437" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1438" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1438" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1438" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1438" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1439" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1439" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1439" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1439" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1440" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1440" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1440" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1440" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1441" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1441" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1441" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1441" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1442" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1442" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1442" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1442" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1443" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1443" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1443" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1443" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1444" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1444" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1444" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1444" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1445" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1445" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1445" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1445" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1446" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1446" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1446" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1446" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1447" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1447" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1447" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1447" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1448" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1448" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1448" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1448" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1449" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1449" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1449" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1449" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1450" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1450" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1450" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1450" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1451" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1451" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1451" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1451" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1452" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1452" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1452" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1452" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="3" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1453" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1453" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1453" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1453" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1370"/>
+  <autoFilter ref="A1:E1453"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1453</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1524</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1453"/>
+  <dimension ref="A1:E1524"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -37406,8 +37406,1783 @@
         </is>
       </c>
     </row>
+    <row r="1454">
+      <c r="A1454" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1454" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1454" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1454" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1454" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1455" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1455" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1455" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1455" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1456" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1456" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1456" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1456" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1457" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1457" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1457" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1457" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1458" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1458" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1458" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1458" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1459" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1459" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1459" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1459" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1460" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1460" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1460" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1460" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1461" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1461" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1461" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1461" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1462" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1462" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1462" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1462" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1463" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1463" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1463" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1463" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1464" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1464" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1464" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1464" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1465" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1465" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1465" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1465" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1466" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1466" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1466" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1466" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1467" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1467" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1467" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1467" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1468" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1468" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1468" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1468" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1469" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1469" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1469" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1469" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1470" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1470" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1470" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1470" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1471" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1471" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1471" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1471" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1472" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1472" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1472" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1472" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1473" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1473" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1473" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1473" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1474" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1474" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1474" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1474" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1475" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1475" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1475" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1475" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1476" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1476" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1476" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1476" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1477" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1477" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1477" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1477" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1478" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1478" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1478" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1478" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1479" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1479" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1479" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1479" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1480" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1480" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1480" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1480" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1481" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1481" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1481" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1481" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1482" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1482" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1482" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1482" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1483" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1483" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1483" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1483" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1484" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1484" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1484" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1484" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1485" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1485" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1485" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1485" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1486" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1486" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1486" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1486" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1487" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1487" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1487" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1487" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1488" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1488" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1488" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1488" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1489" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1489" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1489" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1489" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1490" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1490" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1490" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1490" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1491" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1491" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1491" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1491" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1492" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1492" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1492" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1492" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1493" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1493" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1493" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1493" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1494" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1494" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1494" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1494" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1495" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1495" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1495" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1495" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1496" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1496" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1496" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1496" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1497" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1497" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1497" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1497" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1498" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1498" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1498" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1498" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1499" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1499" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1499" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1499" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1500" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1500" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1500" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1500" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1501" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1501" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1501" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1501" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1502" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1502" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1502" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1502" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="3" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+      <c r="B1503" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1503" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1503" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1503" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="3" t="inlineStr">
+        <is>
+          <t>комплект накладок на педали</t>
+        </is>
+      </c>
+      <c r="B1504" s="3" t="inlineStr">
+        <is>
+          <t>рено кангу 2 комплект накладок на педали</t>
+        </is>
+      </c>
+      <c r="C1504" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1504" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1504" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="3" t="inlineStr">
+        <is>
+          <t>комплект накладок на педали</t>
+        </is>
+      </c>
+      <c r="B1505" s="3" t="inlineStr">
+        <is>
+          <t>w210 комплект накладок на педали</t>
+        </is>
+      </c>
+      <c r="C1505" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1505" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1505" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="3" t="inlineStr">
+        <is>
+          <t>комплект накладок на педали</t>
+        </is>
+      </c>
+      <c r="B1506" s="3" t="inlineStr">
+        <is>
+          <t>комплект накладок на педали ман tgl</t>
+        </is>
+      </c>
+      <c r="C1506" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1506" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1506" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1507" s="3" t="inlineStr">
+        <is>
+          <t>сапун редуктора</t>
+        </is>
+      </c>
+      <c r="C1507" s="3" t="n">
+        <v>5924</v>
+      </c>
+      <c r="D1507" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1507" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1508" s="3" t="inlineStr">
+        <is>
+          <t>втулка скольжения с фланцем</t>
+        </is>
+      </c>
+      <c r="C1508" s="3" t="n">
+        <v>418</v>
+      </c>
+      <c r="D1508" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1508" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1509" s="3" t="inlineStr">
+        <is>
+          <t>сальник dq200</t>
+        </is>
+      </c>
+      <c r="C1509" s="3" t="n">
+        <v>347</v>
+      </c>
+      <c r="D1509" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1509" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1510" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника dq200</t>
+        </is>
+      </c>
+      <c r="C1510" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1510" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1510" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1511" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников dq200</t>
+        </is>
+      </c>
+      <c r="C1511" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1511" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1511" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1512" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1512" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1512" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1512" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1513" s="3" t="inlineStr">
+        <is>
+          <t>сальник привода dq200</t>
+        </is>
+      </c>
+      <c r="C1513" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D1513" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1513" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1514" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C1514" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1514" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1514" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1515" s="3" t="inlineStr">
+        <is>
+          <t>сальники dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1515" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1515" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1515" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1516" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1516" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1516" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1516" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1517" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1517" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1517" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1517" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1518" s="3" t="inlineStr">
+        <is>
+          <t>сальник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1518" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1518" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1518" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1519" s="3" t="inlineStr">
+        <is>
+          <t>замена правого сальника привода dq200</t>
+        </is>
+      </c>
+      <c r="C1519" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1519" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1519" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1520" s="3" t="inlineStr">
+        <is>
+          <t>съемник сальника dq200</t>
+        </is>
+      </c>
+      <c r="C1520" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1520" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1520" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1521" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1521" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1521" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1521" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1522" s="3" t="inlineStr">
+        <is>
+          <t>сальник кпп первичного вала dq200</t>
+        </is>
+      </c>
+      <c r="C1522" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1522" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1522" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1523" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала внутренний и наружный dq200</t>
+        </is>
+      </c>
+      <c r="C1523" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1523" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1523" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1524" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1524" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1524" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1524" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1453"/>
+  <autoFilter ref="A1:E1524"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1524</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1524"/>
+  <dimension ref="A1:E1759"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -39181,8 +39181,5883 @@
         </is>
       </c>
     </row>
+    <row r="1525">
+      <c r="A1525" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1525" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1525" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1525" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1525" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1526" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1526" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1526" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1526" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1527" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1527" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1527" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1527" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1528" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1528" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1528" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1528" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1529" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1529" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1529" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1529" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1530" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1530" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1530" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1530" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1531" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1531" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1531" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1531" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1532" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1532" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1532" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1532" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1533" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1533" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1533" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1533" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1534" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1534" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1534" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1534" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1535" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1535" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1535" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1535" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1536" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1536" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1536" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1536" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1537" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1537" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1537" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1537" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1538" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1538" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1538" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1538" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1539" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1539" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1539" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1539" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1540" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1540" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1540" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1540" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1541" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1541" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1541" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1541" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1542" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1542" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1542" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1542" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1543" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1543" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1543" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1543" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1544" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1544" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1544" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1544" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1545" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1545" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1545" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1545" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1546" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1546" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1546" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1546" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1547" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1547" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1547" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1547" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1548" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1548" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1548" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1548" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1549" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1549" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1549" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1549" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1550" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1550" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1550" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1550" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1551" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1551" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1551" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1551" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1552" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1552" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1552" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1552" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1553" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1553" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1553" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1553" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1554" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1554" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1554" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1554" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1555" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1555" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1555" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1555" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1556" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1556" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1556" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1556" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1557" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1557" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1557" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1557" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1558" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1558" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1558" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1558" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1559" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1559" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1559" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1559" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1560" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1560" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1560" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1560" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1561" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1561" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1561" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1561" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1562" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1562" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1562" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1562" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1563" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1563" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1563" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1563" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1564" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1564" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1564" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1564" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1565" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1565" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1565" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1565" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1566" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1566" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1566" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1566" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1567" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1567" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1567" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1567" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1568" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1568" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1568" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1568" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1569" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1569" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1569" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1569" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1570" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1570" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1570" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1570" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1571" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1571" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1571" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1571" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1572" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1572" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1572" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1572" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1573" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1573" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1573" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1573" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="3" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1574" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1574" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1574" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1574" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1575" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1575" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D1575" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1575" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1576" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C1576" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D1576" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1576" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1577" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1577" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D1577" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1577" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1578" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1578" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D1578" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1578" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1579" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1579" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D1579" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1579" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1580" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1580" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1580" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1580" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1581" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C1581" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D1581" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1581" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1582" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1582" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D1582" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1582" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1583" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1583" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D1583" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1583" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1584" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1584" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D1584" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1584" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1585" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1585" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D1585" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1585" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1586" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C1586" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1586" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1586" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1587" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1587" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D1587" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1587" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1588" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1588" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1588" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1588" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1589" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1589" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D1589" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1589" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1590" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1590" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D1590" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1590" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1591" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1591" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D1591" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1591" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1592" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1592" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1592" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1592" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1593" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C1593" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D1593" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1593" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1594" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1594" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D1594" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1594" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1595" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1595" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1595" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1595" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1596" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1596" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D1596" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1596" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1597" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1597" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D1597" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1597" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1598" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C1598" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D1598" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1598" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1599" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1599" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D1599" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1599" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1600" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C1600" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D1600" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1600" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1601" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1601" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1601" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1601" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1602" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1602" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D1602" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1602" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1603" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1603" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D1603" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1603" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1604" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1604" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1604" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1604" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1605" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1605" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1605" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1605" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1606" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1606" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1606" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1606" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1607" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C1607" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1607" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1607" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1608" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C1608" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D1608" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1608" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1609" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C1609" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1609" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1609" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1610" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C1610" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1610" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1610" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1611" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1611" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1611" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1611" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1612" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C1612" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1612" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1612" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1613" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C1613" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D1613" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1613" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1614" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C1614" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1614" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1614" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1615" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C1615" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1615" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1615" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1616" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C1616" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1616" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1616" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1617" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1617" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1617" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1617" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1618" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C1618" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1618" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1618" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1619" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C1619" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1619" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1619" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1620" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C1620" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1620" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1620" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1621" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C1621" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D1621" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1621" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1622" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C1622" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D1622" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1622" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1623" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C1623" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1623" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1623" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="3" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B1624" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C1624" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1624" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1624" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1625" s="3" t="inlineStr">
+        <is>
+          <t>сальник коленвала</t>
+        </is>
+      </c>
+      <c r="C1625" s="3" t="n">
+        <v>238409</v>
+      </c>
+      <c r="D1625" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1625" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1626" s="3" t="inlineStr">
+        <is>
+          <t>сальник коленвала передний</t>
+        </is>
+      </c>
+      <c r="C1626" s="3" t="n">
+        <v>57272</v>
+      </c>
+      <c r="D1626" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1626" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1627" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C1627" s="3" t="n">
+        <v>51282</v>
+      </c>
+      <c r="D1627" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1627" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1628" s="3" t="inlineStr">
+        <is>
+          <t>вал шестерня</t>
+        </is>
+      </c>
+      <c r="C1628" s="3" t="n">
+        <v>32837</v>
+      </c>
+      <c r="D1628" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1628" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1629" s="3" t="inlineStr">
+        <is>
+          <t>шкив помпы</t>
+        </is>
+      </c>
+      <c r="C1629" s="3" t="n">
+        <v>18365</v>
+      </c>
+      <c r="D1629" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1629" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1630" s="3" t="inlineStr">
+        <is>
+          <t>болт шкива коленвала</t>
+        </is>
+      </c>
+      <c r="C1630" s="3" t="n">
+        <v>17223</v>
+      </c>
+      <c r="D1630" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1630" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1631" s="3" t="inlineStr">
+        <is>
+          <t>коленвал и распредвал</t>
+        </is>
+      </c>
+      <c r="C1631" s="3" t="n">
+        <v>13983</v>
+      </c>
+      <c r="D1631" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1631" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1632" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор коленвала</t>
+        </is>
+      </c>
+      <c r="C1632" s="3" t="n">
+        <v>12671</v>
+      </c>
+      <c r="D1632" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1632" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1633" s="3" t="inlineStr">
+        <is>
+          <t>демпфер коленвала</t>
+        </is>
+      </c>
+      <c r="C1633" s="3" t="n">
+        <v>8205</v>
+      </c>
+      <c r="D1633" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1633" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1634" s="3" t="inlineStr">
+        <is>
+          <t>шкив коленчатого вала</t>
+        </is>
+      </c>
+      <c r="C1634" s="3" t="n">
+        <v>5019</v>
+      </c>
+      <c r="D1634" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1634" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1635" s="3" t="inlineStr">
+        <is>
+          <t>датчики коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1635" s="3" t="n">
+        <v>4461</v>
+      </c>
+      <c r="D1635" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1635" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1636" s="3" t="inlineStr">
+        <is>
+          <t>шлифовка коленвала</t>
+        </is>
+      </c>
+      <c r="C1636" s="3" t="n">
+        <v>3304</v>
+      </c>
+      <c r="D1636" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1636" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1637" s="3" t="inlineStr">
+        <is>
+          <t>сальники коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1637" s="3" t="n">
+        <v>2836</v>
+      </c>
+      <c r="D1637" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1637" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1638" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала</t>
+        </is>
+      </c>
+      <c r="C1638" s="3" t="n">
+        <v>2664</v>
+      </c>
+      <c r="D1638" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1638" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1639" s="3" t="inlineStr">
+        <is>
+          <t>метки коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1639" s="3" t="n">
+        <v>2528</v>
+      </c>
+      <c r="D1639" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1639" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1640" s="3" t="inlineStr">
+        <is>
+          <t>кольцо датчика распредвала</t>
+        </is>
+      </c>
+      <c r="C1640" s="3" t="n">
+        <v>1586</v>
+      </c>
+      <c r="D1640" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1640" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1641" s="3" t="inlineStr">
+        <is>
+          <t>распредвал и коленвал двигателя</t>
+        </is>
+      </c>
+      <c r="C1641" s="3" t="n">
+        <v>1559</v>
+      </c>
+      <c r="D1641" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1641" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1642" s="3" t="inlineStr">
+        <is>
+          <t>съемник подшипника коленвала</t>
+        </is>
+      </c>
+      <c r="C1642" s="3" t="n">
+        <v>973</v>
+      </c>
+      <c r="D1642" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1642" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1643" s="3" t="inlineStr">
+        <is>
+          <t>как намотать пружину на стартер триммера</t>
+        </is>
+      </c>
+      <c r="C1643" s="3" t="n">
+        <v>881</v>
+      </c>
+      <c r="D1643" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1643" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1644" s="3" t="inlineStr">
+        <is>
+          <t>где коленвал и распредвал</t>
+        </is>
+      </c>
+      <c r="C1644" s="3" t="n">
+        <v>760</v>
+      </c>
+      <c r="D1644" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1644" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1645" s="3" t="inlineStr">
+        <is>
+          <t>датчик коленвала и распредвала ниссан</t>
+        </is>
+      </c>
+      <c r="C1645" s="3" t="n">
+        <v>719</v>
+      </c>
+      <c r="D1645" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1645" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1646" s="3" t="inlineStr">
+        <is>
+          <t>как выставить коленвал и распредвал</t>
+        </is>
+      </c>
+      <c r="C1646" s="3" t="n">
+        <v>667</v>
+      </c>
+      <c r="D1646" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1646" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1647" s="3" t="inlineStr">
+        <is>
+          <t>ошибка коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1647" s="3" t="n">
+        <v>633</v>
+      </c>
+      <c r="D1647" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1647" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1648" s="3" t="inlineStr">
+        <is>
+          <t>как снять поршень с шатуна</t>
+        </is>
+      </c>
+      <c r="C1648" s="3" t="n">
+        <v>624</v>
+      </c>
+      <c r="D1648" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1648" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1649" s="3" t="inlineStr">
+        <is>
+          <t>положения коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1649" s="3" t="n">
+        <v>617</v>
+      </c>
+      <c r="D1649" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1649" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1650" s="3" t="inlineStr">
+        <is>
+          <t>тефлоновый сальник коленвала</t>
+        </is>
+      </c>
+      <c r="C1650" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D1650" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1650" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1651" s="3" t="inlineStr">
+        <is>
+          <t>сальник коленвала задний 2108</t>
+        </is>
+      </c>
+      <c r="C1651" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="D1651" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1651" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1652" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1652" s="3" t="n">
+        <v>597</v>
+      </c>
+      <c r="D1652" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1652" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1653" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников распредвалов и коленвала</t>
+        </is>
+      </c>
+      <c r="C1653" s="3" t="n">
+        <v>597</v>
+      </c>
+      <c r="D1653" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1653" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1654" s="3" t="inlineStr">
+        <is>
+          <t>сальник коленвала и распредвала ваз</t>
+        </is>
+      </c>
+      <c r="C1654" s="3" t="n">
+        <v>530</v>
+      </c>
+      <c r="D1654" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1654" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1655" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="C1655" s="3" t="n">
+        <v>524</v>
+      </c>
+      <c r="D1655" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1655" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1656" s="3" t="inlineStr">
+        <is>
+          <t>коленвал и распредвал где находится</t>
+        </is>
+      </c>
+      <c r="C1656" s="3" t="n">
+        <v>514</v>
+      </c>
+      <c r="D1656" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1656" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1657" s="3" t="inlineStr">
+        <is>
+          <t>шестерни распредвала и коленвала</t>
+        </is>
+      </c>
+      <c r="C1657" s="3" t="n">
+        <v>487</v>
+      </c>
+      <c r="D1657" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1657" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1658" s="3" t="inlineStr">
+        <is>
+          <t>датчик положения коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1658" s="3" t="n">
+        <v>483</v>
+      </c>
+      <c r="D1658" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1658" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1659" s="3" t="inlineStr">
+        <is>
+          <t>болт коленвала 2108</t>
+        </is>
+      </c>
+      <c r="C1659" s="3" t="n">
+        <v>433</v>
+      </c>
+      <c r="D1659" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1659" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1660" s="3" t="inlineStr">
+        <is>
+          <t>фиксаторы коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1660" s="3" t="n">
+        <v>426</v>
+      </c>
+      <c r="D1660" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1660" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1661" s="3" t="inlineStr">
+        <is>
+          <t>метки коленвала и распредвала ваз</t>
+        </is>
+      </c>
+      <c r="C1661" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D1661" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1661" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1662" s="3" t="inlineStr">
+        <is>
+          <t>где находится датчик коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1662" s="3" t="n">
+        <v>397</v>
+      </c>
+      <c r="D1662" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1662" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1663" s="3" t="inlineStr">
+        <is>
+          <t>синхронизация коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1663" s="3" t="n">
+        <v>338</v>
+      </c>
+      <c r="D1663" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1663" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1664" s="3" t="inlineStr">
+        <is>
+          <t>ошибка датчика коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1664" s="3" t="n">
+        <v>329</v>
+      </c>
+      <c r="D1664" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1664" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1665" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала ваз</t>
+        </is>
+      </c>
+      <c r="C1665" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="D1665" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1665" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1666" s="3" t="inlineStr">
+        <is>
+          <t>как совместить коленвал и распредвал</t>
+        </is>
+      </c>
+      <c r="C1666" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="D1666" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1666" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1667" s="3" t="inlineStr">
+        <is>
+          <t>коленвал и распредвал в чем разница</t>
+        </is>
+      </c>
+      <c r="C1667" s="3" t="n">
+        <v>247</v>
+      </c>
+      <c r="D1667" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1667" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1668" s="3" t="inlineStr">
+        <is>
+          <t>передний коленвала и распредвалов</t>
+        </is>
+      </c>
+      <c r="C1668" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="D1668" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1668" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1669" s="3" t="inlineStr">
+        <is>
+          <t>ниссан альмера датчик коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1669" s="3" t="n">
+        <v>236</v>
+      </c>
+      <c r="D1669" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1669" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1670" s="3" t="inlineStr">
+        <is>
+          <t>рассинхронизация коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1670" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="D1670" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1670" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1671" s="3" t="inlineStr">
+        <is>
+          <t>датчик распредвала и коленвала одинаковые</t>
+        </is>
+      </c>
+      <c r="C1671" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D1671" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1671" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1672" s="3" t="inlineStr">
+        <is>
+          <t>как совместить метки коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1672" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D1672" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1672" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1673" s="3" t="inlineStr">
+        <is>
+          <t>осциллограммы распредвала и коленвала</t>
+        </is>
+      </c>
+      <c r="C1673" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D1673" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1673" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1674" s="3" t="inlineStr">
+        <is>
+          <t>как снять шкив коленвала съемником</t>
+        </is>
+      </c>
+      <c r="C1674" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="D1674" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1674" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1675" s="3" t="inlineStr">
+        <is>
+          <t>оборот коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1675" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="D1675" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1675" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1676" s="3" t="inlineStr">
+        <is>
+          <t>датчик коленвала и распредвала альмера классик</t>
+        </is>
+      </c>
+      <c r="C1676" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="D1676" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1676" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1677" s="3" t="inlineStr">
+        <is>
+          <t>метки коленвала и распредвала нива</t>
+        </is>
+      </c>
+      <c r="C1677" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="D1677" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1677" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1678" s="3" t="inlineStr">
+        <is>
+          <t>болт шкива коленвала 2108</t>
+        </is>
+      </c>
+      <c r="C1678" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="D1678" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1678" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1679" s="3" t="inlineStr">
+        <is>
+          <t>купить съемник шкива коленвала</t>
+        </is>
+      </c>
+      <c r="C1679" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="D1679" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1679" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1680" s="3" t="inlineStr">
+        <is>
+          <t>купить датчик коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1680" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="D1680" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1680" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1681" s="3" t="inlineStr">
+        <is>
+          <t>коленвал и распредвал фото</t>
+        </is>
+      </c>
+      <c r="C1681" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="D1681" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1681" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1682" s="3" t="inlineStr">
+        <is>
+          <t>датчик коленвала и распредвала ниссан альмера классик</t>
+        </is>
+      </c>
+      <c r="C1682" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D1682" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1682" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1683" s="3" t="inlineStr">
+        <is>
+          <t>как снять шкив коленвала без съемника</t>
+        </is>
+      </c>
+      <c r="C1683" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="D1683" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1683" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1684" s="3" t="inlineStr">
+        <is>
+          <t>распредвал и коленвал расположение</t>
+        </is>
+      </c>
+      <c r="C1684" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="D1684" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1684" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1685" s="3" t="inlineStr">
+        <is>
+          <t>осциллограмма датчика коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1685" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="D1685" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1685" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1686" s="3" t="inlineStr">
+        <is>
+          <t>съемник для снятия шкива коленвала</t>
+        </is>
+      </c>
+      <c r="C1686" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="D1686" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1686" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1687" s="3" t="inlineStr">
+        <is>
+          <t>датчик распредвала и коленвала разница</t>
+        </is>
+      </c>
+      <c r="C1687" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="D1687" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1687" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1688" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала и коленвала одинаковые или нет</t>
+        </is>
+      </c>
+      <c r="C1688" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="D1688" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1688" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1689" s="3" t="inlineStr">
+        <is>
+          <t>не совпадают метки коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1689" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="D1689" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1689" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1690" s="3" t="inlineStr">
+        <is>
+          <t>коленвал и распредвал ваз 2110</t>
+        </is>
+      </c>
+      <c r="C1690" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D1690" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1690" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1691" s="3" t="inlineStr">
+        <is>
+          <t>замена датчиков коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1691" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D1691" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1691" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1692" s="3" t="inlineStr">
+        <is>
+          <t>установка меток коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1692" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="D1692" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1692" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1693" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала змз</t>
+        </is>
+      </c>
+      <c r="C1693" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="D1693" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1693" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1694" s="3" t="inlineStr">
+        <is>
+          <t>синхронизация датчика коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1694" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="D1694" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1694" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1695" s="3" t="inlineStr">
+        <is>
+          <t>распредвал и коленвал отличия</t>
+        </is>
+      </c>
+      <c r="C1695" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D1695" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1695" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1696" s="3" t="inlineStr">
+        <is>
+          <t>гранта сальник коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1696" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="D1696" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1696" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1697" s="3" t="inlineStr">
+        <is>
+          <t>как установить коленвал и распредвал</t>
+        </is>
+      </c>
+      <c r="C1697" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D1697" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1697" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1698" s="3" t="inlineStr">
+        <is>
+          <t>рассинхронизация датчика коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1698" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="D1698" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1698" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1699" s="3" t="inlineStr">
+        <is>
+          <t>как выставить коленвал и распредвал по меткам</t>
+        </is>
+      </c>
+      <c r="C1699" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1699" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1699" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1700" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала и коленвала 2114</t>
+        </is>
+      </c>
+      <c r="C1700" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="D1700" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1700" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1701" s="3" t="inlineStr">
+        <is>
+          <t>как смотать пружину стартера триммера</t>
+        </is>
+      </c>
+      <c r="C1701" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="D1701" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1701" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1702" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкивов коленвала крайслер</t>
+        </is>
+      </c>
+      <c r="C1702" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1702" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1702" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1703" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала тойота</t>
+        </is>
+      </c>
+      <c r="C1703" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="D1703" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1703" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1704" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала змз 409</t>
+        </is>
+      </c>
+      <c r="C1704" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D1704" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1704" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1705" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала форд</t>
+        </is>
+      </c>
+      <c r="C1705" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D1705" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1705" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1706" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала хонда</t>
+        </is>
+      </c>
+      <c r="C1706" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D1706" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1706" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1707" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала 2110</t>
+        </is>
+      </c>
+      <c r="C1707" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1707" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1707" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1708" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала уаз</t>
+        </is>
+      </c>
+      <c r="C1708" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D1708" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1708" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1709" s="3" t="inlineStr">
+        <is>
+          <t>пружина фланца стартера триммера 125с</t>
+        </is>
+      </c>
+      <c r="C1709" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D1709" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1709" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1710" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала ямз</t>
+        </is>
+      </c>
+      <c r="C1710" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1710" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1710" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1711" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала ваз 2110</t>
+        </is>
+      </c>
+      <c r="C1711" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1711" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1711" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1712" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала 2114</t>
+        </is>
+      </c>
+      <c r="C1712" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D1712" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1712" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1713" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала ваз 2114</t>
+        </is>
+      </c>
+      <c r="C1713" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D1713" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1713" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1714" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала акпп</t>
+        </is>
+      </c>
+      <c r="C1714" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D1714" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1714" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1715" s="3" t="inlineStr">
+        <is>
+          <t>размеры съемника шкива коленвала</t>
+        </is>
+      </c>
+      <c r="C1715" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D1715" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1715" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1716" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала патриот</t>
+        </is>
+      </c>
+      <c r="C1716" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D1716" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1716" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1717" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала уаз патриот</t>
+        </is>
+      </c>
+      <c r="C1717" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D1717" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1717" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1718" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала крайслер 2.4</t>
+        </is>
+      </c>
+      <c r="C1718" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D1718" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1718" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1719" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала универсальный</t>
+        </is>
+      </c>
+      <c r="C1719" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D1719" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1719" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1720" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала гранта</t>
+        </is>
+      </c>
+      <c r="C1720" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D1720" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1720" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1721" s="3" t="inlineStr">
+        <is>
+          <t>съемник для снятия шкива коленвала купить</t>
+        </is>
+      </c>
+      <c r="C1721" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D1721" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1721" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1722" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала ваз 2115</t>
+        </is>
+      </c>
+      <c r="C1722" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D1722" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1722" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1723" s="3" t="inlineStr">
+        <is>
+          <t>съемник переднего шкива коленвала</t>
+        </is>
+      </c>
+      <c r="C1723" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D1723" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1723" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1724" s="3" t="inlineStr">
+        <is>
+          <t>съемник шестерней коленвала и шкивов</t>
+        </is>
+      </c>
+      <c r="C1724" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1724" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1724" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1725" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала 2108</t>
+        </is>
+      </c>
+      <c r="C1725" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1725" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1725" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1726" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала 406</t>
+        </is>
+      </c>
+      <c r="C1726" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D1726" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1726" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1727" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала змз 406</t>
+        </is>
+      </c>
+      <c r="C1727" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D1727" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1727" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1728" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала своими руками</t>
+        </is>
+      </c>
+      <c r="C1728" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D1728" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1728" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1729" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала ямз 238</t>
+        </is>
+      </c>
+      <c r="C1729" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D1729" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1729" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1730" s="3" t="inlineStr">
+        <is>
+          <t>съемник для шкива коленвала газель</t>
+        </is>
+      </c>
+      <c r="C1730" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D1730" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1730" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1731" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала рено</t>
+        </is>
+      </c>
+      <c r="C1731" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1731" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1731" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1732" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала ваз 2108</t>
+        </is>
+      </c>
+      <c r="C1732" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D1732" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1732" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1733" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала змз 402</t>
+        </is>
+      </c>
+      <c r="C1733" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1733" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1733" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1734" s="3" t="inlineStr">
+        <is>
+          <t>съемник ступицы шкива коленвала змз 409</t>
+        </is>
+      </c>
+      <c r="C1734" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1734" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1734" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1735" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала приора</t>
+        </is>
+      </c>
+      <c r="C1735" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1735" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1735" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1736" s="3" t="inlineStr">
+        <is>
+          <t>съемник для шкива коленвала 409</t>
+        </is>
+      </c>
+      <c r="C1736" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1736" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1736" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1737" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала мазда</t>
+        </is>
+      </c>
+      <c r="C1737" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D1737" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1737" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1738" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала газель 4216</t>
+        </is>
+      </c>
+      <c r="C1738" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1738" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1738" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1739" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала тойота купить</t>
+        </is>
+      </c>
+      <c r="C1739" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1739" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1739" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1740" s="3" t="inlineStr">
+        <is>
+          <t>съемник шестерней коленвала и шкивов 805040</t>
+        </is>
+      </c>
+      <c r="C1740" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1740" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1740" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1741" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала универсальный купить</t>
+        </is>
+      </c>
+      <c r="C1741" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1741" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1741" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1742" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала логан</t>
+        </is>
+      </c>
+      <c r="C1742" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1742" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1742" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1743" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала для маз</t>
+        </is>
+      </c>
+      <c r="C1743" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1743" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1743" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1744" s="3" t="inlineStr">
+        <is>
+          <t>спаркс nmrv s050 сальник входного вала редуктора</t>
+        </is>
+      </c>
+      <c r="C1744" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1744" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1744" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1745" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала форд фокус</t>
+        </is>
+      </c>
+      <c r="C1745" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1745" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1745" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1746" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала хонда црв двигатель в20в</t>
+        </is>
+      </c>
+      <c r="C1746" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1746" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1746" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1747" s="3" t="inlineStr">
+        <is>
+          <t>съемник шкива коленвала рено логан</t>
+        </is>
+      </c>
+      <c r="C1747" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1747" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1747" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1748" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала vt 2</t>
+        </is>
+      </c>
+      <c r="C1748" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1748" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1748" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1749" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала вариатора вт 2 артикул</t>
+        </is>
+      </c>
+      <c r="C1749" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1749" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1749" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1750" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала voge 525 rr</t>
+        </is>
+      </c>
+      <c r="C1750" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D1750" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1750" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1751" s="3" t="inlineStr">
+        <is>
+          <t>тойота прадо 120 сальник входного вала</t>
+        </is>
+      </c>
+      <c r="C1751" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1751" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1751" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1752" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала кпп ваз классика</t>
+        </is>
+      </c>
+      <c r="C1752" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1752" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1752" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1753" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала рулевой рейки чери амулет</t>
+        </is>
+      </c>
+      <c r="C1753" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1753" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1753" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1754" s="3" t="inlineStr">
+        <is>
+          <t>сальник ведущего входного вала врк шоттель</t>
+        </is>
+      </c>
+      <c r="C1754" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1754" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1754" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1755" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала мотоблок урал мб1</t>
+        </is>
+      </c>
+      <c r="C1755" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1755" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1755" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1756" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала субару</t>
+        </is>
+      </c>
+      <c r="C1756" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1756" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1756" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1757" s="3" t="inlineStr">
+        <is>
+          <t>сальник на гур камаз входного вала</t>
+        </is>
+      </c>
+      <c r="C1757" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1757" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1757" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1758" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала передний акпп 42rle</t>
+        </is>
+      </c>
+      <c r="C1758" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1758" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1758" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+      <c r="B1759" s="3" t="inlineStr">
+        <is>
+          <t>сальник входного вала редуктора nmrv 050 купить</t>
+        </is>
+      </c>
+      <c r="C1759" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1759" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1759" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1524"/>
+  <autoFilter ref="A1:E1759"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$2135</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1759"/>
+  <dimension ref="A1:E2135"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -45056,8 +45056,9408 @@
         </is>
       </c>
     </row>
+    <row r="1760">
+      <c r="A1760" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1760" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора</t>
+        </is>
+      </c>
+      <c r="C1760" s="3" t="n">
+        <v>70662</v>
+      </c>
+      <c r="D1760" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1760" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1761" s="3" t="inlineStr">
+        <is>
+          <t>сальников распредвала</t>
+        </is>
+      </c>
+      <c r="C1761" s="3" t="n">
+        <v>54318</v>
+      </c>
+      <c r="D1761" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1761" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1762" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала</t>
+        </is>
+      </c>
+      <c r="C1762" s="3" t="n">
+        <v>54313</v>
+      </c>
+      <c r="D1762" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1762" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1763" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников коленвала</t>
+        </is>
+      </c>
+      <c r="C1763" s="3" t="n">
+        <v>51339</v>
+      </c>
+      <c r="D1763" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1763" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1764" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C1764" s="3" t="n">
+        <v>51328</v>
+      </c>
+      <c r="D1764" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1764" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1765" s="3" t="inlineStr">
+        <is>
+          <t>вал редуктора</t>
+        </is>
+      </c>
+      <c r="C1765" s="3" t="n">
+        <v>38642</v>
+      </c>
+      <c r="D1765" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1765" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1766" s="3" t="inlineStr">
+        <is>
+          <t>шестерня редуктора</t>
+        </is>
+      </c>
+      <c r="C1766" s="3" t="n">
+        <v>36100</v>
+      </c>
+      <c r="D1766" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1766" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1767" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="C1767" s="3" t="n">
+        <v>26198</v>
+      </c>
+      <c r="D1767" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1767" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1768" s="3" t="inlineStr">
+        <is>
+          <t>хвостовик редуктора</t>
+        </is>
+      </c>
+      <c r="C1768" s="3" t="n">
+        <v>25517</v>
+      </c>
+      <c r="D1768" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1768" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1769" s="3" t="inlineStr">
+        <is>
+          <t>сальник заднего редуктора</t>
+        </is>
+      </c>
+      <c r="C1769" s="3" t="n">
+        <v>21405</v>
+      </c>
+      <c r="D1769" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1769" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1770" s="3" t="inlineStr">
+        <is>
+          <t>полумуфта</t>
+        </is>
+      </c>
+      <c r="C1770" s="3" t="n">
+        <v>15694</v>
+      </c>
+      <c r="D1770" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1770" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1771" s="3" t="inlineStr">
+        <is>
+          <t>передаточное число редуктора</t>
+        </is>
+      </c>
+      <c r="C1771" s="3" t="n">
+        <v>15445</v>
+      </c>
+      <c r="D1771" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1771" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1772" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников редуктора</t>
+        </is>
+      </c>
+      <c r="C1772" s="3" t="n">
+        <v>15435</v>
+      </c>
+      <c r="D1772" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1772" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1773" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника редуктора</t>
+        </is>
+      </c>
+      <c r="C1773" s="3" t="n">
+        <v>15432</v>
+      </c>
+      <c r="D1773" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1773" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1774" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов</t>
+        </is>
+      </c>
+      <c r="C1774" s="3" t="n">
+        <v>15431</v>
+      </c>
+      <c r="D1774" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1774" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1775" s="3" t="inlineStr">
+        <is>
+          <t>шкив распредвала</t>
+        </is>
+      </c>
+      <c r="C1775" s="3" t="n">
+        <v>15143</v>
+      </c>
+      <c r="D1775" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1775" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1776" s="3" t="inlineStr">
+        <is>
+          <t>коленвал и распредвал</t>
+        </is>
+      </c>
+      <c r="C1776" s="3" t="n">
+        <v>13729</v>
+      </c>
+      <c r="D1776" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1776" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1777" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников заднего коленвала</t>
+        </is>
+      </c>
+      <c r="C1777" s="3" t="n">
+        <v>12941</v>
+      </c>
+      <c r="D1777" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1777" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1778" s="3" t="inlineStr">
+        <is>
+          <t>замена заднего сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C1778" s="3" t="n">
+        <v>12939</v>
+      </c>
+      <c r="D1778" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1778" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1779" s="3" t="inlineStr">
+        <is>
+          <t>замена переднего сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C1779" s="3" t="n">
+        <v>12910</v>
+      </c>
+      <c r="D1779" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1779" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1780" s="3" t="inlineStr">
+        <is>
+          <t>замена передних сальников коленвала</t>
+        </is>
+      </c>
+      <c r="C1780" s="3" t="n">
+        <v>12910</v>
+      </c>
+      <c r="D1780" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1780" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1781" s="3" t="inlineStr">
+        <is>
+          <t>фланец редуктора</t>
+        </is>
+      </c>
+      <c r="C1781" s="3" t="n">
+        <v>12469</v>
+      </c>
+      <c r="D1781" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1781" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1782" s="3" t="inlineStr">
+        <is>
+          <t>редуктор автомобиля</t>
+        </is>
+      </c>
+      <c r="C1782" s="3" t="n">
+        <v>10716</v>
+      </c>
+      <c r="D1782" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1782" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1783" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника распредвала</t>
+        </is>
+      </c>
+      <c r="C1783" s="3" t="n">
+        <v>10469</v>
+      </c>
+      <c r="D1783" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1783" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1784" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников распредвала</t>
+        </is>
+      </c>
+      <c r="C1784" s="3" t="n">
+        <v>10469</v>
+      </c>
+      <c r="D1784" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1784" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1785" s="3" t="inlineStr">
+        <is>
+          <t>бугель распредвала</t>
+        </is>
+      </c>
+      <c r="C1785" s="3" t="n">
+        <v>9620</v>
+      </c>
+      <c r="D1785" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1785" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1786" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп</t>
+        </is>
+      </c>
+      <c r="C1786" s="3" t="n">
+        <v>9608</v>
+      </c>
+      <c r="D1786" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1786" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1787" s="3" t="inlineStr">
+        <is>
+          <t>сальник переднего редуктора</t>
+        </is>
+      </c>
+      <c r="C1787" s="3" t="n">
+        <v>9500</v>
+      </c>
+      <c r="D1787" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1787" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1788" s="3" t="inlineStr">
+        <is>
+          <t>сальник хвостовика редуктора</t>
+        </is>
+      </c>
+      <c r="C1788" s="3" t="n">
+        <v>9359</v>
+      </c>
+      <c r="D1788" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1788" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1789" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора моста</t>
+        </is>
+      </c>
+      <c r="C1789" s="3" t="n">
+        <v>7738</v>
+      </c>
+      <c r="D1789" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1789" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1790" s="3" t="inlineStr">
+        <is>
+          <t>сапун редуктора</t>
+        </is>
+      </c>
+      <c r="C1790" s="3" t="n">
+        <v>5924</v>
+      </c>
+      <c r="D1790" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1790" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1791" s="3" t="inlineStr">
+        <is>
+          <t>редуктор авто</t>
+        </is>
+      </c>
+      <c r="C1791" s="3" t="n">
+        <v>5914</v>
+      </c>
+      <c r="D1791" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1791" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1792" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника заднего редуктора</t>
+        </is>
+      </c>
+      <c r="C1792" s="3" t="n">
+        <v>5740</v>
+      </c>
+      <c r="D1792" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1792" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1793" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников заднего редуктора</t>
+        </is>
+      </c>
+      <c r="C1793" s="3" t="n">
+        <v>5740</v>
+      </c>
+      <c r="D1793" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1793" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1794" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора заднего моста</t>
+        </is>
+      </c>
+      <c r="C1794" s="3" t="n">
+        <v>5431</v>
+      </c>
+      <c r="D1794" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1794" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1795" s="3" t="inlineStr">
+        <is>
+          <t>сальник рулевого редуктора</t>
+        </is>
+      </c>
+      <c r="C1795" s="3" t="n">
+        <v>5283</v>
+      </c>
+      <c r="D1795" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1795" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1796" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала ваз</t>
+        </is>
+      </c>
+      <c r="C1796" s="3" t="n">
+        <v>4720</v>
+      </c>
+      <c r="D1796" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1796" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1797" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника первичного вала</t>
+        </is>
+      </c>
+      <c r="C1797" s="3" t="n">
+        <v>4486</v>
+      </c>
+      <c r="D1797" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1797" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1798" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников первичного вала</t>
+        </is>
+      </c>
+      <c r="C1798" s="3" t="n">
+        <v>4486</v>
+      </c>
+      <c r="D1798" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1798" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1799" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора газель</t>
+        </is>
+      </c>
+      <c r="C1799" s="3" t="n">
+        <v>4296</v>
+      </c>
+      <c r="D1799" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1799" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1800" s="3" t="inlineStr">
+        <is>
+          <t>редукторное мотор колесо</t>
+        </is>
+      </c>
+      <c r="C1800" s="3" t="n">
+        <v>4270</v>
+      </c>
+      <c r="D1800" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1800" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1801" s="3" t="inlineStr">
+        <is>
+          <t>редуктор в машине</t>
+        </is>
+      </c>
+      <c r="C1801" s="3" t="n">
+        <v>4010</v>
+      </c>
+      <c r="D1801" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1801" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1802" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала рено</t>
+        </is>
+      </c>
+      <c r="C1802" s="3" t="n">
+        <v>3953</v>
+      </c>
+      <c r="D1802" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1802" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1803" s="3" t="inlineStr">
+        <is>
+          <t>размер сальника редуктора</t>
+        </is>
+      </c>
+      <c r="C1803" s="3" t="n">
+        <v>3945</v>
+      </c>
+      <c r="D1803" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1803" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1804" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала 1.6</t>
+        </is>
+      </c>
+      <c r="C1804" s="3" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D1804" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1804" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1805" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора нива</t>
+        </is>
+      </c>
+      <c r="C1805" s="3" t="n">
+        <v>3903</v>
+      </c>
+      <c r="D1805" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1805" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1806" s="3" t="inlineStr">
+        <is>
+          <t>сальник хвостовика заднего редуктора</t>
+        </is>
+      </c>
+      <c r="C1806" s="3" t="n">
+        <v>3571</v>
+      </c>
+      <c r="D1806" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1806" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1807" s="3" t="inlineStr">
+        <is>
+          <t>размер сальника распредвала</t>
+        </is>
+      </c>
+      <c r="C1807" s="3" t="n">
+        <v>3386</v>
+      </c>
+      <c r="D1807" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1807" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1808" s="3" t="inlineStr">
+        <is>
+          <t>2 сальника распредвала</t>
+        </is>
+      </c>
+      <c r="C1808" s="3" t="n">
+        <v>3345</v>
+      </c>
+      <c r="D1808" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1808" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1809" s="3" t="inlineStr">
+        <is>
+          <t>сальник привода редуктора</t>
+        </is>
+      </c>
+      <c r="C1809" s="3" t="n">
+        <v>3173</v>
+      </c>
+      <c r="D1809" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1809" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1810" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора ваз</t>
+        </is>
+      </c>
+      <c r="C1810" s="3" t="n">
+        <v>2884</v>
+      </c>
+      <c r="D1810" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1810" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1811" s="3" t="inlineStr">
+        <is>
+          <t>сальники коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C1811" s="3" t="n">
+        <v>2836</v>
+      </c>
+      <c r="D1811" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1811" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1812" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора камаз</t>
+        </is>
+      </c>
+      <c r="C1812" s="3" t="n">
+        <v>2697</v>
+      </c>
+      <c r="D1812" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1812" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1813" s="3" t="inlineStr">
+        <is>
+          <t>купить сальник редуктора</t>
+        </is>
+      </c>
+      <c r="C1813" s="3" t="n">
+        <v>2692</v>
+      </c>
+      <c r="D1813" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1813" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1814" s="3" t="inlineStr">
+        <is>
+          <t>сальник углового редуктора</t>
+        </is>
+      </c>
+      <c r="C1814" s="3" t="n">
+        <v>2555</v>
+      </c>
+      <c r="D1814" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1814" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1815" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала ваз</t>
+        </is>
+      </c>
+      <c r="C1815" s="3" t="n">
+        <v>2528</v>
+      </c>
+      <c r="D1815" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1815" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1816" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников коленвала ваз</t>
+        </is>
+      </c>
+      <c r="C1816" s="3" t="n">
+        <v>2528</v>
+      </c>
+      <c r="D1816" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1816" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1817" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала двигатель</t>
+        </is>
+      </c>
+      <c r="C1817" s="3" t="n">
+        <v>2465</v>
+      </c>
+      <c r="D1817" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1817" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1818" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала 1</t>
+        </is>
+      </c>
+      <c r="C1818" s="3" t="n">
+        <v>2389</v>
+      </c>
+      <c r="D1818" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1818" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1819" s="3" t="inlineStr">
+        <is>
+          <t>редуктор высокого давления</t>
+        </is>
+      </c>
+      <c r="C1819" s="3" t="n">
+        <v>2354</v>
+      </c>
+      <c r="D1819" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1819" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1820" s="3" t="inlineStr">
+        <is>
+          <t>поменять сальник редуктора</t>
+        </is>
+      </c>
+      <c r="C1820" s="3" t="n">
+        <v>2316</v>
+      </c>
+      <c r="D1820" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1820" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1821" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала 8 клапанов</t>
+        </is>
+      </c>
+      <c r="C1821" s="3" t="n">
+        <v>2229</v>
+      </c>
+      <c r="D1821" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1821" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1822" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника переднего редуктора</t>
+        </is>
+      </c>
+      <c r="C1822" s="3" t="n">
+        <v>2146</v>
+      </c>
+      <c r="D1822" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1822" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1823" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников переднего редуктора</t>
+        </is>
+      </c>
+      <c r="C1823" s="3" t="n">
+        <v>2146</v>
+      </c>
+      <c r="D1823" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1823" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1824" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала мкпп</t>
+        </is>
+      </c>
+      <c r="C1824" s="3" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D1824" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1824" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1825" s="3" t="inlineStr">
+        <is>
+          <t>сальники на редуктор мотоблока</t>
+        </is>
+      </c>
+      <c r="C1825" s="3" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D1825" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1825" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1826" s="3" t="inlineStr">
+        <is>
+          <t>сальники распредвалов к4м</t>
+        </is>
+      </c>
+      <c r="C1826" s="3" t="n">
+        <v>1968</v>
+      </c>
+      <c r="D1826" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1826" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1827" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала 1.8</t>
+        </is>
+      </c>
+      <c r="C1827" s="3" t="n">
+        <v>1942</v>
+      </c>
+      <c r="D1827" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1827" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1828" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала гранта</t>
+        </is>
+      </c>
+      <c r="C1828" s="3" t="n">
+        <v>1924</v>
+      </c>
+      <c r="D1828" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1828" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1829" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала веста</t>
+        </is>
+      </c>
+      <c r="C1829" s="3" t="n">
+        <v>1907</v>
+      </c>
+      <c r="D1829" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1829" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1830" s="3" t="inlineStr">
+        <is>
+          <t>сальник мотор редуктора</t>
+        </is>
+      </c>
+      <c r="C1830" s="3" t="n">
+        <v>1884</v>
+      </c>
+      <c r="D1830" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1830" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1831" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала форд</t>
+        </is>
+      </c>
+      <c r="C1831" s="3" t="n">
+        <v>1877</v>
+      </c>
+      <c r="D1831" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1831" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1832" s="3" t="inlineStr">
+        <is>
+          <t>сальник коробки первичного вала</t>
+        </is>
+      </c>
+      <c r="C1832" s="3" t="n">
+        <v>1842</v>
+      </c>
+      <c r="D1832" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1832" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1833" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала лада</t>
+        </is>
+      </c>
+      <c r="C1833" s="3" t="n">
+        <v>1836</v>
+      </c>
+      <c r="D1833" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1833" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1834" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала ваз</t>
+        </is>
+      </c>
+      <c r="C1834" s="3" t="n">
+        <v>1821</v>
+      </c>
+      <c r="D1834" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1834" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1835" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала рено</t>
+        </is>
+      </c>
+      <c r="C1835" s="3" t="n">
+        <v>1770</v>
+      </c>
+      <c r="D1835" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1835" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1836" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников коленвала рено</t>
+        </is>
+      </c>
+      <c r="C1836" s="3" t="n">
+        <v>1770</v>
+      </c>
+      <c r="D1836" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1836" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1837" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника хвостовика редуктора</t>
+        </is>
+      </c>
+      <c r="C1837" s="3" t="n">
+        <v>1721</v>
+      </c>
+      <c r="D1837" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1837" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1838" s="3" t="inlineStr">
+        <is>
+          <t>сальник привода заднего редуктора</t>
+        </is>
+      </c>
+      <c r="C1838" s="3" t="n">
+        <v>1660</v>
+      </c>
+      <c r="D1838" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1838" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1839" s="3" t="inlineStr">
+        <is>
+          <t>сальник заднего редуктора нива</t>
+        </is>
+      </c>
+      <c r="C1839" s="3" t="n">
+        <v>1628</v>
+      </c>
+      <c r="D1839" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1839" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1840" s="3" t="inlineStr">
+        <is>
+          <t>сальник лодочного редуктора</t>
+        </is>
+      </c>
+      <c r="C1840" s="3" t="n">
+        <v>1613</v>
+      </c>
+      <c r="D1840" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1840" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1841" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала шевроле</t>
+        </is>
+      </c>
+      <c r="C1841" s="3" t="n">
+        <v>1599</v>
+      </c>
+      <c r="D1841" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1841" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1842" s="3" t="inlineStr">
+        <is>
+          <t>передние сальники распредвала</t>
+        </is>
+      </c>
+      <c r="C1842" s="3" t="n">
+        <v>1591</v>
+      </c>
+      <c r="D1842" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1842" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1843" s="3" t="inlineStr">
+        <is>
+          <t>кольцо датчика распредвала</t>
+        </is>
+      </c>
+      <c r="C1843" s="3" t="n">
+        <v>1576</v>
+      </c>
+      <c r="D1843" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1843" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1844" s="3" t="inlineStr">
+        <is>
+          <t>сальник хвостовика переднего редуктора</t>
+        </is>
+      </c>
+      <c r="C1844" s="3" t="n">
+        <v>1561</v>
+      </c>
+      <c r="D1844" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1844" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1845" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора лодочного мотора</t>
+        </is>
+      </c>
+      <c r="C1845" s="3" t="n">
+        <v>1560</v>
+      </c>
+      <c r="D1845" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1845" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1846" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала шевроле</t>
+        </is>
+      </c>
+      <c r="C1846" s="3" t="n">
+        <v>1521</v>
+      </c>
+      <c r="D1846" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1846" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1847" s="3" t="inlineStr">
+        <is>
+          <t>сальник вала редуктора</t>
+        </is>
+      </c>
+      <c r="C1847" s="3" t="n">
+        <v>1518</v>
+      </c>
+      <c r="D1847" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1847" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1848" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала логан</t>
+        </is>
+      </c>
+      <c r="C1848" s="3" t="n">
+        <v>1498</v>
+      </c>
+      <c r="D1848" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1848" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1849" s="3" t="inlineStr">
+        <is>
+          <t>сальник заднего редуктора газель</t>
+        </is>
+      </c>
+      <c r="C1849" s="3" t="n">
+        <v>1493</v>
+      </c>
+      <c r="D1849" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1849" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1850" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников коленвала цена</t>
+        </is>
+      </c>
+      <c r="C1850" s="3" t="n">
+        <v>1480</v>
+      </c>
+      <c r="D1850" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1850" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1851" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала цена</t>
+        </is>
+      </c>
+      <c r="C1851" s="3" t="n">
+        <v>1478</v>
+      </c>
+      <c r="D1851" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1851" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1852" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника первичного вала кпп</t>
+        </is>
+      </c>
+      <c r="C1852" s="3" t="n">
+        <v>1476</v>
+      </c>
+      <c r="D1852" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1852" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1853" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора уаз</t>
+        </is>
+      </c>
+      <c r="C1853" s="3" t="n">
+        <v>1443</v>
+      </c>
+      <c r="D1853" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1853" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1854" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала опель</t>
+        </is>
+      </c>
+      <c r="C1854" s="3" t="n">
+        <v>1398</v>
+      </c>
+      <c r="D1854" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1854" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1855" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала 2108</t>
+        </is>
+      </c>
+      <c r="C1855" s="3" t="n">
+        <v>1377</v>
+      </c>
+      <c r="D1855" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1855" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1856" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора 2107</t>
+        </is>
+      </c>
+      <c r="C1856" s="3" t="n">
+        <v>1370</v>
+      </c>
+      <c r="D1856" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1856" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1857" s="3" t="inlineStr">
+        <is>
+          <t>сальник коленвала опель замена</t>
+        </is>
+      </c>
+      <c r="C1857" s="3" t="n">
+        <v>1366</v>
+      </c>
+      <c r="D1857" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1857" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1858" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала форд</t>
+        </is>
+      </c>
+      <c r="C1858" s="3" t="n">
+        <v>1357</v>
+      </c>
+      <c r="D1858" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1858" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1859" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала приора</t>
+        </is>
+      </c>
+      <c r="C1859" s="3" t="n">
+        <v>1345</v>
+      </c>
+      <c r="D1859" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1859" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1860" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора шевроле нива</t>
+        </is>
+      </c>
+      <c r="C1860" s="3" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D1860" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1860" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1861" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника редуктора моста</t>
+        </is>
+      </c>
+      <c r="C1861" s="3" t="n">
+        <v>1329</v>
+      </c>
+      <c r="D1861" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1861" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1862" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора переднего моста</t>
+        </is>
+      </c>
+      <c r="C1862" s="3" t="n">
+        <v>1328</v>
+      </c>
+      <c r="D1862" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1862" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1863" s="3" t="inlineStr">
+        <is>
+          <t>размер сальника первичного вала</t>
+        </is>
+      </c>
+      <c r="C1863" s="3" t="n">
+        <v>1326</v>
+      </c>
+      <c r="D1863" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1863" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1864" s="3" t="inlineStr">
+        <is>
+          <t>номер сальника редуктора</t>
+        </is>
+      </c>
+      <c r="C1864" s="3" t="n">
+        <v>1308</v>
+      </c>
+      <c r="D1864" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1864" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1865" s="3" t="inlineStr">
+        <is>
+          <t>сальник переднего редуктора нива</t>
+        </is>
+      </c>
+      <c r="C1865" s="3" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D1865" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1865" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1866" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала ниссан</t>
+        </is>
+      </c>
+      <c r="C1866" s="3" t="n">
+        <v>1285</v>
+      </c>
+      <c r="D1866" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1866" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1867" s="3" t="inlineStr">
+        <is>
+          <t>купить сальник распредвала</t>
+        </is>
+      </c>
+      <c r="C1867" s="3" t="n">
+        <v>1284</v>
+      </c>
+      <c r="D1867" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1867" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1868" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника рулевого редуктора</t>
+        </is>
+      </c>
+      <c r="C1868" s="3" t="n">
+        <v>1257</v>
+      </c>
+      <c r="D1868" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1868" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1869" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников рулевого редуктора</t>
+        </is>
+      </c>
+      <c r="C1869" s="3" t="n">
+        <v>1257</v>
+      </c>
+      <c r="D1869" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1869" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1870" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала дастер</t>
+        </is>
+      </c>
+      <c r="C1870" s="3" t="n">
+        <v>1252</v>
+      </c>
+      <c r="D1870" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1870" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1871" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора бмв</t>
+        </is>
+      </c>
+      <c r="C1871" s="3" t="n">
+        <v>1241</v>
+      </c>
+      <c r="D1871" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1871" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1872" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала акпп</t>
+        </is>
+      </c>
+      <c r="C1872" s="3" t="n">
+        <v>1215</v>
+      </c>
+      <c r="D1872" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1872" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1873" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора ваз 2107</t>
+        </is>
+      </c>
+      <c r="C1873" s="3" t="n">
+        <v>1213</v>
+      </c>
+      <c r="D1873" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1873" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1874" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала киа</t>
+        </is>
+      </c>
+      <c r="C1874" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D1874" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1874" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1875" s="3" t="inlineStr">
+        <is>
+          <t>заменить сальник редуктора</t>
+        </is>
+      </c>
+      <c r="C1875" s="3" t="n">
+        <v>1196</v>
+      </c>
+      <c r="D1875" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1875" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1876" s="3" t="inlineStr">
+        <is>
+          <t>сальники редуктора заднего ваз</t>
+        </is>
+      </c>
+      <c r="C1876" s="3" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D1876" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1876" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1877" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала рено</t>
+        </is>
+      </c>
+      <c r="C1877" s="3" t="n">
+        <v>1183</v>
+      </c>
+      <c r="D1877" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1877" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1878" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала хендай</t>
+        </is>
+      </c>
+      <c r="C1878" s="3" t="n">
+        <v>1167</v>
+      </c>
+      <c r="D1878" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1878" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1879" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала нива</t>
+        </is>
+      </c>
+      <c r="C1879" s="3" t="n">
+        <v>1166</v>
+      </c>
+      <c r="D1879" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1879" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1880" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала ларгус</t>
+        </is>
+      </c>
+      <c r="C1880" s="3" t="n">
+        <v>1147</v>
+      </c>
+      <c r="D1880" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1880" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1881" s="3" t="inlineStr">
+        <is>
+          <t>сальник бортового редуктора</t>
+        </is>
+      </c>
+      <c r="C1881" s="3" t="n">
+        <v>1145</v>
+      </c>
+      <c r="D1881" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1881" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1882" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора некст</t>
+        </is>
+      </c>
+      <c r="C1882" s="3" t="n">
+        <v>1124</v>
+      </c>
+      <c r="D1882" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1882" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1883" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала мазда</t>
+        </is>
+      </c>
+      <c r="C1883" s="3" t="n">
+        <v>1116</v>
+      </c>
+      <c r="D1883" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1883" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1884" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала 2114</t>
+        </is>
+      </c>
+      <c r="C1884" s="3" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D1884" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1884" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1885" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала рено логан</t>
+        </is>
+      </c>
+      <c r="C1885" s="3" t="n">
+        <v>1109</v>
+      </c>
+      <c r="D1885" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1885" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1886" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора урал</t>
+        </is>
+      </c>
+      <c r="C1886" s="3" t="n">
+        <v>1104</v>
+      </c>
+      <c r="D1886" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1886" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1887" s="3" t="inlineStr">
+        <is>
+          <t>сальник редуктора левый</t>
+        </is>
+      </c>
+      <c r="C1887" s="3" t="n">
+        <v>1098</v>
+      </c>
+      <c r="D1887" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1887" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1888" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала фольксваген</t>
+        </is>
+      </c>
+      <c r="C1888" s="3" t="n">
+        <v>1056</v>
+      </c>
+      <c r="D1888" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1888" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1889" s="3" t="inlineStr">
+        <is>
+          <t>как поменять сальник распредвала</t>
+        </is>
+      </c>
+      <c r="C1889" s="3" t="n">
+        <v>1052</v>
+      </c>
+      <c r="D1889" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1889" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1890" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала фокус</t>
+        </is>
+      </c>
+      <c r="C1890" s="3" t="n">
+        <v>1041</v>
+      </c>
+      <c r="D1890" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1890" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1891" s="3" t="inlineStr">
+        <is>
+          <t>сколько сальников распредвала</t>
+        </is>
+      </c>
+      <c r="C1891" s="3" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D1891" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1891" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1892" s="3" t="inlineStr">
+        <is>
+          <t>задний сальник распредвала</t>
+        </is>
+      </c>
+      <c r="C1892" s="3" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D1892" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1892" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1893" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала газель</t>
+        </is>
+      </c>
+      <c r="C1893" s="3" t="n">
+        <v>1017</v>
+      </c>
+      <c r="D1893" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1893" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1894" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала нива</t>
+        </is>
+      </c>
+      <c r="C1894" s="3" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D1894" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1894" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1895" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала форд фокус</t>
+        </is>
+      </c>
+      <c r="C1895" s="3" t="n">
+        <v>982</v>
+      </c>
+      <c r="D1895" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1895" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1896" s="3" t="inlineStr">
+        <is>
+          <t>форд фокус замена сальников коленвала</t>
+        </is>
+      </c>
+      <c r="C1896" s="3" t="n">
+        <v>982</v>
+      </c>
+      <c r="D1896" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1896" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1897" s="3" t="inlineStr">
+        <is>
+          <t>какой сальник на распредвале</t>
+        </is>
+      </c>
+      <c r="C1897" s="3" t="n">
+        <v>967</v>
+      </c>
+      <c r="D1897" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1897" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1898" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала ваз 2114</t>
+        </is>
+      </c>
+      <c r="C1898" s="3" t="n">
+        <v>952</v>
+      </c>
+      <c r="D1898" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1898" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1899" s="3" t="inlineStr">
+        <is>
+          <t>редуктор для компрессора</t>
+        </is>
+      </c>
+      <c r="C1899" s="3" t="n">
+        <v>943</v>
+      </c>
+      <c r="D1899" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1899" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1900" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника распредвала рено</t>
+        </is>
+      </c>
+      <c r="C1900" s="3" t="n">
+        <v>932</v>
+      </c>
+      <c r="D1900" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1900" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1901" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников распредвала рено</t>
+        </is>
+      </c>
+      <c r="C1901" s="3" t="n">
+        <v>932</v>
+      </c>
+      <c r="D1901" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1901" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1902" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала акцент</t>
+        </is>
+      </c>
+      <c r="C1902" s="3" t="n">
+        <v>931</v>
+      </c>
+      <c r="D1902" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1902" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1903" s="3" t="inlineStr">
+        <is>
+          <t>сальники распредвала опель астра</t>
+        </is>
+      </c>
+      <c r="C1903" s="3" t="n">
+        <v>929</v>
+      </c>
+      <c r="D1903" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1903" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1904" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала гранта 8</t>
+        </is>
+      </c>
+      <c r="C1904" s="3" t="n">
+        <v>928</v>
+      </c>
+      <c r="D1904" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1904" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1905" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала тойота</t>
+        </is>
+      </c>
+      <c r="C1905" s="3" t="n">
+        <v>923</v>
+      </c>
+      <c r="D1905" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1905" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1906" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников коленвала тойота</t>
+        </is>
+      </c>
+      <c r="C1906" s="3" t="n">
+        <v>923</v>
+      </c>
+      <c r="D1906" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1906" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1907" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп ваз</t>
+        </is>
+      </c>
+      <c r="C1907" s="3" t="n">
+        <v>922</v>
+      </c>
+      <c r="D1907" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1907" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1908" s="3" t="inlineStr">
+        <is>
+          <t>купить фиксатор распредвалов</t>
+        </is>
+      </c>
+      <c r="C1908" s="3" t="n">
+        <v>912</v>
+      </c>
+      <c r="D1908" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1908" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1909" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала логан</t>
+        </is>
+      </c>
+      <c r="C1909" s="3" t="n">
+        <v>912</v>
+      </c>
+      <c r="D1909" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1909" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1910" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала рено дастер</t>
+        </is>
+      </c>
+      <c r="C1910" s="3" t="n">
+        <v>908</v>
+      </c>
+      <c r="D1910" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1910" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1911" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала калина</t>
+        </is>
+      </c>
+      <c r="C1911" s="3" t="n">
+        <v>882</v>
+      </c>
+      <c r="D1911" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1911" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1912" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала меган</t>
+        </is>
+      </c>
+      <c r="C1912" s="3" t="n">
+        <v>880</v>
+      </c>
+      <c r="D1912" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1912" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1913" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала камаз</t>
+        </is>
+      </c>
+      <c r="C1913" s="3" t="n">
+        <v>870</v>
+      </c>
+      <c r="D1913" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1913" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1914" s="3" t="inlineStr">
+        <is>
+          <t>течь сальника распредвала</t>
+        </is>
+      </c>
+      <c r="C1914" s="3" t="n">
+        <v>867</v>
+      </c>
+      <c r="D1914" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1914" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1915" s="3" t="inlineStr">
+        <is>
+          <t>течь сальников распредвала</t>
+        </is>
+      </c>
+      <c r="C1915" s="3" t="n">
+        <v>867</v>
+      </c>
+      <c r="D1915" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1915" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1916" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала шкода</t>
+        </is>
+      </c>
+      <c r="C1916" s="3" t="n">
+        <v>867</v>
+      </c>
+      <c r="D1916" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1916" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1917" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников коленвала шкода</t>
+        </is>
+      </c>
+      <c r="C1917" s="3" t="n">
+        <v>867</v>
+      </c>
+      <c r="D1917" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1917" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1918" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов веста</t>
+        </is>
+      </c>
+      <c r="C1918" s="3" t="n">
+        <v>855</v>
+      </c>
+      <c r="D1918" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1918" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1919" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала лачетти</t>
+        </is>
+      </c>
+      <c r="C1919" s="3" t="n">
+        <v>839</v>
+      </c>
+      <c r="D1919" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1919" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1920" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала тагаз</t>
+        </is>
+      </c>
+      <c r="C1920" s="3" t="n">
+        <v>836</v>
+      </c>
+      <c r="D1920" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1920" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1921" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала форд фокус</t>
+        </is>
+      </c>
+      <c r="C1921" s="3" t="n">
+        <v>833</v>
+      </c>
+      <c r="D1921" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1921" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1922" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала веста 1.8</t>
+        </is>
+      </c>
+      <c r="C1922" s="3" t="n">
+        <v>827</v>
+      </c>
+      <c r="D1922" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1922" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1923" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала хендай</t>
+        </is>
+      </c>
+      <c r="C1923" s="3" t="n">
+        <v>818</v>
+      </c>
+      <c r="D1923" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1923" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1924" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала видео</t>
+        </is>
+      </c>
+      <c r="C1924" s="3" t="n">
+        <v>816</v>
+      </c>
+      <c r="D1924" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1924" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1925" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала 8 клапанов</t>
+        </is>
+      </c>
+      <c r="C1925" s="3" t="n">
+        <v>811</v>
+      </c>
+      <c r="D1925" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1925" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1926" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала хонда</t>
+        </is>
+      </c>
+      <c r="C1926" s="3" t="n">
+        <v>807</v>
+      </c>
+      <c r="D1926" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1926" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1927" s="3" t="inlineStr">
+        <is>
+          <t>сальник распредвала 16 клапанов артикул</t>
+        </is>
+      </c>
+      <c r="C1927" s="3" t="n">
+        <v>805</v>
+      </c>
+      <c r="D1927" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1927" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1928" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов ваз</t>
+        </is>
+      </c>
+      <c r="C1928" s="3" t="n">
+        <v>805</v>
+      </c>
+      <c r="D1928" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1928" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1929" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов грм</t>
+        </is>
+      </c>
+      <c r="C1929" s="3" t="n">
+        <v>803</v>
+      </c>
+      <c r="D1929" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1929" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1930" s="3" t="inlineStr">
+        <is>
+          <t>как поменять бендикс на стартере</t>
+        </is>
+      </c>
+      <c r="C1930" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="D1930" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1930" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1931" s="3" t="inlineStr">
+        <is>
+          <t>рено логан замена сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C1931" s="3" t="n">
+        <v>792</v>
+      </c>
+      <c r="D1931" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1931" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1932" s="3" t="inlineStr">
+        <is>
+          <t>рено логан замена сальников коленвала</t>
+        </is>
+      </c>
+      <c r="C1932" s="3" t="n">
+        <v>792</v>
+      </c>
+      <c r="D1932" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1932" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1933" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала ауди</t>
+        </is>
+      </c>
+      <c r="C1933" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="D1933" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1933" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1934" s="3" t="inlineStr">
+        <is>
+          <t>грм сальник распредвала</t>
+        </is>
+      </c>
+      <c r="C1934" s="3" t="n">
+        <v>773</v>
+      </c>
+      <c r="D1934" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1934" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1935" s="3" t="inlineStr">
+        <is>
+          <t>набор фиксаторов распредвала</t>
+        </is>
+      </c>
+      <c r="C1935" s="3" t="n">
+        <v>772</v>
+      </c>
+      <c r="D1935" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1935" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1936" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала уаз</t>
+        </is>
+      </c>
+      <c r="C1936" s="3" t="n">
+        <v>764</v>
+      </c>
+      <c r="D1936" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1936" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1937" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала логан</t>
+        </is>
+      </c>
+      <c r="C1937" s="3" t="n">
+        <v>743</v>
+      </c>
+      <c r="D1937" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1937" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1938" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала форд</t>
+        </is>
+      </c>
+      <c r="C1938" s="3" t="n">
+        <v>729</v>
+      </c>
+      <c r="D1938" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1938" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1939" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов 1.8</t>
+        </is>
+      </c>
+      <c r="C1939" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="D1939" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1939" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1940" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала распредвала</t>
+        </is>
+      </c>
+      <c r="C1940" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="D1940" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1940" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1941" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников распредвала коленвала</t>
+        </is>
+      </c>
+      <c r="C1941" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="D1941" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1941" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1942" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала астра</t>
+        </is>
+      </c>
+      <c r="C1942" s="3" t="n">
+        <v>720</v>
+      </c>
+      <c r="D1942" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1942" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1943" s="3" t="inlineStr">
+        <is>
+          <t>после замены сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C1943" s="3" t="n">
+        <v>704</v>
+      </c>
+      <c r="D1943" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1943" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1944" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала 2107</t>
+        </is>
+      </c>
+      <c r="C1944" s="3" t="n">
+        <v>684</v>
+      </c>
+      <c r="D1944" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1944" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1945" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала опель астра</t>
+        </is>
+      </c>
+      <c r="C1945" s="3" t="n">
+        <v>682</v>
+      </c>
+      <c r="D1945" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1945" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1946" s="3" t="inlineStr">
+        <is>
+          <t>замена переднего сальника коленвала двигатель</t>
+        </is>
+      </c>
+      <c r="C1946" s="3" t="n">
+        <v>681</v>
+      </c>
+      <c r="D1946" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1946" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1947" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп газель</t>
+        </is>
+      </c>
+      <c r="C1947" s="3" t="n">
+        <v>676</v>
+      </c>
+      <c r="D1947" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1947" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1948" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала коробки передач</t>
+        </is>
+      </c>
+      <c r="C1948" s="3" t="n">
+        <v>657</v>
+      </c>
+      <c r="D1948" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1948" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1949" s="3" t="inlineStr">
+        <is>
+          <t>замена сальников коленвала стоимость</t>
+        </is>
+      </c>
+      <c r="C1949" s="3" t="n">
+        <v>657</v>
+      </c>
+      <c r="D1949" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1949" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1950" s="3" t="inlineStr">
+        <is>
+          <t>стоимость замены сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C1950" s="3" t="n">
+        <v>657</v>
+      </c>
+      <c r="D1950" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1950" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1951" s="3" t="inlineStr">
+        <is>
+          <t>поменять сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="C1951" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="D1951" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1951" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1952" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов рено</t>
+        </is>
+      </c>
+      <c r="C1952" s="3" t="n">
+        <v>649</v>
+      </c>
+      <c r="D1952" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1952" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1953" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп нива</t>
+        </is>
+      </c>
+      <c r="C1953" s="3" t="n">
+        <v>645</v>
+      </c>
+      <c r="D1953" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1953" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1954" s="3" t="inlineStr">
+        <is>
+          <t>сколько стоит замена сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C1954" s="3" t="n">
+        <v>642</v>
+      </c>
+      <c r="D1954" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1954" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1955" s="3" t="inlineStr">
+        <is>
+          <t>сколько стоит замена сальников коленвала</t>
+        </is>
+      </c>
+      <c r="C1955" s="3" t="n">
+        <v>642</v>
+      </c>
+      <c r="D1955" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1955" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1956" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала поло</t>
+        </is>
+      </c>
+      <c r="C1956" s="3" t="n">
+        <v>632</v>
+      </c>
+      <c r="D1956" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1956" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1957" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала рено логан</t>
+        </is>
+      </c>
+      <c r="C1957" s="3" t="n">
+        <v>628</v>
+      </c>
+      <c r="D1957" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1957" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1958" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала ваз 2107</t>
+        </is>
+      </c>
+      <c r="C1958" s="3" t="n">
+        <v>624</v>
+      </c>
+      <c r="D1958" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1958" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1959" s="3" t="inlineStr">
+        <is>
+          <t>замена переднего сальника коленвала ваз</t>
+        </is>
+      </c>
+      <c r="C1959" s="3" t="n">
+        <v>622</v>
+      </c>
+      <c r="D1959" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1959" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1960" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника коленвала газель</t>
+        </is>
+      </c>
+      <c r="C1960" s="3" t="n">
+        <v>615</v>
+      </c>
+      <c r="D1960" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1960" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1961" s="3" t="inlineStr">
+        <is>
+          <t>размер сальника кпп первичного вала</t>
+        </is>
+      </c>
+      <c r="C1961" s="3" t="n">
+        <v>604</v>
+      </c>
+      <c r="D1961" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1961" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1962" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала поло</t>
+        </is>
+      </c>
+      <c r="C1962" s="3" t="n">
+        <v>593</v>
+      </c>
+      <c r="D1962" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1962" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1963" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала коленвала</t>
+        </is>
+      </c>
+      <c r="C1963" s="3" t="n">
+        <v>578</v>
+      </c>
+      <c r="D1963" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1963" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1964" s="3" t="inlineStr">
+        <is>
+          <t>купить сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="C1964" s="3" t="n">
+        <v>570</v>
+      </c>
+      <c r="D1964" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1964" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1965" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп камаз</t>
+        </is>
+      </c>
+      <c r="C1965" s="3" t="n">
+        <v>569</v>
+      </c>
+      <c r="D1965" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1965" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1966" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала лачетти</t>
+        </is>
+      </c>
+      <c r="C1966" s="3" t="n">
+        <v>533</v>
+      </c>
+      <c r="D1966" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1966" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1967" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов форд</t>
+        </is>
+      </c>
+      <c r="C1967" s="3" t="n">
+        <v>523</v>
+      </c>
+      <c r="D1967" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1967" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1968" s="3" t="inlineStr">
+        <is>
+          <t>фиксаторы распредвалов шкода</t>
+        </is>
+      </c>
+      <c r="C1968" s="3" t="n">
+        <v>522</v>
+      </c>
+      <c r="D1968" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1968" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1969" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп рено</t>
+        </is>
+      </c>
+      <c r="C1969" s="3" t="n">
+        <v>517</v>
+      </c>
+      <c r="D1969" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1969" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1970" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп уаз</t>
+        </is>
+      </c>
+      <c r="C1970" s="3" t="n">
+        <v>506</v>
+      </c>
+      <c r="D1970" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1970" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1971" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника первичного вала ваз</t>
+        </is>
+      </c>
+      <c r="C1971" s="3" t="n">
+        <v>498</v>
+      </c>
+      <c r="D1971" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1971" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1972" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов веста 1.8</t>
+        </is>
+      </c>
+      <c r="C1972" s="3" t="n">
+        <v>491</v>
+      </c>
+      <c r="D1972" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1972" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1973" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов фольксваген</t>
+        </is>
+      </c>
+      <c r="C1973" s="3" t="n">
+        <v>491</v>
+      </c>
+      <c r="D1973" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1973" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1974" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала киа</t>
+        </is>
+      </c>
+      <c r="C1974" s="3" t="n">
+        <v>487</v>
+      </c>
+      <c r="D1974" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1974" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1975" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала ямз</t>
+        </is>
+      </c>
+      <c r="C1975" s="3" t="n">
+        <v>473</v>
+      </c>
+      <c r="D1975" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1975" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1976" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала форд фокус</t>
+        </is>
+      </c>
+      <c r="C1976" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="D1976" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1976" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1977" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор шестерни распредвала</t>
+        </is>
+      </c>
+      <c r="C1977" s="3" t="n">
+        <v>460</v>
+      </c>
+      <c r="D1977" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1977" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1978" s="3" t="inlineStr">
+        <is>
+          <t>втулка первичного вала кпп</t>
+        </is>
+      </c>
+      <c r="C1978" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1978" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1978" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1979" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов опель</t>
+        </is>
+      </c>
+      <c r="C1979" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="D1979" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1979" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1980" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала лада</t>
+        </is>
+      </c>
+      <c r="C1980" s="3" t="n">
+        <v>422</v>
+      </c>
+      <c r="D1980" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1980" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1981" s="3" t="inlineStr">
+        <is>
+          <t>размеры фиксаторов распредвалов</t>
+        </is>
+      </c>
+      <c r="C1981" s="3" t="n">
+        <v>418</v>
+      </c>
+      <c r="D1981" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1981" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1982" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп 2107</t>
+        </is>
+      </c>
+      <c r="C1982" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="D1982" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1982" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1983" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала ларгус</t>
+        </is>
+      </c>
+      <c r="C1983" s="3" t="n">
+        <v>414</v>
+      </c>
+      <c r="D1983" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1983" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1984" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала 2110</t>
+        </is>
+      </c>
+      <c r="C1984" s="3" t="n">
+        <v>413</v>
+      </c>
+      <c r="D1984" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1984" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1985" s="3" t="inlineStr">
+        <is>
+          <t>замена сальника первичного вала мкпп</t>
+        </is>
+      </c>
+      <c r="C1985" s="3" t="n">
+        <v>406</v>
+      </c>
+      <c r="D1985" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1985" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1986" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала нива шевроле</t>
+        </is>
+      </c>
+      <c r="C1986" s="3" t="n">
+        <v>404</v>
+      </c>
+      <c r="D1986" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1986" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1987" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор шкива распредвала</t>
+        </is>
+      </c>
+      <c r="C1987" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="D1987" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1987" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1988" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов cfna</t>
+        </is>
+      </c>
+      <c r="C1988" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="D1988" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1988" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1989" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов 16 клапанов</t>
+        </is>
+      </c>
+      <c r="C1989" s="3" t="n">
+        <v>393</v>
+      </c>
+      <c r="D1989" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1989" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1990" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов к4м</t>
+        </is>
+      </c>
+      <c r="C1990" s="3" t="n">
+        <v>393</v>
+      </c>
+      <c r="D1990" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1990" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1991" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп ваз 2107</t>
+        </is>
+      </c>
+      <c r="C1991" s="3" t="n">
+        <v>383</v>
+      </c>
+      <c r="D1991" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1991" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1992" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп логан</t>
+        </is>
+      </c>
+      <c r="C1992" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="D1992" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1992" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1993" s="3" t="inlineStr">
+        <is>
+          <t>замена сальник коробки первичного вала</t>
+        </is>
+      </c>
+      <c r="C1993" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="D1993" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1993" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1994" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов ваз 16</t>
+        </is>
+      </c>
+      <c r="C1994" s="3" t="n">
+        <v>368</v>
+      </c>
+      <c r="D1994" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1994" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1995" s="3" t="inlineStr">
+        <is>
+          <t>номер сальника первичного вала</t>
+        </is>
+      </c>
+      <c r="C1995" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="D1995" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1995" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1996" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов лада</t>
+        </is>
+      </c>
+      <c r="C1996" s="3" t="n">
+        <v>362</v>
+      </c>
+      <c r="D1996" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1996" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1997" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала гранта</t>
+        </is>
+      </c>
+      <c r="C1997" s="3" t="n">
+        <v>358</v>
+      </c>
+      <c r="D1997" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1997" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1998" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов vag</t>
+        </is>
+      </c>
+      <c r="C1998" s="3" t="n">
+        <v>356</v>
+      </c>
+      <c r="D1998" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1998" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B1999" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала поло 1.6</t>
+        </is>
+      </c>
+      <c r="C1999" s="3" t="n">
+        <v>353</v>
+      </c>
+      <c r="D1999" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E1999" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2000" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов универсальный</t>
+        </is>
+      </c>
+      <c r="C2000" s="3" t="n">
+        <v>345</v>
+      </c>
+      <c r="D2000" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2000" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2001" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала кпп рено логан</t>
+        </is>
+      </c>
+      <c r="C2001" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="D2001" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2001" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2002" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала солярис</t>
+        </is>
+      </c>
+      <c r="C2002" s="3" t="n">
+        <v>334</v>
+      </c>
+      <c r="D2002" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2002" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2003" s="3" t="inlineStr">
+        <is>
+          <t>сальник крышки первичного вала</t>
+        </is>
+      </c>
+      <c r="C2003" s="3" t="n">
+        <v>333</v>
+      </c>
+      <c r="D2003" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2003" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2004" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала газ</t>
+        </is>
+      </c>
+      <c r="C2004" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="D2004" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2004" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2005" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов вольво</t>
+        </is>
+      </c>
+      <c r="C2005" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="D2005" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2005" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2006" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов фольксваген поло</t>
+        </is>
+      </c>
+      <c r="C2006" s="3" t="n">
+        <v>308</v>
+      </c>
+      <c r="D2006" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2006" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2007" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов ваз 16 клапанов</t>
+        </is>
+      </c>
+      <c r="C2007" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="D2007" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2007" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2008" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала ауди</t>
+        </is>
+      </c>
+      <c r="C2008" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="D2008" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2008" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2009" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов форд фокус</t>
+        </is>
+      </c>
+      <c r="C2009" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="D2009" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2009" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2010" s="3" t="inlineStr">
+        <is>
+          <t>подшипник первичного вала признаки неисправности</t>
+        </is>
+      </c>
+      <c r="C2010" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="D2010" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2010" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2011" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала шевроле</t>
+        </is>
+      </c>
+      <c r="C2011" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="D2011" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2011" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2012" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов cfna 1.6</t>
+        </is>
+      </c>
+      <c r="C2012" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="D2012" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2012" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2013" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов дастер</t>
+        </is>
+      </c>
+      <c r="C2013" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="D2013" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2013" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2014" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов своими руками</t>
+        </is>
+      </c>
+      <c r="C2014" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="D2014" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2014" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2015" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала f4r</t>
+        </is>
+      </c>
+      <c r="C2015" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="D2015" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2015" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2016" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала 1.2</t>
+        </is>
+      </c>
+      <c r="C2016" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="D2016" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2016" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2017" s="3" t="inlineStr">
+        <is>
+          <t>подшипник первичного вала акпп</t>
+        </is>
+      </c>
+      <c r="C2017" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="D2017" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2017" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2018" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов поло седан</t>
+        </is>
+      </c>
+      <c r="C2018" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2018" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2018" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2019" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов фольксваген 1.6</t>
+        </is>
+      </c>
+      <c r="C2019" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="D2019" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2019" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2020" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов лада веста</t>
+        </is>
+      </c>
+      <c r="C2020" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="D2020" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2020" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2021" s="3" t="inlineStr">
+        <is>
+          <t>фиксаторы распредвалов лады веста</t>
+        </is>
+      </c>
+      <c r="C2021" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="D2021" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2021" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2022" s="3" t="inlineStr">
+        <is>
+          <t>фиксаторы распредвалов опель астра</t>
+        </is>
+      </c>
+      <c r="C2022" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="D2022" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2022" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2023" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов tsi</t>
+        </is>
+      </c>
+      <c r="C2023" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="D2023" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2023" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2024" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала фольксваген поло 1.6</t>
+        </is>
+      </c>
+      <c r="C2024" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="D2024" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2024" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2025" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов киа</t>
+        </is>
+      </c>
+      <c r="C2025" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="D2025" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2025" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2026" s="3" t="inlineStr">
+        <is>
+          <t>набор фиксаторов распредвала для установки фаз</t>
+        </is>
+      </c>
+      <c r="C2026" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="D2026" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2026" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2027" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвалов чертежи</t>
+        </is>
+      </c>
+      <c r="C2027" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="D2027" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2027" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2028" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала пежо</t>
+        </is>
+      </c>
+      <c r="C2028" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="D2028" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2028" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2029" s="3" t="inlineStr">
+        <is>
+          <t>планка фиксатор распредвала</t>
+        </is>
+      </c>
+      <c r="C2029" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="D2029" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2029" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2030" s="3" t="inlineStr">
+        <is>
+          <t>фиксатор распредвала для установки фаз грм</t>
+        </is>
+      </c>
+      <c r="C2030" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="D2030" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2030" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2031" s="3" t="inlineStr">
+        <is>
+          <t>сальник коленвала передний камаз евро 2</t>
+        </is>
+      </c>
+      <c r="C2031" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="D2031" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2031" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2032" s="3" t="inlineStr">
+        <is>
+          <t>реверс редуктор для мотоблока</t>
+        </is>
+      </c>
+      <c r="C2032" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D2032" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2032" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2033" s="3" t="inlineStr">
+        <is>
+          <t>съемник и установщик ремня на шкив</t>
+        </is>
+      </c>
+      <c r="C2033" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D2033" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2033" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2034" s="3" t="inlineStr">
+        <is>
+          <t>съемник шестерни распредвала газель</t>
+        </is>
+      </c>
+      <c r="C2034" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="D2034" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2034" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="3" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+      <c r="B2035" s="3" t="inlineStr">
+        <is>
+          <t>как поменять втулку распредвала на мтз 82</t>
+        </is>
+      </c>
+      <c r="C2035" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="D2035" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2035" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2036" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C2036" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D2036" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2036" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2037" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C2037" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D2037" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2037" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2038" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2038" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D2038" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2038" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2039" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2039" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D2039" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2039" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2040" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C2040" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D2040" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2040" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2041" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2041" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D2041" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2041" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2042" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C2042" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D2042" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2042" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2043" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2043" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D2043" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2043" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2044" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C2044" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D2044" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2044" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2045" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2045" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D2045" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2045" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2046" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2046" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D2046" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2046" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2047" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C2047" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D2047" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2047" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2048" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2048" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D2048" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2048" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2049" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2049" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D2049" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2049" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2050" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2050" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D2050" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2050" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2051" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2051" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D2051" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2051" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2052" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C2052" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D2052" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2052" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2053" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C2053" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D2053" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2053" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2054" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C2054" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D2054" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2054" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2055" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2055" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D2055" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2055" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2056" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2056" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2056" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2056" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2057" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C2057" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D2057" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2057" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2058" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2058" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D2058" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2058" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2059" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C2059" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D2059" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2059" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2060" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2060" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D2060" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2060" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2061" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C2061" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D2061" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2061" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2062" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C2062" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D2062" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2062" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2063" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2063" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D2063" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2063" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2064" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C2064" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2064" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2064" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2065" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C2065" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D2065" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2065" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2066" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2066" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D2066" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2066" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2067" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C2067" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D2067" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2067" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2068" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C2068" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D2068" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2068" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2069" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C2069" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D2069" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2069" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2070" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C2070" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D2070" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2070" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2071" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C2071" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D2071" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2071" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2072" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2072" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D2072" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2072" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2073" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C2073" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2073" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2073" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2074" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C2074" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2074" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2074" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2075" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C2075" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2075" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2075" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2076" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2076" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2076" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2076" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2077" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C2077" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2077" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2077" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2078" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2078" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2078" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2078" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2079" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C2079" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2079" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2079" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2080" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C2080" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2080" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2080" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2081" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C2081" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2081" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2081" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2082" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C2082" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2082" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2082" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2083" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C2083" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2083" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2083" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2084" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2084" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2084" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2084" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="3" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2085" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2085" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2085" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2085" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2086" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C2086" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D2086" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2086" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2087" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C2087" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D2087" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2087" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2088" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2088" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D2088" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2088" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2089" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2089" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D2089" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2089" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2090" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C2090" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D2090" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2090" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2091" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2091" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D2091" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2091" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2092" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C2092" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D2092" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2092" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2093" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2093" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D2093" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2093" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2094" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C2094" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D2094" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2094" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2095" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2095" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D2095" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2095" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2096" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2096" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D2096" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2096" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2097" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C2097" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D2097" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2097" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2098" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2098" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D2098" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2098" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2099" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2099" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D2099" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2099" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2100" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2100" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D2100" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2100" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2101" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2101" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D2101" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2101" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2102" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C2102" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D2102" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2102" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2103" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C2103" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D2103" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2103" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2104" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C2104" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D2104" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2104" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2105" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2105" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D2105" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2105" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2106" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2106" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2106" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2106" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2107" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C2107" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D2107" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2107" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2108" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2108" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D2108" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2108" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2109" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C2109" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D2109" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2109" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2110" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2110" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D2110" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2110" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2111" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C2111" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D2111" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2111" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2112" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 febi</t>
+        </is>
+      </c>
+      <c r="C2112" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D2112" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2112" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2113" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2113" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D2113" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2113" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2114" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 замена</t>
+        </is>
+      </c>
+      <c r="C2114" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2114" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2114" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2115" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C2115" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D2115" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2115" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2116" s="3" t="inlineStr">
+        <is>
+          <t>какое масло заливать в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2116" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D2116" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2116" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2117" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C2117" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D2117" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2117" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2118" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C2118" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D2118" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2118" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2119" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 febi</t>
+        </is>
+      </c>
+      <c r="C2119" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D2119" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2119" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2120" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник коробки dq200</t>
+        </is>
+      </c>
+      <c r="C2120" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D2120" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2120" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2121" s="3" t="inlineStr">
+        <is>
+          <t>dq200 плата мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C2121" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D2121" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2121" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2122" s="3" t="inlineStr">
+        <is>
+          <t>замена масла мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2122" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D2122" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2122" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2123" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 цена</t>
+        </is>
+      </c>
+      <c r="C2123" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2123" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2123" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2124" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник в сборе dq200</t>
+        </is>
+      </c>
+      <c r="C2124" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2124" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2124" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2125" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 сколько масла</t>
+        </is>
+      </c>
+      <c r="C2125" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2125" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2125" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2126" s="3" t="inlineStr">
+        <is>
+          <t>жидкость в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2126" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2126" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2126" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2127" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 0am</t>
+        </is>
+      </c>
+      <c r="C2127" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2127" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2127" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2128" s="3" t="inlineStr">
+        <is>
+          <t>плата управления мехатроником дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2128" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2128" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2128" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2129" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 замена</t>
+        </is>
+      </c>
+      <c r="C2129" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2129" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2129" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2130" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремкомплект</t>
+        </is>
+      </c>
+      <c r="C2130" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2130" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2130" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2131" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 ремонт</t>
+        </is>
+      </c>
+      <c r="C2131" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2131" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2131" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2132" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 оригинальный</t>
+        </is>
+      </c>
+      <c r="C2132" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2132" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2132" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2133" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 гидроплита</t>
+        </is>
+      </c>
+      <c r="C2133" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2133" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2133" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2134" s="3" t="inlineStr">
+        <is>
+          <t>замена масла в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2134" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2134" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2134" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="3" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+      <c r="B2135" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2135" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2135" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2135" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759"/>
+  <autoFilter ref="A1:E2135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/seo_keywords.xlsx
+++ b/data/seo_keywords.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Тексты Ozon-WB" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$2135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Семантика'!$A$1:$E$2285</definedName>
   </definedNames>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2135"/>
+  <dimension ref="A1:E2285"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -54456,8 +54456,3758 @@
         </is>
       </c>
     </row>
+    <row r="2136">
+      <c r="A2136" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2136" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C2136" s="3" t="n">
+        <v>3433</v>
+      </c>
+      <c r="D2136" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2136" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2137" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник</t>
+        </is>
+      </c>
+      <c r="C2137" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D2137" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2137" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2138" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2138" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="D2138" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2138" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2139" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2139" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="D2139" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2139" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2140" s="3" t="inlineStr">
+        <is>
+          <t>dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C2140" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D2140" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2140" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2141" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2141" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D2141" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2141" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2142" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 масло в мехатроник</t>
+        </is>
+      </c>
+      <c r="C2142" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="D2142" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2142" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2143" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2143" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="D2143" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2143" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2144" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 мехатроник купить</t>
+        </is>
+      </c>
+      <c r="C2144" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="D2144" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2144" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2145" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dsg 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2145" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D2145" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2145" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2146" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2146" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="D2146" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2146" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2147" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг dq200</t>
+        </is>
+      </c>
+      <c r="C2147" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D2147" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2147" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2148" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник на дсг 7 dq200 купить</t>
+        </is>
+      </c>
+      <c r="C2148" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D2148" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2148" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2149" s="3" t="inlineStr">
+        <is>
+          <t>как снять мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2149" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D2149" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2149" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2150" s="3" t="inlineStr">
+        <is>
+          <t>новый мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2150" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D2150" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2150" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2151" s="3" t="inlineStr">
+        <is>
+          <t>масло в мехатроник дсг 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2151" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D2151" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2151" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2152" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 купить новый</t>
+        </is>
+      </c>
+      <c r="C2152" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D2152" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2152" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2153" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 цена</t>
+        </is>
+      </c>
+      <c r="C2153" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D2153" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2153" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2154" s="3" t="inlineStr">
+        <is>
+          <t>dsg 7 dq200 новый мехатроник</t>
+        </is>
+      </c>
+      <c r="C2154" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D2154" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2154" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2155" s="3" t="inlineStr">
+        <is>
+          <t>какое масло в мехатроник dsg 7 dq200</t>
+        </is>
+      </c>
+      <c r="C2155" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D2155" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2155" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2156" s="3" t="inlineStr">
+        <is>
+          <t>плата мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2156" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2156" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2156" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2157" s="3" t="inlineStr">
+        <is>
+          <t>мехатроник dq200 артикул</t>
+        </is>
+      </c>
+      <c r="C2157" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D2157" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2157" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2158" s="3" t="inlineStr">
+        <is>
+          <t>какое масло лить в мехатроник dq200</t>
+        </is>
+      </c>
+      <c r="C2158" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D2158" s="3" t="inlineStr">
+        <is>
+          <t>wordstat_api</t>
+        </is>
+      </c>
+      <c r="E2158" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" s="3" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B2159" s="3" t="inlineStr">
+        <is>
+          <t>dsg dq200 как снять мехатроник</t>
+        </is>
+      </c>
+      <c r="C2159" s="3" t="n">
+        <v>73</v>
+ 